--- a/output/Utair статус 02.10.2026.xlsx
+++ b/output/Utair статус 02.10.2026.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Отгружено'!$A$1:$BM$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'В работе'!$A$1:$BM$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'В работе'!$A$1:$BM$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -686,7 +686,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дата отчёта: 02.10.2026   |   В работе: 52 поз.   |   Отгружено: 49 поз.</t>
+          <t>Дата отчёта: 02.10.2026   |   В работе: 51 поз.   |   Отгружено: 49 поз.</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>704099</v>
+        <v>702099</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>657488.5</v>
@@ -782,22 +782,22 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>486997.15</v>
+        <v>486807.15</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>33100</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>18981.399419</v>
+        <v>18971.614419</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>704099</v>
+        <v>702099</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>165020.450581</v>
+        <v>163220.235581</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>46610.5</v>
+        <v>44610.5</v>
       </c>
       <c r="H10" s="13" t="n">
         <v>657488.5</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="M33" s="19" t="inlineStr">
         <is>
-          <t>статус → отгружено; дата поставки в периоде</t>
+          <t>дата поставки в периоде</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM54"/>
+  <dimension ref="A1:BM53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15877,18 +15877,18 @@
       <c r="AD2" s="27" t="n"/>
       <c r="AE2" s="27" t="n"/>
       <c r="AF2" s="28" t="n">
-        <v>486997.15</v>
+        <v>486807.15</v>
       </c>
       <c r="AG2" s="27" t="n"/>
       <c r="AH2" s="28" t="n">
-        <v>704099</v>
+        <v>702099</v>
       </c>
       <c r="AI2" s="28" t="n">
         <v>33100</v>
       </c>
       <c r="AJ2" s="27" t="n"/>
       <c r="AK2" s="28" t="n">
-        <v>18981.399419</v>
+        <v>18971.614419</v>
       </c>
       <c r="AL2" s="27" t="n"/>
       <c r="AM2" s="27" t="n"/>
@@ -15898,7 +15898,7 @@
       <c r="AQ2" s="27" t="n"/>
       <c r="AR2" s="27" t="n"/>
       <c r="AS2" s="28" t="n">
-        <v>46610.5</v>
+        <v>44610.5</v>
       </c>
       <c r="AT2" s="27" t="n"/>
       <c r="AU2" s="27" t="n"/>
@@ -19407,7 +19407,7 @@
     </row>
     <row r="17">
       <c r="A17" s="29" t="n">
-        <v>10082615365</v>
+        <v>12082610355</v>
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
@@ -19424,15 +19424,15 @@
           <t>KDV-1</t>
         </is>
       </c>
-      <c r="E17" s="40" t="inlineStr">
-        <is>
-          <t>1 NOT PAID</t>
+      <c r="E17" s="41" t="inlineStr">
+        <is>
+          <t>6 TROUBLE</t>
         </is>
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20318726</t>
+          <t>DAT MOW
+P20339826</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
@@ -19457,19 +19457,21 @@
       </c>
       <c r="K17" s="29" t="inlineStr">
         <is>
-          <t>137-00-870-14GK</t>
-        </is>
-      </c>
-      <c r="L17" s="29" t="n">
-        <v/>
+          <t>CF2051</t>
+        </is>
+      </c>
+      <c r="L17" s="29" t="inlineStr">
+        <is>
+          <t>CF-2051</t>
+        </is>
       </c>
       <c r="M17" s="29" t="inlineStr">
         <is>
-          <t>SHROUD, IAT AISLE OUTER</t>
+          <t>CAM FOLLOWER</t>
         </is>
       </c>
       <c r="N17" s="31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O17" s="29" t="inlineStr">
         <is>
@@ -19482,10 +19484,10 @@
         </is>
       </c>
       <c r="Q17" s="32" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="R17" s="29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="S17" s="29" t="inlineStr">
         <is>
@@ -19499,14 +19501,14 @@
         <v/>
       </c>
       <c r="V17" s="32" t="n">
-        <v>46254</v>
-      </c>
-      <c r="W17" s="32" t="n">
-        <v>46244</v>
+        <v>46271</v>
+      </c>
+      <c r="W17" s="29" t="n">
+        <v/>
       </c>
       <c r="X17" s="29" t="inlineStr">
         <is>
-          <t>Продажа со склада</t>
+          <t>Продажа от поставщика</t>
         </is>
       </c>
       <c r="Y17" s="29" t="inlineStr">
@@ -19514,8 +19516,10 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="Z17" s="29" t="n">
-        <v/>
+      <c r="Z17" s="29" t="inlineStr">
+        <is>
+          <t>BLUE OCEAN SOLUTIONS</t>
+        </is>
       </c>
       <c r="AA17" s="29" t="n">
         <v/>
@@ -19525,23 +19529,23 @@
       </c>
       <c r="AC17" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>№2248 - cancel</t>
         </is>
       </c>
       <c r="AD17" s="29" t="n">
         <v/>
       </c>
       <c r="AE17" s="33" t="n">
-        <v>190</v>
+        <v>671.5</v>
       </c>
       <c r="AF17" s="33" t="n">
-        <v>190</v>
+        <v>4700.5</v>
       </c>
       <c r="AG17" s="33" t="n">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="AH17" s="33" t="n">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="AI17" s="33" t="n">
         <v>0</v>
@@ -19550,7 +19554,7 @@
         <v/>
       </c>
       <c r="AK17" s="33" t="n">
-        <v>9.785</v>
+        <v>242.07575</v>
       </c>
       <c r="AL17" s="33" t="n">
         <v/>
@@ -19571,7 +19575,7 @@
       </c>
       <c r="AQ17" s="29" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
+          <t>Частичная предоплата</t>
         </is>
       </c>
       <c r="AR17" s="29" t="n">
@@ -19580,14 +19584,14 @@
       <c r="AS17" s="33" t="n">
         <v/>
       </c>
-      <c r="AT17" s="32" t="n">
-        <v>46289</v>
+      <c r="AT17" s="29" t="n">
+        <v/>
       </c>
       <c r="AU17" s="33" t="n">
-        <v>2000</v>
+        <v/>
       </c>
       <c r="AV17" s="33" t="n">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="AW17" s="29" t="n">
         <v/>
@@ -19596,19 +19600,23 @@
         <v/>
       </c>
       <c r="AY17" s="29" t="n">
-        <v>190</v>
+        <v>4700.5</v>
       </c>
       <c r="AZ17" s="34" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="BA17" s="29" t="n">
         <v/>
       </c>
-      <c r="BB17" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BC17" s="29" t="n">
-        <v/>
+      <c r="BB17" s="29" t="inlineStr">
+        <is>
+          <t>UNSOLVED</t>
+        </is>
+      </c>
+      <c r="BC17" s="29" t="inlineStr">
+        <is>
+          <t>Sold, new price too high, ищем с Даней</t>
+        </is>
       </c>
       <c r="BD17" s="29" t="n">
         <v/>
@@ -19643,7 +19651,7 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>12082610355</v>
+        <v>13082611355</v>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
@@ -19657,18 +19665,18 @@
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>KDV-1</t>
-        </is>
-      </c>
-      <c r="E18" s="41" t="inlineStr">
-        <is>
-          <t>6 TROUBLE</t>
+          <t>KDV-3+RAP</t>
+        </is>
+      </c>
+      <c r="E18" s="39" t="inlineStr">
+        <is>
+          <t>2 PAID</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20339826</t>
+          <t>DDP MOW
+P20349026</t>
         </is>
       </c>
       <c r="G18" s="19" t="inlineStr">
@@ -19683,31 +19691,28 @@
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J18" s="19" t="inlineStr">
         <is>
-          <t>B735</t>
-        </is>
-      </c>
-      <c r="K18" s="19" t="inlineStr">
-        <is>
-          <t>CF2051</t>
-        </is>
-      </c>
-      <c r="L18" s="19" t="inlineStr">
-        <is>
-          <t>CF-2051</t>
-        </is>
+          <t>B738</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>902862</v>
+      </c>
+      <c r="L18" s="19" t="n">
+        <v/>
       </c>
       <c r="M18" s="19" t="inlineStr">
         <is>
-          <t>CAM FOLLOWER</t>
+          <t>FIRE DETECTOR
+ASSY</t>
         </is>
       </c>
       <c r="N18" s="20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O18" s="19" t="inlineStr">
         <is>
@@ -19716,11 +19721,11 @@
       </c>
       <c r="P18" s="19" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q18" s="35" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="R18" s="19" t="n">
         <v>25</v>
@@ -19733,11 +19738,13 @@
       <c r="T18" s="19" t="n">
         <v/>
       </c>
-      <c r="U18" s="19" t="n">
-        <v/>
+      <c r="U18" s="19" t="inlineStr">
+        <is>
+          <t>PRIORITY NET</t>
+        </is>
       </c>
       <c r="V18" s="35" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="W18" s="19" t="n">
         <v/>
@@ -19749,69 +19756,76 @@
       </c>
       <c r="Y18" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z18" s="19" t="inlineStr">
         <is>
-          <t>BLUE OCEAN SOLUTIONS</t>
+          <t>LUFTHANSA</t>
         </is>
       </c>
       <c r="AA18" s="19" t="n">
         <v/>
       </c>
-      <c r="AB18" s="19" t="n">
-        <v/>
+      <c r="AB18" s="19" t="inlineStr">
+        <is>
+          <t>JP160926-1</t>
+        </is>
       </c>
       <c r="AC18" s="19" t="inlineStr">
         <is>
-          <t>№2248 - cancel</t>
-        </is>
-      </c>
-      <c r="AD18" s="19" t="n">
-        <v/>
+          <t>#6134</t>
+        </is>
+      </c>
+      <c r="AD18" s="19" t="inlineStr">
+        <is>
+          <t>3766
+9436 - sold</t>
+        </is>
       </c>
       <c r="AE18" s="21" t="n">
-        <v>671.5</v>
+        <v>10500</v>
       </c>
       <c r="AF18" s="21" t="n">
-        <v>4700.5</v>
+        <v>10500</v>
       </c>
       <c r="AG18" s="21" t="n">
-        <v>1100</v>
+        <v>14500</v>
       </c>
       <c r="AH18" s="21" t="n">
-        <v>7700</v>
+        <v>14500</v>
       </c>
       <c r="AI18" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AK18" s="21" t="n">
+        <v>540.75</v>
+      </c>
+      <c r="AL18" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AM18" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AN18" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ18" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AK18" s="21" t="n">
-        <v>242.07575</v>
-      </c>
-      <c r="AL18" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AM18" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AN18" s="19" t="n">
-        <v>0.22</v>
-      </c>
       <c r="AO18" s="19" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP18" s="19" t="n">
-        <v/>
+          <t>ЕСТЬ МПТ на Самолеты типов Boeing 737</t>
+        </is>
+      </c>
+      <c r="AP18" s="19" t="inlineStr">
+        <is>
+          <t>Есть МПТ</t>
+        </is>
       </c>
       <c r="AQ18" s="19" t="inlineStr">
         <is>
-          <t>Частичная предоплата</t>
+          <t>Постоплата 100%</t>
         </is>
       </c>
       <c r="AR18" s="19" t="n">
@@ -19827,41 +19841,43 @@
         <v/>
       </c>
       <c r="AV18" s="21" t="n">
-        <v>7700</v>
-      </c>
-      <c r="AW18" s="19" t="n">
-        <v/>
+        <v>14500</v>
+      </c>
+      <c r="AW18" s="36" t="n">
+        <v>46297</v>
       </c>
       <c r="AX18" s="19" t="n">
-        <v/>
+        <v>10500</v>
       </c>
       <c r="AY18" s="19" t="n">
-        <v>4700.5</v>
+        <v>0</v>
       </c>
       <c r="AZ18" s="36" t="n">
-        <v>46246</v>
+        <v>46274</v>
       </c>
       <c r="BA18" s="19" t="n">
         <v/>
       </c>
       <c r="BB18" s="19" t="inlineStr">
         <is>
-          <t>UNSOLVED</t>
+          <t>arrived at DXB and is under customs clearance</t>
         </is>
       </c>
       <c r="BC18" s="19" t="inlineStr">
         <is>
-          <t>Sold, new price too high, ищем с Даней</t>
+          <t>до 05.10</t>
         </is>
       </c>
       <c r="BD18" s="19" t="n">
         <v/>
       </c>
       <c r="BE18" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BF18" s="19" t="n">
-        <v/>
+        <v>11600</v>
+      </c>
+      <c r="BF18" s="19" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
       </c>
       <c r="BG18" s="19" t="n">
         <v/>
@@ -19872,8 +19888,10 @@
       <c r="BI18" s="19" t="n">
         <v/>
       </c>
-      <c r="BJ18" s="19" t="n">
-        <v/>
+      <c r="BJ18" s="19" t="inlineStr">
+        <is>
+          <t>160926-1</t>
+        </is>
       </c>
       <c r="BK18" s="19" t="n">
         <v/>
@@ -19887,7 +19905,7 @@
     </row>
     <row r="19">
       <c r="A19" s="29" t="n">
-        <v>13082611355</v>
+        <v>19082612405</v>
       </c>
       <c r="B19" s="29" t="inlineStr">
         <is>
@@ -19912,7 +19930,7 @@
       <c r="F19" s="29" t="inlineStr">
         <is>
           <t>DDP MOW
-P20349026</t>
+P20368026</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
@@ -19932,19 +19950,21 @@
       </c>
       <c r="J19" s="29" t="inlineStr">
         <is>
-          <t>B738</t>
-        </is>
-      </c>
-      <c r="K19" s="29" t="n">
-        <v>902862</v>
+          <t>B737</t>
+        </is>
+      </c>
+      <c r="K19" s="29" t="inlineStr">
+        <is>
+          <t>102LA2AG</t>
+        </is>
       </c>
       <c r="L19" s="29" t="n">
         <v/>
       </c>
       <c r="M19" s="29" t="inlineStr">
         <is>
-          <t>FIRE DETECTOR
-ASSY</t>
+          <t>SENSOR-TOTAL AIR
+TEMPERATURE</t>
         </is>
       </c>
       <c r="N19" s="31" t="n">
@@ -19961,7 +19981,7 @@
         </is>
       </c>
       <c r="Q19" s="32" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="R19" s="29" t="n">
         <v>25</v>
@@ -19976,11 +19996,11 @@
       </c>
       <c r="U19" s="29" t="inlineStr">
         <is>
-          <t>PRIORITY NET</t>
+          <t>POST AUG-26</t>
         </is>
       </c>
       <c r="V19" s="32" t="n">
-        <v>46272</v>
+        <v>46278</v>
       </c>
       <c r="W19" s="29" t="n">
         <v/>
@@ -19992,53 +20012,54 @@
       </c>
       <c r="Y19" s="29" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="Z19" s="29" t="inlineStr">
         <is>
-          <t>LUFTHANSA</t>
-        </is>
-      </c>
-      <c r="AA19" s="29" t="n">
-        <v/>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="AA19" s="29" t="inlineStr">
+        <is>
+          <t>FLIGHT AEROTECH</t>
+        </is>
       </c>
       <c r="AB19" s="29" t="inlineStr">
         <is>
-          <t>JP160926-1</t>
+          <t>KTM51908251513</t>
         </is>
       </c>
       <c r="AC19" s="29" t="inlineStr">
         <is>
-          <t>#6134</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AD19" s="29" t="inlineStr">
         <is>
-          <t>3766
-9436 - sold</t>
+          <t>A28158</t>
         </is>
       </c>
       <c r="AE19" s="33" t="n">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="AF19" s="33" t="n">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="AG19" s="33" t="n">
-        <v>14500</v>
+        <v>16500</v>
       </c>
       <c r="AH19" s="33" t="n">
-        <v>14500</v>
+        <v>16500</v>
       </c>
       <c r="AI19" s="33" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ19" s="33" t="n">
         <v/>
       </c>
       <c r="AK19" s="33" t="n">
-        <v>540.75</v>
+        <v>618</v>
       </c>
       <c r="AL19" s="33" t="n">
         <v/>
@@ -20061,7 +20082,7 @@
       </c>
       <c r="AQ19" s="29" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
+          <t>Частичная предоплата</t>
         </is>
       </c>
       <c r="AR19" s="29" t="n">
@@ -20077,38 +20098,38 @@
         <v/>
       </c>
       <c r="AV19" s="33" t="n">
-        <v>14500</v>
+        <v>16500</v>
       </c>
       <c r="AW19" s="34" t="n">
-        <v>46297</v>
+        <v>46261</v>
       </c>
       <c r="AX19" s="29" t="n">
-        <v>10500</v>
+        <v>12000</v>
       </c>
       <c r="AY19" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AZ19" s="34" t="n">
-        <v>46274</v>
+        <v>46253</v>
       </c>
       <c r="BA19" s="29" t="n">
         <v/>
       </c>
       <c r="BB19" s="29" t="inlineStr">
         <is>
-          <t>arrived at DXB and is under customs clearance</t>
+          <t>Dubai now</t>
         </is>
       </c>
       <c r="BC19" s="29" t="inlineStr">
         <is>
-          <t>до 05.10</t>
+          <t>до 01.10</t>
         </is>
       </c>
       <c r="BD19" s="29" t="n">
         <v/>
       </c>
       <c r="BE19" s="29" t="n">
-        <v>11600</v>
+        <v>13200</v>
       </c>
       <c r="BF19" s="29" t="inlineStr">
         <is>
@@ -20126,7 +20147,7 @@
       </c>
       <c r="BJ19" s="29" t="inlineStr">
         <is>
-          <t>160926-1</t>
+          <t>KT MNT CONSOLE-5</t>
         </is>
       </c>
       <c r="BK19" s="29" t="n">
@@ -20141,7 +20162,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>19082612405</v>
+        <v>24082615515</v>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
@@ -20155,18 +20176,18 @@
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>KDV-3+RAP</t>
-        </is>
-      </c>
-      <c r="E20" s="39" t="inlineStr">
-        <is>
-          <t>2 PAID</t>
+          <t>KDV-1</t>
+        </is>
+      </c>
+      <c r="E20" s="41" t="inlineStr">
+        <is>
+          <t>6 TROUBLE</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20368026</t>
+          <t>DAT MOW
+P20388326</t>
         </is>
       </c>
       <c r="G20" s="19" t="inlineStr">
@@ -20181,30 +20202,31 @@
       </c>
       <c r="I20" s="19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J20" s="19" t="inlineStr">
         <is>
-          <t>B737</t>
+          <t>B734</t>
         </is>
       </c>
       <c r="K20" s="19" t="inlineStr">
         <is>
-          <t>102LA2AG</t>
-        </is>
-      </c>
-      <c r="L20" s="19" t="n">
-        <v/>
+          <t>T30L9M4</t>
+        </is>
+      </c>
+      <c r="L20" s="19" t="inlineStr">
+        <is>
+          <t>T30L-9</t>
+        </is>
       </c>
       <c r="M20" s="19" t="inlineStr">
         <is>
-          <t>SENSOR-TOTAL AIR
-TEMPERATURE</t>
+          <t>TIE WRAP LONG</t>
         </is>
       </c>
       <c r="N20" s="20" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
@@ -20213,14 +20235,14 @@
       </c>
       <c r="P20" s="19" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q20" s="35" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="R20" s="19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="S20" s="19" t="inlineStr">
         <is>
@@ -20230,13 +20252,11 @@
       <c r="T20" s="19" t="n">
         <v/>
       </c>
-      <c r="U20" s="19" t="inlineStr">
-        <is>
-          <t>POST AUG-26</t>
-        </is>
+      <c r="U20" s="19" t="n">
+        <v/>
       </c>
       <c r="V20" s="35" t="n">
-        <v>46278</v>
+        <v>46288</v>
       </c>
       <c r="W20" s="19" t="n">
         <v/>
@@ -20248,54 +20268,48 @@
       </c>
       <c r="Y20" s="19" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z20" s="19" t="inlineStr">
         <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="AA20" s="19" t="inlineStr">
-        <is>
-          <t>FLIGHT AEROTECH</t>
-        </is>
-      </c>
-      <c r="AB20" s="19" t="inlineStr">
-        <is>
-          <t>KTM51908251513</t>
-        </is>
+          <t>BLUE OCEAN SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="AA20" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AB20" s="19" t="n">
+        <v/>
       </c>
       <c r="AC20" s="19" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD20" s="19" t="inlineStr">
-        <is>
-          <t>A28158</t>
-        </is>
+          <t>№2318</t>
+        </is>
+      </c>
+      <c r="AD20" s="19" t="n">
+        <v/>
       </c>
       <c r="AE20" s="21" t="n">
-        <v>12000</v>
+        <v>1.4</v>
       </c>
       <c r="AF20" s="21" t="n">
-        <v>12000</v>
+        <v>112</v>
       </c>
       <c r="AG20" s="21" t="n">
-        <v>16500</v>
+        <v>4</v>
       </c>
       <c r="AH20" s="21" t="n">
-        <v>16500</v>
+        <v>320</v>
       </c>
       <c r="AI20" s="21" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AJ20" s="21" t="n">
         <v/>
       </c>
       <c r="AK20" s="21" t="n">
-        <v>618</v>
+        <v>5.768</v>
       </c>
       <c r="AL20" s="21" t="n">
         <v/>
@@ -20304,21 +20318,19 @@
         <v/>
       </c>
       <c r="AN20" s="19" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO20" s="19" t="inlineStr">
         <is>
-          <t>ЕСТЬ МПТ на Самолеты типов Boeing 737</t>
-        </is>
-      </c>
-      <c r="AP20" s="19" t="inlineStr">
-        <is>
-          <t>Есть МПТ</t>
-        </is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP20" s="19" t="n">
+        <v/>
       </c>
       <c r="AQ20" s="19" t="inlineStr">
         <is>
-          <t>Частичная предоплата</t>
+          <t>Постоплата 100%</t>
         </is>
       </c>
       <c r="AR20" s="19" t="n">
@@ -20334,43 +20346,41 @@
         <v/>
       </c>
       <c r="AV20" s="21" t="n">
-        <v>16500</v>
-      </c>
-      <c r="AW20" s="36" t="n">
-        <v>46261</v>
+        <v>320</v>
+      </c>
+      <c r="AW20" s="19" t="n">
+        <v/>
       </c>
       <c r="AX20" s="19" t="n">
-        <v>12000</v>
+        <v/>
       </c>
       <c r="AY20" s="19" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="AZ20" s="36" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="BA20" s="19" t="n">
         <v/>
       </c>
       <c r="BB20" s="19" t="inlineStr">
         <is>
-          <t>Dubai now</t>
+          <t>UNSOLVED</t>
         </is>
       </c>
       <c r="BC20" s="19" t="inlineStr">
         <is>
-          <t>до 01.10</t>
+          <t>UNSOLVED, MOQ - 1000ea</t>
         </is>
       </c>
       <c r="BD20" s="19" t="n">
         <v/>
       </c>
       <c r="BE20" s="19" t="n">
-        <v>13200</v>
-      </c>
-      <c r="BF20" s="19" t="inlineStr">
-        <is>
-          <t>Ф</t>
-        </is>
+        <v/>
+      </c>
+      <c r="BF20" s="19" t="n">
+        <v/>
       </c>
       <c r="BG20" s="19" t="n">
         <v/>
@@ -20381,10 +20391,8 @@
       <c r="BI20" s="19" t="n">
         <v/>
       </c>
-      <c r="BJ20" s="19" t="inlineStr">
-        <is>
-          <t>KT MNT CONSOLE-5</t>
-        </is>
+      <c r="BJ20" s="19" t="n">
+        <v/>
       </c>
       <c r="BK20" s="19" t="n">
         <v/>
@@ -20398,7 +20406,7 @@
     </row>
     <row r="21">
       <c r="A21" s="29" t="n">
-        <v>24082615515</v>
+        <v>26082610155</v>
       </c>
       <c r="B21" s="29" t="inlineStr">
         <is>
@@ -20423,7 +20431,7 @@
       <c r="F21" s="29" t="inlineStr">
         <is>
           <t>DAT MOW
-P20388326</t>
+P20416026</t>
         </is>
       </c>
       <c r="G21" s="29" t="inlineStr">
@@ -20443,26 +20451,24 @@
       </c>
       <c r="J21" s="29" t="inlineStr">
         <is>
-          <t>B734</t>
+          <t>B738</t>
         </is>
       </c>
       <c r="K21" s="29" t="inlineStr">
         <is>
-          <t>T30L9M4</t>
-        </is>
-      </c>
-      <c r="L21" s="29" t="inlineStr">
-        <is>
-          <t>T30L-9</t>
-        </is>
+          <t>MS27502B19C</t>
+        </is>
+      </c>
+      <c r="L21" s="29" t="n">
+        <v/>
       </c>
       <c r="M21" s="29" t="inlineStr">
         <is>
-          <t>TIE WRAP LONG</t>
+          <t>COVER, ELECTRICAL CONNECTOR</t>
         </is>
       </c>
       <c r="N21" s="31" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="O21" s="29" t="inlineStr">
         <is>
@@ -20475,7 +20481,7 @@
         </is>
       </c>
       <c r="Q21" s="32" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="R21" s="29" t="n">
         <v>30</v>
@@ -20492,7 +20498,7 @@
         <v/>
       </c>
       <c r="V21" s="32" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="W21" s="29" t="n">
         <v/>
@@ -20520,23 +20526,23 @@
       </c>
       <c r="AC21" s="29" t="inlineStr">
         <is>
-          <t>№2318</t>
+          <t>№2334</t>
         </is>
       </c>
       <c r="AD21" s="29" t="n">
         <v/>
       </c>
       <c r="AE21" s="33" t="n">
-        <v>1.4</v>
+        <v>50</v>
       </c>
       <c r="AF21" s="33" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="AG21" s="33" t="n">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="AH21" s="33" t="n">
-        <v>320</v>
+        <v>256</v>
       </c>
       <c r="AI21" s="33" t="n">
         <v>0</v>
@@ -20545,7 +20551,7 @@
         <v/>
       </c>
       <c r="AK21" s="33" t="n">
-        <v>5.768</v>
+        <v>5.15</v>
       </c>
       <c r="AL21" s="33" t="n">
         <v/>
@@ -20582,7 +20588,7 @@
         <v/>
       </c>
       <c r="AV21" s="33" t="n">
-        <v>320</v>
+        <v>256</v>
       </c>
       <c r="AW21" s="29" t="n">
         <v/>
@@ -20591,10 +20597,10 @@
         <v/>
       </c>
       <c r="AY21" s="29" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="AZ21" s="34" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="BA21" s="29" t="n">
         <v/>
@@ -20606,7 +20612,7 @@
       </c>
       <c r="BC21" s="29" t="inlineStr">
         <is>
-          <t>UNSOLVED, MOQ - 1000ea</t>
+          <t>У оманца солд. Но вроде ищет ,пока не отменяю + Дане положила на поиск. Ютэйр предупрежден</t>
         </is>
       </c>
       <c r="BD21" s="29" t="n">
@@ -20642,7 +20648,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>26082610155</v>
+        <v>27082616305</v>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
@@ -20656,18 +20662,18 @@
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>KDV-1</t>
-        </is>
-      </c>
-      <c r="E22" s="41" t="inlineStr">
-        <is>
-          <t>6 TROUBLE</t>
+          <t>KDV-3+RAP</t>
+        </is>
+      </c>
+      <c r="E22" s="40" t="inlineStr">
+        <is>
+          <t>1 NOT PAID</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20416026</t>
+          <t>DDP MOW
+P20426126</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
@@ -20682,17 +20688,17 @@
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J22" s="19" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>ATR72</t>
         </is>
       </c>
       <c r="K22" s="19" t="inlineStr">
         <is>
-          <t>MS27502B19C</t>
+          <t>82425-00-0060</t>
         </is>
       </c>
       <c r="L22" s="19" t="n">
@@ -20700,11 +20706,12 @@
       </c>
       <c r="M22" s="19" t="inlineStr">
         <is>
-          <t>COVER, ELECTRICAL CONNECTOR</t>
+          <t>NAVIGATION
+PROCESSOR UNIT</t>
         </is>
       </c>
       <c r="N22" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O22" s="19" t="inlineStr">
         <is>
@@ -20713,11 +20720,11 @@
       </c>
       <c r="P22" s="19" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q22" s="35" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="R22" s="19" t="n">
         <v>30</v>
@@ -20734,7 +20741,7 @@
         <v/>
       </c>
       <c r="V22" s="35" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="W22" s="19" t="n">
         <v/>
@@ -20746,65 +20753,73 @@
       </c>
       <c r="Y22" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="Z22" s="19" t="inlineStr">
         <is>
-          <t>BLUE OCEAN SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="AA22" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AB22" s="19" t="n">
-        <v/>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="AA22" s="19" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+      <c r="AB22" s="19" t="inlineStr">
+        <is>
+          <t>KTM409261005</t>
+        </is>
       </c>
       <c r="AC22" s="19" t="inlineStr">
         <is>
-          <t>№2334</t>
-        </is>
-      </c>
-      <c r="AD22" s="19" t="n">
-        <v/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD22" s="19" t="inlineStr">
+        <is>
+          <t>32651633</t>
+        </is>
       </c>
       <c r="AE22" s="21" t="n">
-        <v>50</v>
+        <v>38500</v>
       </c>
       <c r="AF22" s="21" t="n">
-        <v>100</v>
+        <v>38500</v>
       </c>
       <c r="AG22" s="21" t="n">
-        <v>128</v>
+        <v>48900</v>
       </c>
       <c r="AH22" s="21" t="n">
-        <v>256</v>
+        <v>48900</v>
       </c>
       <c r="AI22" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AJ22" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AK22" s="21" t="n">
+        <v>1982.75</v>
+      </c>
+      <c r="AL22" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AM22" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AN22" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ22" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AK22" s="21" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AL22" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AM22" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AN22" s="19" t="n">
-        <v>0.22</v>
-      </c>
       <c r="AO22" s="19" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP22" s="19" t="n">
-        <v/>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP22" s="19" t="inlineStr">
+        <is>
+          <t>Получаем МПТ</t>
+        </is>
       </c>
       <c r="AQ22" s="19" t="inlineStr">
         <is>
@@ -20824,7 +20839,7 @@
         <v/>
       </c>
       <c r="AV22" s="21" t="n">
-        <v>256</v>
+        <v>48900</v>
       </c>
       <c r="AW22" s="19" t="n">
         <v/>
@@ -20833,23 +20848,19 @@
         <v/>
       </c>
       <c r="AY22" s="19" t="n">
-        <v>100</v>
+        <v>38500</v>
       </c>
       <c r="AZ22" s="36" t="n">
-        <v>46260</v>
+        <v>46269</v>
       </c>
       <c r="BA22" s="19" t="n">
         <v/>
       </c>
-      <c r="BB22" s="19" t="inlineStr">
-        <is>
-          <t>UNSOLVED</t>
-        </is>
-      </c>
-      <c r="BC22" s="19" t="inlineStr">
-        <is>
-          <t>У оманца солд. Но вроде ищет ,пока не отменяю + Дане положила на поиск. Ютэйр предупрежден</t>
-        </is>
+      <c r="BB22" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BC22" s="19" t="n">
+        <v/>
       </c>
       <c r="BD22" s="19" t="n">
         <v/>
@@ -20884,7 +20895,7 @@
     </row>
     <row r="23">
       <c r="A23" s="29" t="n">
-        <v>27082616305</v>
+        <v>4092612345</v>
       </c>
       <c r="B23" s="29" t="inlineStr">
         <is>
@@ -20898,7 +20909,7 @@
       </c>
       <c r="D23" s="29" t="inlineStr">
         <is>
-          <t>KDV-3+RAP</t>
+          <t>KDV-3</t>
         </is>
       </c>
       <c r="E23" s="40" t="inlineStr">
@@ -20909,7 +20920,7 @@
       <c r="F23" s="29" t="inlineStr">
         <is>
           <t>DDP MOW
-P20426126</t>
+P20461626</t>
         </is>
       </c>
       <c r="G23" s="29" t="inlineStr">
@@ -20929,21 +20940,22 @@
       </c>
       <c r="J23" s="29" t="inlineStr">
         <is>
-          <t>ATR72</t>
+          <t>737ALL</t>
         </is>
       </c>
       <c r="K23" s="29" t="inlineStr">
         <is>
-          <t>82425-00-0060</t>
-        </is>
-      </c>
-      <c r="L23" s="29" t="n">
-        <v/>
+          <t>RD-AX7308-01</t>
+        </is>
+      </c>
+      <c r="L23" s="29" t="inlineStr">
+        <is>
+          <t>RDAX7308-01</t>
+        </is>
       </c>
       <c r="M23" s="29" t="inlineStr">
         <is>
-          <t>NAVIGATION
-PROCESSOR UNIT</t>
+          <t>REPRODUCER</t>
         </is>
       </c>
       <c r="N23" s="31" t="n">
@@ -20960,15 +20972,13 @@
         </is>
       </c>
       <c r="Q23" s="32" t="n">
-        <v>46261</v>
+        <v>46269</v>
       </c>
       <c r="R23" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="S23" s="29" t="inlineStr">
-        <is>
-          <t>STK</t>
-        </is>
+      <c r="S23" s="29" t="n">
+        <v>8</v>
       </c>
       <c r="T23" s="29" t="n">
         <v/>
@@ -20977,7 +20987,7 @@
         <v/>
       </c>
       <c r="V23" s="32" t="n">
-        <v>46291</v>
+        <v>46299</v>
       </c>
       <c r="W23" s="29" t="n">
         <v/>
@@ -20989,54 +20999,48 @@
       </c>
       <c r="Y23" s="29" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="Z23" s="29" t="inlineStr">
         <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="AA23" s="29" t="inlineStr">
-        <is>
-          <t>PIONEER</t>
-        </is>
-      </c>
-      <c r="AB23" s="29" t="inlineStr">
-        <is>
-          <t>KTM409261005</t>
-        </is>
+          <t>LUFTHANSA</t>
+        </is>
+      </c>
+      <c r="AA23" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AB23" s="29" t="n">
+        <v/>
       </c>
       <c r="AC23" s="29" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD23" s="29" t="inlineStr">
-        <is>
-          <t>32651633</t>
-        </is>
+          <t>#6116</t>
+        </is>
+      </c>
+      <c r="AD23" s="29" t="n">
+        <v/>
       </c>
       <c r="AE23" s="33" t="n">
-        <v>38500</v>
+        <v>1610</v>
       </c>
       <c r="AF23" s="33" t="n">
-        <v>38500</v>
+        <v>1610</v>
       </c>
       <c r="AG23" s="33" t="n">
-        <v>48900</v>
+        <v>2800</v>
       </c>
       <c r="AH23" s="33" t="n">
-        <v>48900</v>
+        <v>2800</v>
       </c>
       <c r="AI23" s="33" t="n">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="AJ23" s="33" t="n">
         <v/>
       </c>
       <c r="AK23" s="33" t="n">
-        <v>1982.75</v>
+        <v>82.91500000000001</v>
       </c>
       <c r="AL23" s="33" t="n">
         <v/>
@@ -21075,7 +21079,7 @@
         <v/>
       </c>
       <c r="AV23" s="33" t="n">
-        <v>48900</v>
+        <v>2800</v>
       </c>
       <c r="AW23" s="29" t="n">
         <v/>
@@ -21084,16 +21088,20 @@
         <v/>
       </c>
       <c r="AY23" s="29" t="n">
-        <v>38500</v>
-      </c>
-      <c r="AZ23" s="34" t="n">
-        <v>46269</v>
+        <v>1610</v>
+      </c>
+      <c r="AZ23" s="29" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
       </c>
       <c r="BA23" s="29" t="n">
         <v/>
       </c>
-      <c r="BB23" s="29" t="n">
-        <v/>
+      <c r="BB23" s="29" t="inlineStr">
+        <is>
+          <t>UNCONFIRMED YET</t>
+        </is>
       </c>
       <c r="BC23" s="29" t="n">
         <v/>
@@ -21131,7 +21139,7 @@
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>4092612345</v>
+        <v>7092610195</v>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
@@ -21156,7 +21164,7 @@
       <c r="F24" s="19" t="inlineStr">
         <is>
           <t>DDP MOW
-P20461626</t>
+P20456326</t>
         </is>
       </c>
       <c r="G24" s="19" t="inlineStr">
@@ -21176,22 +21184,22 @@
       </c>
       <c r="J24" s="19" t="inlineStr">
         <is>
-          <t>737ALL</t>
+          <t>737CL</t>
         </is>
       </c>
       <c r="K24" s="19" t="inlineStr">
         <is>
-          <t>RD-AX7308-01</t>
+          <t>E-329E</t>
         </is>
       </c>
       <c r="L24" s="19" t="inlineStr">
         <is>
-          <t>RDAX7308-01</t>
+          <t>E329E</t>
         </is>
       </c>
       <c r="M24" s="19" t="inlineStr">
         <is>
-          <t>REPRODUCER</t>
+          <t>RELAY</t>
         </is>
       </c>
       <c r="N24" s="20" t="n">
@@ -21208,13 +21216,13 @@
         </is>
       </c>
       <c r="Q24" s="35" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="R24" s="19" t="n">
         <v>30</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T24" s="19" t="n">
         <v/>
@@ -21223,7 +21231,7 @@
         <v/>
       </c>
       <c r="V24" s="35" t="n">
-        <v>46299</v>
+        <v>46302</v>
       </c>
       <c r="W24" s="19" t="n">
         <v/>
@@ -21251,32 +21259,32 @@
       </c>
       <c r="AC24" s="19" t="inlineStr">
         <is>
-          <t>#6116</t>
+          <t>#6122</t>
         </is>
       </c>
       <c r="AD24" s="19" t="n">
         <v/>
       </c>
       <c r="AE24" s="21" t="n">
-        <v>1610</v>
+        <v>1500</v>
       </c>
       <c r="AF24" s="21" t="n">
-        <v>1610</v>
+        <v>1500</v>
       </c>
       <c r="AG24" s="21" t="n">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="AH24" s="21" t="n">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="AI24" s="21" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AJ24" s="21" t="n">
         <v/>
       </c>
       <c r="AK24" s="21" t="n">
-        <v>82.91500000000001</v>
+        <v>77.25</v>
       </c>
       <c r="AL24" s="21" t="n">
         <v/>
@@ -21315,7 +21323,7 @@
         <v/>
       </c>
       <c r="AV24" s="21" t="n">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="AW24" s="19" t="n">
         <v/>
@@ -21324,7 +21332,7 @@
         <v/>
       </c>
       <c r="AY24" s="19" t="n">
-        <v>1610</v>
+        <v>1500</v>
       </c>
       <c r="AZ24" s="19" t="inlineStr">
         <is>
@@ -21375,7 +21383,7 @@
     </row>
     <row r="25">
       <c r="A25" s="29" t="n">
-        <v>7092610195</v>
+        <v>9092611085</v>
       </c>
       <c r="B25" s="29" t="inlineStr">
         <is>
@@ -21400,7 +21408,7 @@
       <c r="F25" s="29" t="inlineStr">
         <is>
           <t>DDP MOW
-P20456326</t>
+P20478226</t>
         </is>
       </c>
       <c r="G25" s="29" t="inlineStr">
@@ -21420,22 +21428,22 @@
       </c>
       <c r="J25" s="29" t="inlineStr">
         <is>
-          <t>737CL</t>
+          <t>737ALL</t>
         </is>
       </c>
       <c r="K25" s="29" t="inlineStr">
         <is>
-          <t>E-329E</t>
+          <t>CGAB1400-00</t>
         </is>
       </c>
       <c r="L25" s="29" t="inlineStr">
         <is>
-          <t>E329E</t>
+          <t>CGAB1400-01</t>
         </is>
       </c>
       <c r="M25" s="29" t="inlineStr">
         <is>
-          <t>RELAY</t>
+          <t>SMOKE DETECTOR</t>
         </is>
       </c>
       <c r="N25" s="31" t="n">
@@ -21452,13 +21460,13 @@
         </is>
       </c>
       <c r="Q25" s="32" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="R25" s="29" t="n">
         <v>30</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T25" s="29" t="n">
         <v/>
@@ -21467,7 +21475,7 @@
         <v/>
       </c>
       <c r="V25" s="32" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="W25" s="29" t="n">
         <v/>
@@ -21495,23 +21503,23 @@
       </c>
       <c r="AC25" s="29" t="inlineStr">
         <is>
-          <t>#6122</t>
+          <t>#6133</t>
         </is>
       </c>
       <c r="AD25" s="29" t="n">
         <v/>
       </c>
       <c r="AE25" s="33" t="n">
-        <v>1500</v>
+        <v>1610</v>
       </c>
       <c r="AF25" s="33" t="n">
-        <v>1500</v>
+        <v>1610</v>
       </c>
       <c r="AG25" s="33" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="AH25" s="33" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="AI25" s="33" t="n">
         <v>150</v>
@@ -21520,7 +21528,7 @@
         <v/>
       </c>
       <c r="AK25" s="33" t="n">
-        <v>77.25</v>
+        <v>80.7415</v>
       </c>
       <c r="AL25" s="33" t="n">
         <v/>
@@ -21559,7 +21567,7 @@
         <v/>
       </c>
       <c r="AV25" s="33" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="AW25" s="29" t="n">
         <v/>
@@ -21568,7 +21576,7 @@
         <v/>
       </c>
       <c r="AY25" s="29" t="n">
-        <v>1500</v>
+        <v>1610</v>
       </c>
       <c r="AZ25" s="29" t="inlineStr">
         <is>
@@ -21619,7 +21627,7 @@
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>9092611085</v>
+        <v>10092610465</v>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
@@ -21644,7 +21652,7 @@
       <c r="F26" s="19" t="inlineStr">
         <is>
           <t>DDP MOW
-P20478226</t>
+P20486326</t>
         </is>
       </c>
       <c r="G26" s="19" t="inlineStr">
@@ -21664,22 +21672,20 @@
       </c>
       <c r="J26" s="19" t="inlineStr">
         <is>
-          <t>737ALL</t>
+          <t>ATR72</t>
         </is>
       </c>
       <c r="K26" s="19" t="inlineStr">
         <is>
-          <t>CGAB1400-00</t>
-        </is>
-      </c>
-      <c r="L26" s="19" t="inlineStr">
-        <is>
-          <t>CGAB1400-01</t>
-        </is>
+          <t>301-2640</t>
+        </is>
+      </c>
+      <c r="L26" s="19" t="n">
+        <v/>
       </c>
       <c r="M26" s="19" t="inlineStr">
         <is>
-          <t>SMOKE DETECTOR</t>
+          <t>ATTENDANT PANEL</t>
         </is>
       </c>
       <c r="N26" s="20" t="n">
@@ -21696,13 +21702,13 @@
         </is>
       </c>
       <c r="Q26" s="35" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="R26" s="19" t="n">
         <v>30</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T26" s="19" t="n">
         <v/>
@@ -21711,7 +21717,7 @@
         <v/>
       </c>
       <c r="V26" s="35" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="W26" s="19" t="n">
         <v/>
@@ -21723,48 +21729,52 @@
       </c>
       <c r="Y26" s="19" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z26" s="19" t="inlineStr">
         <is>
-          <t>LUFTHANSA</t>
-        </is>
-      </c>
-      <c r="AA26" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AB26" s="19" t="n">
-        <v/>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="AA26" s="19" t="inlineStr">
+        <is>
+          <t>ALOIA AEROSPACE</t>
+        </is>
+      </c>
+      <c r="AB26" s="19" t="inlineStr">
+        <is>
+          <t>KTM1009261616</t>
+        </is>
       </c>
       <c r="AC26" s="19" t="inlineStr">
         <is>
-          <t>#6133</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AD26" s="19" t="n">
         <v/>
       </c>
       <c r="AE26" s="21" t="n">
-        <v>1610</v>
+        <v>11500</v>
       </c>
       <c r="AF26" s="21" t="n">
-        <v>1610</v>
+        <v>11500</v>
       </c>
       <c r="AG26" s="21" t="n">
-        <v>2500</v>
+        <v>18900</v>
       </c>
       <c r="AH26" s="21" t="n">
-        <v>2500</v>
+        <v>18900</v>
       </c>
       <c r="AI26" s="21" t="n">
-        <v>150</v>
+        <v>2000</v>
       </c>
       <c r="AJ26" s="21" t="n">
         <v/>
       </c>
       <c r="AK26" s="21" t="n">
-        <v>80.7415</v>
+        <v>576.725</v>
       </c>
       <c r="AL26" s="21" t="n">
         <v/>
@@ -21803,29 +21813,25 @@
         <v/>
       </c>
       <c r="AV26" s="21" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AW26" s="19" t="n">
-        <v/>
+        <v>18900</v>
+      </c>
+      <c r="AW26" s="36" t="n">
+        <v>46289</v>
       </c>
       <c r="AX26" s="19" t="n">
-        <v/>
+        <v>11500</v>
       </c>
       <c r="AY26" s="19" t="n">
-        <v>1610</v>
-      </c>
-      <c r="AZ26" s="19" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AZ26" s="36" t="n">
+        <v>46275</v>
       </c>
       <c r="BA26" s="19" t="n">
         <v/>
       </c>
-      <c r="BB26" s="19" t="inlineStr">
-        <is>
-          <t>UNCONFIRMED YET</t>
-        </is>
+      <c r="BB26" s="19" t="n">
+        <v/>
       </c>
       <c r="BC26" s="19" t="n">
         <v/>
@@ -21863,7 +21869,7 @@
     </row>
     <row r="27">
       <c r="A27" s="29" t="n">
-        <v>10092610465</v>
+        <v>11092612015</v>
       </c>
       <c r="B27" s="29" t="inlineStr">
         <is>
@@ -21887,8 +21893,8 @@
       </c>
       <c r="F27" s="29" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20486326</t>
+          <t>DAT MOW
+P20479926</t>
         </is>
       </c>
       <c r="G27" s="29" t="inlineStr">
@@ -21908,12 +21914,12 @@
       </c>
       <c r="J27" s="29" t="inlineStr">
         <is>
-          <t>ATR72</t>
+          <t>B737CL</t>
         </is>
       </c>
       <c r="K27" s="29" t="inlineStr">
         <is>
-          <t>301-2640</t>
+          <t>0851CM-2</t>
         </is>
       </c>
       <c r="L27" s="29" t="n">
@@ -21921,7 +21927,7 @@
       </c>
       <c r="M27" s="29" t="inlineStr">
         <is>
-          <t>ATTENDANT PANEL</t>
+          <t>ELEVATOR PITOT PROBE</t>
         </is>
       </c>
       <c r="N27" s="31" t="n">
@@ -21938,13 +21944,15 @@
         </is>
       </c>
       <c r="Q27" s="32" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="R27" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="S27" s="29" t="n">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="S27" s="29" t="inlineStr">
+        <is>
+          <t>7-12 дней</t>
+        </is>
       </c>
       <c r="T27" s="29" t="n">
         <v/>
@@ -21953,7 +21961,7 @@
         <v/>
       </c>
       <c r="V27" s="32" t="n">
-        <v>46305</v>
+        <v>46318</v>
       </c>
       <c r="W27" s="29" t="n">
         <v/>
@@ -21965,7 +21973,7 @@
       </c>
       <c r="Y27" s="29" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="Z27" s="29" t="inlineStr">
@@ -21975,12 +21983,12 @@
       </c>
       <c r="AA27" s="29" t="inlineStr">
         <is>
-          <t>ALOIA AEROSPACE</t>
+          <t>GENERAL AIRFRAME SUPPORT</t>
         </is>
       </c>
       <c r="AB27" s="29" t="inlineStr">
         <is>
-          <t>KTM1009261616</t>
+          <t>KTM1109261552</t>
         </is>
       </c>
       <c r="AC27" s="29" t="inlineStr">
@@ -21992,25 +22000,25 @@
         <v/>
       </c>
       <c r="AE27" s="33" t="n">
-        <v>11500</v>
+        <v>3895</v>
       </c>
       <c r="AF27" s="33" t="n">
-        <v>11500</v>
+        <v>3895</v>
       </c>
       <c r="AG27" s="33" t="n">
-        <v>18900</v>
+        <v>8500</v>
       </c>
       <c r="AH27" s="33" t="n">
-        <v>18900</v>
+        <v>8500</v>
       </c>
       <c r="AI27" s="33" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" s="33" t="n">
         <v/>
       </c>
       <c r="AK27" s="33" t="n">
-        <v>576.725</v>
+        <v>195.33425</v>
       </c>
       <c r="AL27" s="33" t="n">
         <v/>
@@ -22023,17 +22031,17 @@
       </c>
       <c r="AO27" s="29" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
+          <t>ЕСТЬ МПТ на Самолеты типа Boeing 737</t>
         </is>
       </c>
       <c r="AP27" s="29" t="inlineStr">
         <is>
-          <t>Получаем МПТ</t>
+          <t>Есть МПТ</t>
         </is>
       </c>
       <c r="AQ27" s="29" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
+          <t>Частичная предоплата</t>
         </is>
       </c>
       <c r="AR27" s="29" t="n">
@@ -22049,19 +22057,19 @@
         <v/>
       </c>
       <c r="AV27" s="33" t="n">
-        <v>18900</v>
-      </c>
-      <c r="AW27" s="34" t="n">
-        <v>46289</v>
+        <v>8500</v>
+      </c>
+      <c r="AW27" s="29" t="n">
+        <v/>
       </c>
       <c r="AX27" s="29" t="n">
-        <v>11500</v>
+        <v/>
       </c>
       <c r="AY27" s="29" t="n">
-        <v>0</v>
+        <v>3895</v>
       </c>
       <c r="AZ27" s="34" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="BA27" s="29" t="n">
         <v/>
@@ -22105,7 +22113,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>11092612015</v>
+        <v>11092613005</v>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
@@ -22122,15 +22130,15 @@
           <t>KDV-3</t>
         </is>
       </c>
-      <c r="E28" s="40" t="inlineStr">
-        <is>
-          <t>1 NOT PAID</t>
+      <c r="E28" s="39" t="inlineStr">
+        <is>
+          <t>2 PAID</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20479926</t>
+          <t>DDP MOW
+P20501426</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
@@ -22155,7 +22163,7 @@
       </c>
       <c r="K28" s="19" t="inlineStr">
         <is>
-          <t>0851CM-2</t>
+          <t>3604524-54</t>
         </is>
       </c>
       <c r="L28" s="19" t="n">
@@ -22163,11 +22171,12 @@
       </c>
       <c r="M28" s="19" t="inlineStr">
         <is>
-          <t>ELEVATOR PITOT PROBE</t>
+          <t>COMBUSTOR UNIT
+ASSY</t>
         </is>
       </c>
       <c r="N28" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O28" s="19" t="inlineStr">
         <is>
@@ -22183,11 +22192,11 @@
         <v>46276</v>
       </c>
       <c r="R28" s="19" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="S28" s="19" t="inlineStr">
         <is>
-          <t>7-12 дней</t>
+          <t>STK</t>
         </is>
       </c>
       <c r="T28" s="19" t="n">
@@ -22197,7 +22206,7 @@
         <v/>
       </c>
       <c r="V28" s="35" t="n">
-        <v>46318</v>
+        <v>46301</v>
       </c>
       <c r="W28" s="19" t="n">
         <v/>
@@ -22209,7 +22218,7 @@
       </c>
       <c r="Y28" s="19" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z28" s="19" t="inlineStr">
@@ -22219,12 +22228,12 @@
       </c>
       <c r="AA28" s="19" t="inlineStr">
         <is>
-          <t>GENERAL AIRFRAME SUPPORT</t>
+          <t>SETNA IO</t>
         </is>
       </c>
       <c r="AB28" s="19" t="inlineStr">
         <is>
-          <t>KTM1109261552</t>
+          <t>KTM1109261011</t>
         </is>
       </c>
       <c r="AC28" s="19" t="inlineStr">
@@ -22236,25 +22245,25 @@
         <v/>
       </c>
       <c r="AE28" s="21" t="n">
-        <v>3895</v>
+        <v>5000</v>
       </c>
       <c r="AF28" s="21" t="n">
-        <v>3895</v>
+        <v>15000</v>
       </c>
       <c r="AG28" s="21" t="n">
-        <v>8500</v>
+        <v>9100</v>
       </c>
       <c r="AH28" s="21" t="n">
-        <v>8500</v>
+        <v>27300</v>
       </c>
       <c r="AI28" s="21" t="n">
-        <v>1000</v>
+        <v>3900</v>
       </c>
       <c r="AJ28" s="21" t="n">
         <v/>
       </c>
       <c r="AK28" s="21" t="n">
-        <v>195.33425</v>
+        <v>752.25</v>
       </c>
       <c r="AL28" s="21" t="n">
         <v/>
@@ -22267,7 +22276,7 @@
       </c>
       <c r="AO28" s="19" t="inlineStr">
         <is>
-          <t>ЕСТЬ МПТ на Самолеты типа Boeing 737</t>
+          <t>НЕТ МПТ</t>
         </is>
       </c>
       <c r="AP28" s="19" t="inlineStr">
@@ -22293,16 +22302,16 @@
         <v/>
       </c>
       <c r="AV28" s="21" t="n">
-        <v>8500</v>
-      </c>
-      <c r="AW28" s="19" t="n">
-        <v/>
+        <v>27300</v>
+      </c>
+      <c r="AW28" s="36" t="n">
+        <v>46289</v>
       </c>
       <c r="AX28" s="19" t="n">
-        <v/>
+        <v>15000</v>
       </c>
       <c r="AY28" s="19" t="n">
-        <v>3895</v>
+        <v>0</v>
       </c>
       <c r="AZ28" s="36" t="n">
         <v>46276</v>
@@ -22349,7 +22358,7 @@
     </row>
     <row r="29">
       <c r="A29" s="29" t="n">
-        <v>11092613005</v>
+        <v>1109269415</v>
       </c>
       <c r="B29" s="29" t="inlineStr">
         <is>
@@ -22363,18 +22372,18 @@
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
-          <t>KDV-3</t>
-        </is>
-      </c>
-      <c r="E29" s="39" t="inlineStr">
-        <is>
-          <t>2 PAID</t>
+          <t>KDV-1</t>
+        </is>
+      </c>
+      <c r="E29" s="40" t="inlineStr">
+        <is>
+          <t>1 NOT PAID</t>
         </is>
       </c>
       <c r="F29" s="29" t="inlineStr">
         <is>
           <t>DDP MOW
-P20501426</t>
+P20497326</t>
         </is>
       </c>
       <c r="G29" s="29" t="inlineStr">
@@ -22389,17 +22398,17 @@
       </c>
       <c r="I29" s="29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J29" s="29" t="inlineStr">
         <is>
-          <t>B737CL</t>
+          <t>737CL</t>
         </is>
       </c>
       <c r="K29" s="29" t="inlineStr">
         <is>
-          <t>3604524-54</t>
+          <t>1002992-309</t>
         </is>
       </c>
       <c r="L29" s="29" t="n">
@@ -22407,12 +22416,11 @@
       </c>
       <c r="M29" s="29" t="inlineStr">
         <is>
-          <t>COMBUSTOR UNIT
-ASSY</t>
+          <t>PIVOT COVER</t>
         </is>
       </c>
       <c r="N29" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O29" s="29" t="inlineStr">
         <is>
@@ -22421,14 +22429,14 @@
       </c>
       <c r="P29" s="29" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q29" s="32" t="n">
         <v>46276</v>
       </c>
       <c r="R29" s="29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="S29" s="29" t="inlineStr">
         <is>
@@ -22438,11 +22446,13 @@
       <c r="T29" s="29" t="n">
         <v/>
       </c>
-      <c r="U29" s="29" t="n">
-        <v/>
+      <c r="U29" s="29" t="inlineStr">
+        <is>
+          <t>PRIORITY NET</t>
+        </is>
       </c>
       <c r="V29" s="32" t="n">
-        <v>46301</v>
+        <v>46306</v>
       </c>
       <c r="W29" s="29" t="n">
         <v/>
@@ -22454,52 +22464,50 @@
       </c>
       <c r="Y29" s="29" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z29" s="29" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>LUFTHANSA</t>
         </is>
       </c>
       <c r="AA29" s="29" t="inlineStr">
         <is>
-          <t>SETNA IO</t>
-        </is>
-      </c>
-      <c r="AB29" s="29" t="inlineStr">
-        <is>
-          <t>KTM1109261011</t>
-        </is>
+          <t>SATAIR</t>
+        </is>
+      </c>
+      <c r="AB29" s="29" t="n">
+        <v/>
       </c>
       <c r="AC29" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#6148</t>
         </is>
       </c>
       <c r="AD29" s="29" t="n">
         <v/>
       </c>
       <c r="AE29" s="33" t="n">
-        <v>5000</v>
+        <v>99</v>
       </c>
       <c r="AF29" s="33" t="n">
-        <v>15000</v>
+        <v>198</v>
       </c>
       <c r="AG29" s="33" t="n">
-        <v>9100</v>
+        <v>185</v>
       </c>
       <c r="AH29" s="33" t="n">
-        <v>27300</v>
+        <v>370</v>
       </c>
       <c r="AI29" s="33" t="n">
-        <v>3900</v>
+        <v>50</v>
       </c>
       <c r="AJ29" s="33" t="n">
         <v/>
       </c>
       <c r="AK29" s="33" t="n">
-        <v>752.25</v>
+        <v>9.9297</v>
       </c>
       <c r="AL29" s="33" t="n">
         <v/>
@@ -22508,21 +22516,19 @@
         <v/>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO29" s="29" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP29" s="29" t="inlineStr">
-        <is>
-          <t>Есть МПТ</t>
-        </is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP29" s="29" t="n">
+        <v/>
       </c>
       <c r="AQ29" s="29" t="inlineStr">
         <is>
-          <t>Частичная предоплата</t>
+          <t>Постоплата 100%</t>
         </is>
       </c>
       <c r="AR29" s="29" t="n">
@@ -22538,16 +22544,16 @@
         <v/>
       </c>
       <c r="AV29" s="33" t="n">
-        <v>27300</v>
-      </c>
-      <c r="AW29" s="34" t="n">
-        <v>46289</v>
+        <v>370</v>
+      </c>
+      <c r="AW29" s="29" t="n">
+        <v/>
       </c>
       <c r="AX29" s="29" t="n">
-        <v>15000</v>
+        <v/>
       </c>
       <c r="AY29" s="29" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="AZ29" s="34" t="n">
         <v>46276</v>
@@ -22555,8 +22561,10 @@
       <c r="BA29" s="29" t="n">
         <v/>
       </c>
-      <c r="BB29" s="29" t="n">
-        <v/>
+      <c r="BB29" s="29" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
       </c>
       <c r="BC29" s="29" t="n">
         <v/>
@@ -22594,7 +22602,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>1109269415</v>
+        <v>1109269585</v>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
@@ -22619,7 +22627,7 @@
       <c r="F30" s="19" t="inlineStr">
         <is>
           <t>DDP MOW
-P20497326</t>
+P20498826</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
@@ -22639,12 +22647,12 @@
       </c>
       <c r="J30" s="19" t="inlineStr">
         <is>
-          <t>737CL</t>
+          <t>B738</t>
         </is>
       </c>
       <c r="K30" s="19" t="inlineStr">
         <is>
-          <t>1002992-309</t>
+          <t>BACR15BA2AD5C</t>
         </is>
       </c>
       <c r="L30" s="19" t="n">
@@ -22652,11 +22660,11 @@
       </c>
       <c r="M30" s="19" t="inlineStr">
         <is>
-          <t>PIVOT COVER</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="N30" s="20" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="O30" s="19" t="inlineStr">
         <is>
@@ -22672,7 +22680,7 @@
         <v>46276</v>
       </c>
       <c r="R30" s="19" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S30" s="19" t="inlineStr">
         <is>
@@ -22682,13 +22690,11 @@
       <c r="T30" s="19" t="n">
         <v/>
       </c>
-      <c r="U30" s="19" t="inlineStr">
-        <is>
-          <t>PRIORITY NET</t>
-        </is>
+      <c r="U30" s="19" t="n">
+        <v/>
       </c>
       <c r="V30" s="35" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="W30" s="19" t="n">
         <v/>
@@ -22705,45 +22711,43 @@
       </c>
       <c r="Z30" s="19" t="inlineStr">
         <is>
-          <t>LUFTHANSA</t>
-        </is>
-      </c>
-      <c r="AA30" s="19" t="inlineStr">
-        <is>
-          <t>SATAIR</t>
-        </is>
+          <t>BLUE OCEAN SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="AA30" s="19" t="n">
+        <v/>
       </c>
       <c r="AB30" s="19" t="n">
         <v/>
       </c>
       <c r="AC30" s="19" t="inlineStr">
         <is>
-          <t>#6148</t>
+          <t>№2373</t>
         </is>
       </c>
       <c r="AD30" s="19" t="n">
         <v/>
       </c>
       <c r="AE30" s="21" t="n">
-        <v>99</v>
+        <v>1.6</v>
       </c>
       <c r="AF30" s="21" t="n">
-        <v>198</v>
+        <v>102.4</v>
       </c>
       <c r="AG30" s="21" t="n">
-        <v>185</v>
+        <v>5</v>
       </c>
       <c r="AH30" s="21" t="n">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="AI30" s="21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AJ30" s="21" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK30" s="21" t="n">
-        <v>9.9297</v>
+        <v>5.2736</v>
       </c>
       <c r="AL30" s="21" t="n">
         <v/>
@@ -22780,7 +22784,7 @@
         <v/>
       </c>
       <c r="AV30" s="21" t="n">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="AW30" s="19" t="n">
         <v/>
@@ -22789,7 +22793,7 @@
         <v/>
       </c>
       <c r="AY30" s="19" t="n">
-        <v>198</v>
+        <v>102.4</v>
       </c>
       <c r="AZ30" s="36" t="n">
         <v>46276</v>
@@ -22799,20 +22803,24 @@
       </c>
       <c r="BB30" s="19" t="inlineStr">
         <is>
-          <t>PAID</t>
-        </is>
-      </c>
-      <c r="BC30" s="19" t="n">
-        <v/>
+          <t>BOS WHS</t>
+        </is>
+      </c>
+      <c r="BC30" s="19" t="inlineStr">
+        <is>
+          <t>до 21.10</t>
+        </is>
       </c>
       <c r="BD30" s="19" t="n">
         <v/>
       </c>
       <c r="BE30" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BF30" s="19" t="n">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="BF30" s="19" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
       </c>
       <c r="BG30" s="19" t="n">
         <v/>
@@ -22824,13 +22832,13 @@
         <v/>
       </c>
       <c r="BJ30" s="19" t="n">
-        <v/>
+        <v>30092026</v>
       </c>
       <c r="BK30" s="19" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL30" s="19" t="n">
-        <v/>
+        <v>102.4</v>
       </c>
       <c r="BM30" s="19" t="n">
         <v/>
@@ -22838,7 +22846,7 @@
     </row>
     <row r="31">
       <c r="A31" s="29" t="n">
-        <v>1109269585</v>
+        <v>16092610575</v>
       </c>
       <c r="B31" s="29" t="inlineStr">
         <is>
@@ -22852,7 +22860,7 @@
       </c>
       <c r="D31" s="29" t="inlineStr">
         <is>
-          <t>KDV-1</t>
+          <t>KDV-3</t>
         </is>
       </c>
       <c r="E31" s="40" t="inlineStr">
@@ -22862,8 +22870,8 @@
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20498826</t>
+          <t>DAT MOW
+P20515326</t>
         </is>
       </c>
       <c r="G31" s="29" t="inlineStr">
@@ -22878,17 +22886,17 @@
       </c>
       <c r="I31" s="29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J31" s="29" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>737CL</t>
         </is>
       </c>
       <c r="K31" s="29" t="inlineStr">
         <is>
-          <t>BACR15BA2AD5C</t>
+          <t>65C27506-3</t>
         </is>
       </c>
       <c r="L31" s="29" t="n">
@@ -22896,11 +22904,11 @@
       </c>
       <c r="M31" s="29" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>TRANSMISSION ASSY, RH, #6</t>
         </is>
       </c>
       <c r="N31" s="31" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="O31" s="29" t="inlineStr">
         <is>
@@ -22909,14 +22917,14 @@
       </c>
       <c r="P31" s="29" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q31" s="32" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="R31" s="29" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S31" s="29" t="inlineStr">
         <is>
@@ -22942,12 +22950,12 @@
       </c>
       <c r="Y31" s="29" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z31" s="29" t="inlineStr">
         <is>
-          <t>BLUE OCEAN SOLUTIONS</t>
+          <t>LUFTHANSA</t>
         </is>
       </c>
       <c r="AA31" s="29" t="n">
@@ -22958,45 +22966,45 @@
       </c>
       <c r="AC31" s="29" t="inlineStr">
         <is>
-          <t>№2373</t>
+          <t>#6187</t>
         </is>
       </c>
       <c r="AD31" s="29" t="n">
         <v/>
       </c>
       <c r="AE31" s="33" t="n">
-        <v>1.6</v>
+        <v>4030</v>
       </c>
       <c r="AF31" s="33" t="n">
-        <v>102.4</v>
+        <v>4030</v>
       </c>
       <c r="AG31" s="33" t="n">
-        <v>5</v>
+        <v>5700</v>
       </c>
       <c r="AH31" s="33" t="n">
-        <v>320</v>
+        <v>5700</v>
       </c>
       <c r="AI31" s="33" t="n">
+        <v>400</v>
+      </c>
+      <c r="AJ31" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AK31" s="33" t="n">
+        <v>202.1045</v>
+      </c>
+      <c r="AL31" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AM31" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AN31" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AJ31" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" s="33" t="n">
-        <v>5.2736</v>
-      </c>
-      <c r="AL31" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AM31" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AN31" s="29" t="n">
-        <v>0.22</v>
-      </c>
       <c r="AO31" s="29" t="inlineStr">
         <is>
-          <t>Не применимо</t>
+          <t>НЕТ МПТ</t>
         </is>
       </c>
       <c r="AP31" s="29" t="n">
@@ -23020,7 +23028,7 @@
         <v/>
       </c>
       <c r="AV31" s="33" t="n">
-        <v>320</v>
+        <v>5700</v>
       </c>
       <c r="AW31" s="29" t="n">
         <v/>
@@ -23029,34 +23037,32 @@
         <v/>
       </c>
       <c r="AY31" s="29" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="AZ31" s="34" t="n">
-        <v>46276</v>
+        <v>4030</v>
+      </c>
+      <c r="AZ31" s="29" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
       </c>
       <c r="BA31" s="29" t="n">
         <v/>
       </c>
       <c r="BB31" s="29" t="inlineStr">
         <is>
-          <t>BOS WHS</t>
-        </is>
-      </c>
-      <c r="BC31" s="29" t="inlineStr">
-        <is>
-          <t>до 21.10</t>
-        </is>
+          <t>UNCONFIRMED YET</t>
+        </is>
+      </c>
+      <c r="BC31" s="29" t="n">
+        <v/>
       </c>
       <c r="BD31" s="29" t="n">
         <v/>
       </c>
       <c r="BE31" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF31" s="29" t="inlineStr">
-        <is>
-          <t>Ф</t>
-        </is>
+        <v/>
+      </c>
+      <c r="BF31" s="29" t="n">
+        <v/>
       </c>
       <c r="BG31" s="29" t="n">
         <v/>
@@ -23068,13 +23074,13 @@
         <v/>
       </c>
       <c r="BJ31" s="29" t="n">
-        <v>30092026</v>
+        <v/>
       </c>
       <c r="BK31" s="29" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="BL31" s="29" t="n">
-        <v>102.4</v>
+        <v/>
       </c>
       <c r="BM31" s="29" t="n">
         <v/>
@@ -23082,7 +23088,7 @@
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
-        <v>16092610575</v>
+        <v>16092612555</v>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
@@ -23106,8 +23112,8 @@
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20515326</t>
+          <t>DDP MOW
+P20518126</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
@@ -23127,12 +23133,12 @@
       </c>
       <c r="J32" s="19" t="inlineStr">
         <is>
-          <t>737CL</t>
+          <t>B738</t>
         </is>
       </c>
       <c r="K32" s="19" t="inlineStr">
         <is>
-          <t>65C27506-3</t>
+          <t>901950-02</t>
         </is>
       </c>
       <c r="L32" s="19" t="n">
@@ -23140,7 +23146,9 @@
       </c>
       <c r="M32" s="19" t="inlineStr">
         <is>
-          <t>TRANSMISSION ASSY, RH, #6</t>
+          <t>FIRE &amp; OVERHEAT
+DETECTION CTR
+UNIT</t>
         </is>
       </c>
       <c r="N32" s="20" t="n">
@@ -23186,7 +23194,7 @@
       </c>
       <c r="Y32" s="19" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="Z32" s="19" t="inlineStr">
@@ -23197,37 +23205,41 @@
       <c r="AA32" s="19" t="n">
         <v/>
       </c>
-      <c r="AB32" s="19" t="n">
-        <v/>
+      <c r="AB32" s="19" t="inlineStr">
+        <is>
+          <t>JP230926-1</t>
+        </is>
       </c>
       <c r="AC32" s="19" t="inlineStr">
         <is>
-          <t>#6187</t>
-        </is>
-      </c>
-      <c r="AD32" s="19" t="n">
-        <v/>
+          <t>#6188</t>
+        </is>
+      </c>
+      <c r="AD32" s="19" t="inlineStr">
+        <is>
+          <t>2859</t>
+        </is>
       </c>
       <c r="AE32" s="21" t="n">
-        <v>4030</v>
+        <v>2710</v>
       </c>
       <c r="AF32" s="21" t="n">
-        <v>4030</v>
+        <v>2710</v>
       </c>
       <c r="AG32" s="21" t="n">
-        <v>5700</v>
+        <v>4000</v>
       </c>
       <c r="AH32" s="21" t="n">
-        <v>5700</v>
+        <v>4000</v>
       </c>
       <c r="AI32" s="21" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="AJ32" s="21" t="n">
         <v/>
       </c>
       <c r="AK32" s="21" t="n">
-        <v>202.1045</v>
+        <v>135.9065</v>
       </c>
       <c r="AL32" s="21" t="n">
         <v/>
@@ -23243,8 +23255,10 @@
           <t>НЕТ МПТ</t>
         </is>
       </c>
-      <c r="AP32" s="19" t="n">
-        <v/>
+      <c r="AP32" s="19" t="inlineStr">
+        <is>
+          <t>Есть МПТ</t>
+        </is>
       </c>
       <c r="AQ32" s="19" t="inlineStr">
         <is>
@@ -23264,7 +23278,7 @@
         <v/>
       </c>
       <c r="AV32" s="21" t="n">
-        <v>5700</v>
+        <v>4000</v>
       </c>
       <c r="AW32" s="19" t="n">
         <v/>
@@ -23273,7 +23287,7 @@
         <v/>
       </c>
       <c r="AY32" s="19" t="n">
-        <v>4030</v>
+        <v>2710</v>
       </c>
       <c r="AZ32" s="19" t="inlineStr">
         <is>
@@ -23283,25 +23297,29 @@
       <c r="BA32" s="19" t="n">
         <v/>
       </c>
-      <c r="BB32" s="19" t="inlineStr">
-        <is>
-          <t>UNCONFIRMED YET</t>
-        </is>
-      </c>
-      <c r="BC32" s="19" t="n">
-        <v/>
+      <c r="BB32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BC32" s="19" t="inlineStr">
+        <is>
+          <t>до 11.10</t>
+        </is>
       </c>
       <c r="BD32" s="19" t="n">
         <v/>
       </c>
       <c r="BE32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BF32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BG32" s="19" t="n">
-        <v/>
+        <v>3200</v>
+      </c>
+      <c r="BF32" s="19" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
+      <c r="BG32" s="19" t="inlineStr">
+        <is>
+          <t>230926-1 /// AXIS</t>
+        </is>
       </c>
       <c r="BH32" s="19" t="n">
         <v/>
@@ -23309,8 +23327,10 @@
       <c r="BI32" s="19" t="n">
         <v/>
       </c>
-      <c r="BJ32" s="19" t="n">
-        <v/>
+      <c r="BJ32" s="19" t="inlineStr">
+        <is>
+          <t>230926-1</t>
+        </is>
       </c>
       <c r="BK32" s="19" t="n">
         <v/>
@@ -23324,7 +23344,7 @@
     </row>
     <row r="33">
       <c r="A33" s="29" t="n">
-        <v>16092612555</v>
+        <v>16092613402</v>
       </c>
       <c r="B33" s="29" t="inlineStr">
         <is>
@@ -23338,18 +23358,18 @@
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
-          <t>KDV-3</t>
-        </is>
-      </c>
-      <c r="E33" s="40" t="inlineStr">
-        <is>
-          <t>1 NOT PAID</t>
+          <t>KDV-1</t>
+        </is>
+      </c>
+      <c r="E33" s="41" t="inlineStr">
+        <is>
+          <t>6 TROUBLE</t>
         </is>
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20518126</t>
+          <t>DAT MOW
+P20518726</t>
         </is>
       </c>
       <c r="G33" s="29" t="inlineStr">
@@ -23364,17 +23384,15 @@
       </c>
       <c r="I33" s="29" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J33" s="29" t="inlineStr">
-        <is>
-          <t>B738</t>
-        </is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J33" s="29" t="n">
+        <v/>
       </c>
       <c r="K33" s="29" t="inlineStr">
         <is>
-          <t>901950-02</t>
+          <t>BACR13CF2AB</t>
         </is>
       </c>
       <c r="L33" s="29" t="n">
@@ -23382,13 +23400,11 @@
       </c>
       <c r="M33" s="29" t="inlineStr">
         <is>
-          <t>FIRE &amp; OVERHEAT
-DETECTION CTR
-UNIT</t>
+          <t>RELAY</t>
         </is>
       </c>
       <c r="N33" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" s="29" t="inlineStr">
         <is>
@@ -23397,7 +23413,7 @@
       </c>
       <c r="P33" s="29" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q33" s="32" t="n">
@@ -23430,52 +23446,48 @@
       </c>
       <c r="Y33" s="29" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z33" s="29" t="inlineStr">
         <is>
-          <t>LUFTHANSA</t>
+          <t>BLUE OCEAN SOLUTIONS</t>
         </is>
       </c>
       <c r="AA33" s="29" t="n">
         <v/>
       </c>
-      <c r="AB33" s="29" t="inlineStr">
-        <is>
-          <t>JP230926-1</t>
-        </is>
+      <c r="AB33" s="29" t="n">
+        <v/>
       </c>
       <c r="AC33" s="29" t="inlineStr">
         <is>
-          <t>#6188</t>
-        </is>
-      </c>
-      <c r="AD33" s="29" t="inlineStr">
-        <is>
-          <t>2859</t>
-        </is>
+          <t>№2389</t>
+        </is>
+      </c>
+      <c r="AD33" s="29" t="n">
+        <v/>
       </c>
       <c r="AE33" s="33" t="n">
-        <v>2710</v>
+        <v>133</v>
       </c>
       <c r="AF33" s="33" t="n">
-        <v>2710</v>
+        <v>266</v>
       </c>
       <c r="AG33" s="33" t="n">
-        <v>4000</v>
+        <v>220</v>
       </c>
       <c r="AH33" s="33" t="n">
-        <v>4000</v>
+        <v>440</v>
       </c>
       <c r="AI33" s="33" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="AJ33" s="33" t="n">
         <v/>
       </c>
       <c r="AK33" s="33" t="n">
-        <v>135.9065</v>
+        <v>13.3399</v>
       </c>
       <c r="AL33" s="33" t="n">
         <v/>
@@ -23484,17 +23496,15 @@
         <v/>
       </c>
       <c r="AN33" s="29" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO33" s="29" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP33" s="29" t="inlineStr">
-        <is>
-          <t>Есть МПТ</t>
-        </is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP33" s="29" t="n">
+        <v/>
       </c>
       <c r="AQ33" s="29" t="inlineStr">
         <is>
@@ -23514,7 +23524,7 @@
         <v/>
       </c>
       <c r="AV33" s="33" t="n">
-        <v>4000</v>
+        <v>440</v>
       </c>
       <c r="AW33" s="29" t="n">
         <v/>
@@ -23523,39 +23533,35 @@
         <v/>
       </c>
       <c r="AY33" s="29" t="n">
-        <v>2710</v>
-      </c>
-      <c r="AZ33" s="29" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
+        <v>266</v>
+      </c>
+      <c r="AZ33" s="34" t="n">
+        <v>46281</v>
       </c>
       <c r="BA33" s="29" t="n">
         <v/>
       </c>
-      <c r="BB33" s="29" t="n">
-        <v/>
+      <c r="BB33" s="29" t="inlineStr">
+        <is>
+          <t>UNSOLVED</t>
+        </is>
       </c>
       <c r="BC33" s="29" t="inlineStr">
         <is>
-          <t>до 11.10</t>
+          <t>Stock out</t>
         </is>
       </c>
       <c r="BD33" s="29" t="n">
         <v/>
       </c>
       <c r="BE33" s="29" t="n">
-        <v>3200</v>
-      </c>
-      <c r="BF33" s="29" t="inlineStr">
-        <is>
-          <t>Ф</t>
-        </is>
-      </c>
-      <c r="BG33" s="29" t="inlineStr">
-        <is>
-          <t>230926-1 /// AXIS</t>
-        </is>
+        <v/>
+      </c>
+      <c r="BF33" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BG33" s="29" t="n">
+        <v/>
       </c>
       <c r="BH33" s="29" t="n">
         <v/>
@@ -23563,10 +23569,8 @@
       <c r="BI33" s="29" t="n">
         <v/>
       </c>
-      <c r="BJ33" s="29" t="inlineStr">
-        <is>
-          <t>230926-1</t>
-        </is>
+      <c r="BJ33" s="29" t="n">
+        <v/>
       </c>
       <c r="BK33" s="29" t="n">
         <v/>
@@ -23597,9 +23601,9 @@
           <t>KDV-1</t>
         </is>
       </c>
-      <c r="E34" s="41" t="inlineStr">
-        <is>
-          <t>6 TROUBLE</t>
+      <c r="E34" s="40" t="inlineStr">
+        <is>
+          <t>1 NOT PAID</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -23628,7 +23632,7 @@
       </c>
       <c r="K34" s="19" t="inlineStr">
         <is>
-          <t>BACR13CF2AB</t>
+          <t>BACR15FT6AD12C</t>
         </is>
       </c>
       <c r="L34" s="19" t="n">
@@ -23636,11 +23640,11 @@
       </c>
       <c r="M34" s="19" t="inlineStr">
         <is>
-          <t>RELAY</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="N34" s="20" t="n">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="O34" s="19" t="inlineStr">
         <is>
@@ -23698,32 +23702,32 @@
       </c>
       <c r="AC34" s="19" t="inlineStr">
         <is>
-          <t>№2389</t>
+          <t>№2387</t>
         </is>
       </c>
       <c r="AD34" s="19" t="n">
         <v/>
       </c>
       <c r="AE34" s="21" t="n">
-        <v>133</v>
+        <v>0.4</v>
       </c>
       <c r="AF34" s="21" t="n">
-        <v>266</v>
+        <v>100</v>
       </c>
       <c r="AG34" s="21" t="n">
-        <v>220</v>
+        <v>1.1</v>
       </c>
       <c r="AH34" s="21" t="n">
-        <v>440</v>
+        <v>275</v>
       </c>
       <c r="AI34" s="21" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" s="21" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK34" s="21" t="n">
-        <v>13.3399</v>
+        <v>5.015</v>
       </c>
       <c r="AL34" s="21" t="n">
         <v/>
@@ -23760,7 +23764,7 @@
         <v/>
       </c>
       <c r="AV34" s="21" t="n">
-        <v>440</v>
+        <v>275</v>
       </c>
       <c r="AW34" s="19" t="n">
         <v/>
@@ -23769,7 +23773,7 @@
         <v/>
       </c>
       <c r="AY34" s="19" t="n">
-        <v>266</v>
+        <v>100</v>
       </c>
       <c r="AZ34" s="36" t="n">
         <v>46281</v>
@@ -23779,13 +23783,11 @@
       </c>
       <c r="BB34" s="19" t="inlineStr">
         <is>
-          <t>UNSOLVED</t>
-        </is>
-      </c>
-      <c r="BC34" s="19" t="inlineStr">
-        <is>
-          <t>Stock out</t>
-        </is>
+          <t>BOS WHS</t>
+        </is>
+      </c>
+      <c r="BC34" s="19" t="n">
+        <v/>
       </c>
       <c r="BD34" s="19" t="n">
         <v/>
@@ -23793,8 +23795,10 @@
       <c r="BE34" s="19" t="n">
         <v/>
       </c>
-      <c r="BF34" s="19" t="n">
-        <v/>
+      <c r="BF34" s="19" t="inlineStr">
+        <is>
+          <t>Др</t>
+        </is>
       </c>
       <c r="BG34" s="19" t="n">
         <v/>
@@ -23809,10 +23813,10 @@
         <v/>
       </c>
       <c r="BK34" s="19" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL34" s="19" t="n">
-        <v/>
+        <v>100</v>
       </c>
       <c r="BM34" s="19" t="n">
         <v/>
@@ -23868,7 +23872,7 @@
       </c>
       <c r="K35" s="29" t="inlineStr">
         <is>
-          <t>BACR15FT6AD12C</t>
+          <t>BACS12HN3-5</t>
         </is>
       </c>
       <c r="L35" s="29" t="n">
@@ -23876,11 +23880,11 @@
       </c>
       <c r="M35" s="29" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>SCREW</t>
         </is>
       </c>
       <c r="N35" s="31" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="O35" s="29" t="inlineStr">
         <is>
@@ -23938,23 +23942,23 @@
       </c>
       <c r="AC35" s="29" t="inlineStr">
         <is>
-          <t>№2387</t>
+          <t>№2388</t>
         </is>
       </c>
       <c r="AD35" s="29" t="n">
         <v/>
       </c>
       <c r="AE35" s="33" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="AF35" s="33" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="AG35" s="33" t="n">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="AH35" s="33" t="n">
-        <v>275</v>
+        <v>350</v>
       </c>
       <c r="AI35" s="33" t="n">
         <v>0</v>
@@ -23963,7 +23967,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="33" t="n">
-        <v>5.015</v>
+        <v>6.77025</v>
       </c>
       <c r="AL35" s="33" t="n">
         <v/>
@@ -24000,7 +24004,7 @@
         <v/>
       </c>
       <c r="AV35" s="33" t="n">
-        <v>275</v>
+        <v>350</v>
       </c>
       <c r="AW35" s="29" t="n">
         <v/>
@@ -24009,7 +24013,7 @@
         <v/>
       </c>
       <c r="AY35" s="29" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="AZ35" s="34" t="n">
         <v>46281</v>
@@ -24052,7 +24056,7 @@
         <v>0</v>
       </c>
       <c r="BL35" s="29" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="BM35" s="29" t="n">
         <v/>
@@ -24060,7 +24064,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>16092613402</v>
+        <v>17092612085</v>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
@@ -24085,7 +24089,7 @@
       <c r="F36" s="19" t="inlineStr">
         <is>
           <t>DAT MOW
-P20518726</t>
+P20526726</t>
         </is>
       </c>
       <c r="G36" s="19" t="inlineStr">
@@ -24103,12 +24107,14 @@
           <t>E</t>
         </is>
       </c>
-      <c r="J36" s="19" t="n">
-        <v/>
+      <c r="J36" s="19" t="inlineStr">
+        <is>
+          <t>ATR72</t>
+        </is>
       </c>
       <c r="K36" s="19" t="inlineStr">
         <is>
-          <t>BACS12HN3-5</t>
+          <t>ST3086-013WE</t>
         </is>
       </c>
       <c r="L36" s="19" t="n">
@@ -24116,11 +24122,11 @@
       </c>
       <c r="M36" s="19" t="inlineStr">
         <is>
-          <t>SCREW</t>
+          <t>PACKING</t>
         </is>
       </c>
       <c r="N36" s="20" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="O36" s="19" t="inlineStr">
         <is>
@@ -24133,7 +24139,7 @@
         </is>
       </c>
       <c r="Q36" s="35" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="R36" s="19" t="n">
         <v>30</v>
@@ -24146,11 +24152,13 @@
       <c r="T36" s="19" t="n">
         <v/>
       </c>
-      <c r="U36" s="19" t="n">
-        <v/>
+      <c r="U36" s="19" t="inlineStr">
+        <is>
+          <t>PRIORITY NET</t>
+        </is>
       </c>
       <c r="V36" s="35" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="W36" s="19" t="n">
         <v/>
@@ -24167,43 +24175,45 @@
       </c>
       <c r="Z36" s="19" t="inlineStr">
         <is>
-          <t>BLUE OCEAN SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="AA36" s="19" t="n">
-        <v/>
+          <t>LUFTHANSA</t>
+        </is>
+      </c>
+      <c r="AA36" s="19" t="inlineStr">
+        <is>
+          <t>WENCOR</t>
+        </is>
       </c>
       <c r="AB36" s="19" t="n">
         <v/>
       </c>
       <c r="AC36" s="19" t="inlineStr">
         <is>
-          <t>№2388</t>
+          <t>#6203</t>
         </is>
       </c>
       <c r="AD36" s="19" t="n">
         <v/>
       </c>
       <c r="AE36" s="21" t="n">
-        <v>2.7</v>
+        <v>200</v>
       </c>
       <c r="AF36" s="21" t="n">
-        <v>135</v>
+        <v>6000</v>
       </c>
       <c r="AG36" s="21" t="n">
-        <v>7</v>
+        <v>310</v>
       </c>
       <c r="AH36" s="21" t="n">
-        <v>350</v>
+        <v>9300</v>
       </c>
       <c r="AI36" s="21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ36" s="21" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AK36" s="21" t="n">
-        <v>6.77025</v>
+        <v>300.9</v>
       </c>
       <c r="AL36" s="21" t="n">
         <v/>
@@ -24224,7 +24234,7 @@
       </c>
       <c r="AQ36" s="19" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
+          <t>Частичная предоплата</t>
         </is>
       </c>
       <c r="AR36" s="19" t="n">
@@ -24240,7 +24250,7 @@
         <v/>
       </c>
       <c r="AV36" s="21" t="n">
-        <v>350</v>
+        <v>9300</v>
       </c>
       <c r="AW36" s="19" t="n">
         <v/>
@@ -24249,17 +24259,17 @@
         <v/>
       </c>
       <c r="AY36" s="19" t="n">
-        <v>135</v>
+        <v>6000</v>
       </c>
       <c r="AZ36" s="36" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="BA36" s="19" t="n">
         <v/>
       </c>
       <c r="BB36" s="19" t="inlineStr">
         <is>
-          <t>BOS WHS</t>
+          <t>HA WHS</t>
         </is>
       </c>
       <c r="BC36" s="19" t="n">
@@ -24289,10 +24299,10 @@
         <v/>
       </c>
       <c r="BK36" s="19" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="BL36" s="19" t="n">
-        <v>135</v>
+        <v/>
       </c>
       <c r="BM36" s="19" t="n">
         <v/>
@@ -24300,7 +24310,7 @@
     </row>
     <row r="37">
       <c r="A37" s="29" t="n">
-        <v>17092612085</v>
+        <v>17092615215</v>
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
@@ -24314,7 +24324,7 @@
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>KDV-1</t>
+          <t>KDV-3</t>
         </is>
       </c>
       <c r="E37" s="40" t="inlineStr">
@@ -24324,8 +24334,8 @@
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20526726</t>
+          <t>DDP MOW
+P20530826</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
@@ -24340,17 +24350,17 @@
       </c>
       <c r="I37" s="29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J37" s="29" t="inlineStr">
         <is>
-          <t>ATR72</t>
+          <t>737ALL</t>
         </is>
       </c>
       <c r="K37" s="29" t="inlineStr">
         <is>
-          <t>ST3086-013WE</t>
+          <t>1150002-1</t>
         </is>
       </c>
       <c r="L37" s="29" t="n">
@@ -24358,11 +24368,11 @@
       </c>
       <c r="M37" s="29" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>SENSOR</t>
         </is>
       </c>
       <c r="N37" s="31" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O37" s="29" t="inlineStr">
         <is>
@@ -24371,7 +24381,7 @@
       </c>
       <c r="P37" s="29" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q37" s="32" t="n">
@@ -24388,10 +24398,8 @@
       <c r="T37" s="29" t="n">
         <v/>
       </c>
-      <c r="U37" s="29" t="inlineStr">
-        <is>
-          <t>PRIORITY NET</t>
-        </is>
+      <c r="U37" s="29" t="n">
+        <v/>
       </c>
       <c r="V37" s="32" t="n">
         <v>46312</v>
@@ -24406,7 +24414,7 @@
       </c>
       <c r="Y37" s="29" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>TEST</t>
         </is>
       </c>
       <c r="Z37" s="29" t="inlineStr">
@@ -24414,42 +24422,44 @@
           <t>LUFTHANSA</t>
         </is>
       </c>
-      <c r="AA37" s="29" t="inlineStr">
-        <is>
-          <t>WENCOR</t>
-        </is>
-      </c>
-      <c r="AB37" s="29" t="n">
-        <v/>
+      <c r="AA37" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AB37" s="29" t="inlineStr">
+        <is>
+          <t>JP280926-3</t>
+        </is>
       </c>
       <c r="AC37" s="29" t="inlineStr">
         <is>
-          <t>#6203</t>
-        </is>
-      </c>
-      <c r="AD37" s="29" t="n">
-        <v/>
+          <t>#6204</t>
+        </is>
+      </c>
+      <c r="AD37" s="29" t="inlineStr">
+        <is>
+          <t>012C-3004</t>
+        </is>
       </c>
       <c r="AE37" s="33" t="n">
+        <v>2300</v>
+      </c>
+      <c r="AF37" s="33" t="n">
+        <v>2300</v>
+      </c>
+      <c r="AG37" s="33" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AH37" s="33" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AI37" s="33" t="n">
         <v>200</v>
       </c>
-      <c r="AF37" s="33" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AG37" s="33" t="n">
-        <v>310</v>
-      </c>
-      <c r="AH37" s="33" t="n">
-        <v>9300</v>
-      </c>
-      <c r="AI37" s="33" t="n">
-        <v>100</v>
-      </c>
       <c r="AJ37" s="33" t="n">
         <v/>
       </c>
       <c r="AK37" s="33" t="n">
-        <v>300.9</v>
+        <v>115.345</v>
       </c>
       <c r="AL37" s="33" t="n">
         <v/>
@@ -24458,19 +24468,21 @@
         <v/>
       </c>
       <c r="AN37" s="29" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AO37" s="29" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP37" s="29" t="n">
-        <v/>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP37" s="29" t="inlineStr">
+        <is>
+          <t>Получаем МПТ</t>
+        </is>
       </c>
       <c r="AQ37" s="29" t="inlineStr">
         <is>
-          <t>Частичная предоплата</t>
+          <t>Постоплата 100%</t>
         </is>
       </c>
       <c r="AR37" s="29" t="n">
@@ -24486,7 +24498,7 @@
         <v/>
       </c>
       <c r="AV37" s="33" t="n">
-        <v>9300</v>
+        <v>3600</v>
       </c>
       <c r="AW37" s="29" t="n">
         <v/>
@@ -24495,31 +24507,35 @@
         <v/>
       </c>
       <c r="AY37" s="29" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AZ37" s="34" t="n">
-        <v>46282</v>
+        <v>2300</v>
+      </c>
+      <c r="AZ37" s="29" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
       </c>
       <c r="BA37" s="29" t="n">
         <v/>
       </c>
       <c r="BB37" s="29" t="inlineStr">
         <is>
-          <t>HA WHS</t>
-        </is>
-      </c>
-      <c r="BC37" s="29" t="n">
-        <v/>
+          <t>pick up 02/10</t>
+        </is>
+      </c>
+      <c r="BC37" s="29" t="inlineStr">
+        <is>
+          <t>до 10.10</t>
+        </is>
       </c>
       <c r="BD37" s="29" t="n">
         <v/>
       </c>
       <c r="BE37" s="29" t="n">
-        <v/>
+        <v>2880</v>
       </c>
       <c r="BF37" s="29" t="inlineStr">
         <is>
-          <t>Др</t>
+          <t>Ф</t>
         </is>
       </c>
       <c r="BG37" s="29" t="n">
@@ -24531,8 +24547,10 @@
       <c r="BI37" s="29" t="n">
         <v/>
       </c>
-      <c r="BJ37" s="29" t="n">
-        <v/>
+      <c r="BJ37" s="29" t="inlineStr">
+        <is>
+          <t>280926-3</t>
+        </is>
       </c>
       <c r="BK37" s="29" t="n">
         <v/>
@@ -24546,7 +24564,7 @@
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>17092615215</v>
+        <v>21092614525</v>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
@@ -24571,7 +24589,7 @@
       <c r="F38" s="19" t="inlineStr">
         <is>
           <t>DDP MOW
-P20530826</t>
+P20536126</t>
         </is>
       </c>
       <c r="G38" s="19" t="inlineStr">
@@ -24621,7 +24639,7 @@
         </is>
       </c>
       <c r="Q38" s="35" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="R38" s="19" t="n">
         <v>30</v>
@@ -24638,7 +24656,7 @@
         <v/>
       </c>
       <c r="V38" s="35" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="W38" s="19" t="n">
         <v/>
@@ -24650,7 +24668,7 @@
       </c>
       <c r="Y38" s="19" t="inlineStr">
         <is>
-          <t>TEST</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="Z38" s="19" t="inlineStr">
@@ -24661,32 +24679,30 @@
       <c r="AA38" s="19" t="n">
         <v/>
       </c>
-      <c r="AB38" s="19" t="inlineStr">
-        <is>
-          <t>JP280926-3</t>
-        </is>
+      <c r="AB38" s="19" t="n">
+        <v/>
       </c>
       <c r="AC38" s="19" t="inlineStr">
         <is>
-          <t>#6204</t>
+          <t>#6229</t>
         </is>
       </c>
       <c r="AD38" s="19" t="inlineStr">
         <is>
-          <t>012C-3004</t>
+          <t>1150002-09716</t>
         </is>
       </c>
       <c r="AE38" s="21" t="n">
-        <v>2300</v>
+        <v>2760</v>
       </c>
       <c r="AF38" s="21" t="n">
-        <v>2300</v>
+        <v>2760</v>
       </c>
       <c r="AG38" s="21" t="n">
-        <v>3600</v>
+        <v>4300</v>
       </c>
       <c r="AH38" s="21" t="n">
-        <v>3600</v>
+        <v>4300</v>
       </c>
       <c r="AI38" s="21" t="n">
         <v>200</v>
@@ -24695,7 +24711,7 @@
         <v/>
       </c>
       <c r="AK38" s="21" t="n">
-        <v>115.345</v>
+        <v>138.414</v>
       </c>
       <c r="AL38" s="21" t="n">
         <v/>
@@ -24734,7 +24750,7 @@
         <v/>
       </c>
       <c r="AV38" s="21" t="n">
-        <v>3600</v>
+        <v>4300</v>
       </c>
       <c r="AW38" s="19" t="n">
         <v/>
@@ -24743,7 +24759,7 @@
         <v/>
       </c>
       <c r="AY38" s="19" t="n">
-        <v>2300</v>
+        <v>2760</v>
       </c>
       <c r="AZ38" s="19" t="inlineStr">
         <is>
@@ -24755,24 +24771,20 @@
       </c>
       <c r="BB38" s="19" t="inlineStr">
         <is>
-          <t>pick up 02/10</t>
-        </is>
-      </c>
-      <c r="BC38" s="19" t="inlineStr">
-        <is>
-          <t>до 10.10</t>
-        </is>
+          <t>UNCONFIRMED YET</t>
+        </is>
+      </c>
+      <c r="BC38" s="19" t="n">
+        <v/>
       </c>
       <c r="BD38" s="19" t="n">
         <v/>
       </c>
       <c r="BE38" s="19" t="n">
-        <v>2880</v>
-      </c>
-      <c r="BF38" s="19" t="inlineStr">
-        <is>
-          <t>Ф</t>
-        </is>
+        <v/>
+      </c>
+      <c r="BF38" s="19" t="n">
+        <v/>
       </c>
       <c r="BG38" s="19" t="n">
         <v/>
@@ -24783,10 +24795,8 @@
       <c r="BI38" s="19" t="n">
         <v/>
       </c>
-      <c r="BJ38" s="19" t="inlineStr">
-        <is>
-          <t>280926-3</t>
-        </is>
+      <c r="BJ38" s="19" t="n">
+        <v/>
       </c>
       <c r="BK38" s="19" t="n">
         <v/>
@@ -24800,7 +24810,7 @@
     </row>
     <row r="39">
       <c r="A39" s="29" t="n">
-        <v>21092614525</v>
+        <v>23092613105</v>
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
@@ -24814,7 +24824,7 @@
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>KDV-3</t>
+          <t>KDV-1</t>
         </is>
       </c>
       <c r="E39" s="40" t="inlineStr">
@@ -24824,8 +24834,8 @@
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20536126</t>
+          <t>DAT MOW
+P20561926</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
@@ -24840,29 +24850,27 @@
       </c>
       <c r="I39" s="29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J39" s="29" t="inlineStr">
         <is>
-          <t>737ALL</t>
-        </is>
-      </c>
-      <c r="K39" s="29" t="inlineStr">
-        <is>
-          <t>1150002-1</t>
-        </is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="K39" s="29" t="n">
+        <v>10009255</v>
       </c>
       <c r="L39" s="29" t="n">
         <v/>
       </c>
       <c r="M39" s="29" t="inlineStr">
         <is>
-          <t>SENSOR</t>
+          <t>POPPET</t>
         </is>
       </c>
       <c r="N39" s="31" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O39" s="29" t="inlineStr">
         <is>
@@ -24871,11 +24879,11 @@
       </c>
       <c r="P39" s="29" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q39" s="32" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="R39" s="29" t="n">
         <v>30</v>
@@ -24888,11 +24896,13 @@
       <c r="T39" s="29" t="n">
         <v/>
       </c>
-      <c r="U39" s="29" t="n">
-        <v/>
+      <c r="U39" s="29" t="inlineStr">
+        <is>
+          <t>PRIORITY NET</t>
+        </is>
       </c>
       <c r="V39" s="32" t="n">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="W39" s="29" t="n">
         <v/>
@@ -24904,7 +24914,7 @@
       </c>
       <c r="Y39" s="29" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z39" s="29" t="inlineStr">
@@ -24912,42 +24922,42 @@
           <t>LUFTHANSA</t>
         </is>
       </c>
-      <c r="AA39" s="29" t="n">
-        <v/>
+      <c r="AA39" s="29" t="inlineStr">
+        <is>
+          <t>AVIALL</t>
+        </is>
       </c>
       <c r="AB39" s="29" t="n">
         <v/>
       </c>
       <c r="AC39" s="29" t="inlineStr">
         <is>
-          <t>#6229</t>
-        </is>
-      </c>
-      <c r="AD39" s="29" t="inlineStr">
-        <is>
-          <t>1150002-09716</t>
-        </is>
+          <t>#6244</t>
+        </is>
+      </c>
+      <c r="AD39" s="29" t="n">
+        <v/>
       </c>
       <c r="AE39" s="33" t="n">
-        <v>2760</v>
+        <v>11</v>
       </c>
       <c r="AF39" s="33" t="n">
-        <v>2760</v>
+        <v>220</v>
       </c>
       <c r="AG39" s="33" t="n">
-        <v>4300</v>
+        <v>21</v>
       </c>
       <c r="AH39" s="33" t="n">
-        <v>4300</v>
+        <v>420</v>
       </c>
       <c r="AI39" s="33" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="AJ39" s="33" t="n">
         <v/>
       </c>
       <c r="AK39" s="33" t="n">
-        <v>138.414</v>
+        <v>11.033</v>
       </c>
       <c r="AL39" s="33" t="n">
         <v/>
@@ -24956,17 +24966,15 @@
         <v/>
       </c>
       <c r="AN39" s="29" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO39" s="29" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP39" s="29" t="inlineStr">
-        <is>
-          <t>Получаем МПТ</t>
-        </is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP39" s="29" t="n">
+        <v/>
       </c>
       <c r="AQ39" s="29" t="inlineStr">
         <is>
@@ -24986,7 +24994,7 @@
         <v/>
       </c>
       <c r="AV39" s="33" t="n">
-        <v>4300</v>
+        <v>420</v>
       </c>
       <c r="AW39" s="29" t="n">
         <v/>
@@ -24995,19 +25003,17 @@
         <v/>
       </c>
       <c r="AY39" s="29" t="n">
-        <v>2760</v>
-      </c>
-      <c r="AZ39" s="29" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
+        <v>220</v>
+      </c>
+      <c r="AZ39" s="34" t="n">
+        <v>46290</v>
       </c>
       <c r="BA39" s="29" t="n">
         <v/>
       </c>
       <c r="BB39" s="29" t="inlineStr">
         <is>
-          <t>UNCONFIRMED YET</t>
+          <t>HA WHS</t>
         </is>
       </c>
       <c r="BC39" s="29" t="n">
@@ -25019,8 +25025,10 @@
       <c r="BE39" s="29" t="n">
         <v/>
       </c>
-      <c r="BF39" s="29" t="n">
-        <v/>
+      <c r="BF39" s="29" t="inlineStr">
+        <is>
+          <t>Др</t>
+        </is>
       </c>
       <c r="BG39" s="29" t="n">
         <v/>
@@ -25095,18 +25103,18 @@
         </is>
       </c>
       <c r="K40" s="19" t="n">
-        <v>10009255</v>
+        <v>10009072</v>
       </c>
       <c r="L40" s="19" t="n">
         <v/>
       </c>
       <c r="M40" s="19" t="inlineStr">
         <is>
-          <t>POPPET</t>
+          <t>INSTRUCTION DECAL</t>
         </is>
       </c>
       <c r="N40" s="20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O40" s="19" t="inlineStr">
         <is>
@@ -25168,23 +25176,23 @@
       </c>
       <c r="AC40" s="19" t="inlineStr">
         <is>
-          <t>#6244</t>
+          <t>#6245</t>
         </is>
       </c>
       <c r="AD40" s="19" t="n">
         <v/>
       </c>
       <c r="AE40" s="21" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AF40" s="21" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AG40" s="21" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="AH40" s="21" t="n">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="AI40" s="21" t="n">
         <v>50</v>
@@ -25193,7 +25201,7 @@
         <v/>
       </c>
       <c r="AK40" s="21" t="n">
-        <v>11.033</v>
+        <v>10.03</v>
       </c>
       <c r="AL40" s="21" t="n">
         <v/>
@@ -25230,7 +25238,7 @@
         <v/>
       </c>
       <c r="AV40" s="21" t="n">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="AW40" s="19" t="n">
         <v/>
@@ -25239,7 +25247,7 @@
         <v/>
       </c>
       <c r="AY40" s="19" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AZ40" s="36" t="n">
         <v>46290</v>
@@ -25290,7 +25298,7 @@
     </row>
     <row r="41">
       <c r="A41" s="29" t="n">
-        <v>23092613105</v>
+        <v>2309268425</v>
       </c>
       <c r="B41" s="29" t="inlineStr">
         <is>
@@ -25315,7 +25323,7 @@
       <c r="F41" s="29" t="inlineStr">
         <is>
           <t>DAT MOW
-P20561926</t>
+P20557426</t>
         </is>
       </c>
       <c r="G41" s="29" t="inlineStr">
@@ -25335,22 +25343,24 @@
       </c>
       <c r="J41" s="29" t="inlineStr">
         <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="K41" s="29" t="n">
-        <v>10009072</v>
+          <t>BOEING</t>
+        </is>
+      </c>
+      <c r="K41" s="29" t="inlineStr">
+        <is>
+          <t>3-906S383-70</t>
+        </is>
       </c>
       <c r="L41" s="29" t="n">
         <v/>
       </c>
       <c r="M41" s="29" t="inlineStr">
         <is>
-          <t>INSTRUCTION DECAL</t>
+          <t>PACKING</t>
         </is>
       </c>
       <c r="N41" s="31" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="O41" s="29" t="inlineStr">
         <is>
@@ -25404,7 +25414,7 @@
       </c>
       <c r="AA41" s="29" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="AB41" s="29" t="n">
@@ -25412,23 +25422,23 @@
       </c>
       <c r="AC41" s="29" t="inlineStr">
         <is>
-          <t>#6245</t>
+          <t>#6235</t>
         </is>
       </c>
       <c r="AD41" s="29" t="n">
         <v/>
       </c>
       <c r="AE41" s="33" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="AF41" s="33" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AG41" s="33" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="AH41" s="33" t="n">
-        <v>440</v>
+        <v>800</v>
       </c>
       <c r="AI41" s="33" t="n">
         <v>50</v>
@@ -25437,7 +25447,7 @@
         <v/>
       </c>
       <c r="AK41" s="33" t="n">
-        <v>10.03</v>
+        <v>20.6</v>
       </c>
       <c r="AL41" s="33" t="n">
         <v/>
@@ -25474,7 +25484,7 @@
         <v/>
       </c>
       <c r="AV41" s="33" t="n">
-        <v>440</v>
+        <v>800</v>
       </c>
       <c r="AW41" s="29" t="n">
         <v/>
@@ -25483,17 +25493,17 @@
         <v/>
       </c>
       <c r="AY41" s="29" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AZ41" s="34" t="n">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="BA41" s="29" t="n">
         <v/>
       </c>
       <c r="BB41" s="29" t="inlineStr">
         <is>
-          <t>HA WHS</t>
+          <t>PAID</t>
         </is>
       </c>
       <c r="BC41" s="29" t="n">
@@ -25505,10 +25515,8 @@
       <c r="BE41" s="29" t="n">
         <v/>
       </c>
-      <c r="BF41" s="29" t="inlineStr">
-        <is>
-          <t>Др</t>
-        </is>
+      <c r="BF41" s="29" t="n">
+        <v/>
       </c>
       <c r="BG41" s="29" t="n">
         <v/>
@@ -25534,7 +25542,7 @@
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>2309268425</v>
+        <v>24092613345</v>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
@@ -25548,7 +25556,7 @@
       </c>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>KDV-1</t>
+          <t>KDV-3</t>
         </is>
       </c>
       <c r="E42" s="40" t="inlineStr">
@@ -25558,8 +25566,8 @@
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20557426</t>
+          <t>DDP MOW
+P20568326</t>
         </is>
       </c>
       <c r="G42" s="19" t="inlineStr">
@@ -25574,17 +25582,17 @@
       </c>
       <c r="I42" s="19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J42" s="19" t="inlineStr">
         <is>
-          <t>BOEING</t>
+          <t>737ALL</t>
         </is>
       </c>
       <c r="K42" s="19" t="inlineStr">
         <is>
-          <t>3-906S383-70</t>
+          <t>398908-5</t>
         </is>
       </c>
       <c r="L42" s="19" t="n">
@@ -25592,11 +25600,11 @@
       </c>
       <c r="M42" s="19" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>VALVE ASSY - TEMP CONT</t>
         </is>
       </c>
       <c r="N42" s="20" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="O42" s="19" t="inlineStr">
         <is>
@@ -25605,30 +25613,26 @@
       </c>
       <c r="P42" s="19" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q42" s="35" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="R42" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="S42" s="19" t="inlineStr">
-        <is>
-          <t>STK</t>
-        </is>
+      <c r="S42" s="19" t="n">
+        <v>14</v>
       </c>
       <c r="T42" s="19" t="n">
         <v/>
       </c>
-      <c r="U42" s="19" t="inlineStr">
-        <is>
-          <t>PRIORITY NET</t>
-        </is>
+      <c r="U42" s="19" t="n">
+        <v/>
       </c>
       <c r="V42" s="35" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="W42" s="19" t="n">
         <v/>
@@ -25640,50 +25644,54 @@
       </c>
       <c r="Y42" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="Z42" s="19" t="inlineStr">
         <is>
-          <t>LUFTHANSA</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="AA42" s="19" t="inlineStr">
         <is>
-          <t>WENCOR</t>
-        </is>
-      </c>
-      <c r="AB42" s="19" t="n">
-        <v/>
+          <t>OH CAPITAL ASSETS</t>
+        </is>
+      </c>
+      <c r="AB42" s="19" t="inlineStr">
+        <is>
+          <t>KTM2509261157</t>
+        </is>
       </c>
       <c r="AC42" s="19" t="inlineStr">
         <is>
-          <t>#6235</t>
-        </is>
-      </c>
-      <c r="AD42" s="19" t="n">
-        <v/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD42" s="19" t="inlineStr">
+        <is>
+          <t>18426</t>
+        </is>
       </c>
       <c r="AE42" s="21" t="n">
-        <v>2</v>
+        <v>10000</v>
       </c>
       <c r="AF42" s="21" t="n">
-        <v>400</v>
+        <v>10000</v>
       </c>
       <c r="AG42" s="21" t="n">
-        <v>4</v>
+        <v>14200</v>
       </c>
       <c r="AH42" s="21" t="n">
-        <v>800</v>
+        <v>14200</v>
       </c>
       <c r="AI42" s="21" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AJ42" s="21" t="n">
         <v/>
       </c>
       <c r="AK42" s="21" t="n">
-        <v>20.6</v>
+        <v>501.5</v>
       </c>
       <c r="AL42" s="21" t="n">
         <v/>
@@ -25692,15 +25700,17 @@
         <v/>
       </c>
       <c r="AN42" s="19" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AO42" s="19" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP42" s="19" t="n">
-        <v/>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP42" s="19" t="inlineStr">
+        <is>
+          <t>Получаем МПТ</t>
+        </is>
       </c>
       <c r="AQ42" s="19" t="inlineStr">
         <is>
@@ -25720,7 +25730,7 @@
         <v/>
       </c>
       <c r="AV42" s="21" t="n">
-        <v>800</v>
+        <v>14200</v>
       </c>
       <c r="AW42" s="19" t="n">
         <v/>
@@ -25729,18 +25739,16 @@
         <v/>
       </c>
       <c r="AY42" s="19" t="n">
-        <v>400</v>
+        <v>10000</v>
       </c>
       <c r="AZ42" s="36" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="BA42" s="19" t="n">
         <v/>
       </c>
-      <c r="BB42" s="19" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
+      <c r="BB42" s="19" t="n">
+        <v/>
       </c>
       <c r="BC42" s="19" t="n">
         <v/>
@@ -25778,7 +25786,7 @@
     </row>
     <row r="43">
       <c r="A43" s="29" t="n">
-        <v>24092613345</v>
+        <v>25092613455</v>
       </c>
       <c r="B43" s="29" t="inlineStr">
         <is>
@@ -25803,7 +25811,7 @@
       <c r="F43" s="29" t="inlineStr">
         <is>
           <t>DDP MOW
-P20568326</t>
+P20523626</t>
         </is>
       </c>
       <c r="G43" s="29" t="inlineStr">
@@ -25818,25 +25826,27 @@
       </c>
       <c r="I43" s="29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J43" s="29" t="inlineStr">
         <is>
-          <t>737ALL</t>
+          <t>B762</t>
         </is>
       </c>
       <c r="K43" s="29" t="inlineStr">
         <is>
-          <t>398908-5</t>
-        </is>
-      </c>
-      <c r="L43" s="29" t="n">
-        <v/>
+          <t>121282-25</t>
+        </is>
+      </c>
+      <c r="L43" s="29" t="inlineStr">
+        <is>
+          <t>DEC39-166-519</t>
+        </is>
       </c>
       <c r="M43" s="29" t="inlineStr">
         <is>
-          <t>VALVE ASSY - TEMP CONT</t>
+          <t>SHAFT ASSY</t>
         </is>
       </c>
       <c r="N43" s="31" t="n">
@@ -25849,17 +25859,19 @@
       </c>
       <c r="P43" s="29" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q43" s="32" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="R43" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="S43" s="29" t="n">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="S43" s="29" t="inlineStr">
+        <is>
+          <t>STK</t>
+        </is>
       </c>
       <c r="T43" s="29" t="n">
         <v/>
@@ -25868,7 +25880,7 @@
         <v/>
       </c>
       <c r="V43" s="32" t="n">
-        <v>46319</v>
+        <v>46317</v>
       </c>
       <c r="W43" s="29" t="n">
         <v/>
@@ -25880,7 +25892,7 @@
       </c>
       <c r="Y43" s="29" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z43" s="29" t="inlineStr">
@@ -25890,12 +25902,12 @@
       </c>
       <c r="AA43" s="29" t="inlineStr">
         <is>
-          <t>OH CAPITAL ASSETS</t>
+          <t>HANGAR BARN</t>
         </is>
       </c>
       <c r="AB43" s="29" t="inlineStr">
         <is>
-          <t>KTM2509261157</t>
+          <t>KTM3009261621</t>
         </is>
       </c>
       <c r="AC43" s="29" t="inlineStr">
@@ -25903,31 +25915,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD43" s="29" t="inlineStr">
-        <is>
-          <t>18426</t>
-        </is>
+      <c r="AD43" s="29" t="n">
+        <v/>
       </c>
       <c r="AE43" s="33" t="n">
-        <v>10000</v>
+        <v>11604</v>
       </c>
       <c r="AF43" s="33" t="n">
-        <v>10000</v>
+        <v>11604</v>
       </c>
       <c r="AG43" s="33" t="n">
-        <v>14200</v>
+        <v>16100</v>
       </c>
       <c r="AH43" s="33" t="n">
-        <v>14200</v>
+        <v>16100</v>
       </c>
       <c r="AI43" s="33" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" s="33" t="n">
         <v/>
       </c>
       <c r="AK43" s="33" t="n">
-        <v>501.5</v>
+        <v>581.9406</v>
       </c>
       <c r="AL43" s="33" t="n">
         <v/>
@@ -25936,11 +25946,11 @@
         <v/>
       </c>
       <c r="AN43" s="29" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO43" s="29" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
+          <t>Не применимо</t>
         </is>
       </c>
       <c r="AP43" s="29" t="inlineStr">
@@ -25950,7 +25960,7 @@
       </c>
       <c r="AQ43" s="29" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
+          <t>Частичная предоплата</t>
         </is>
       </c>
       <c r="AR43" s="29" t="n">
@@ -25966,7 +25976,7 @@
         <v/>
       </c>
       <c r="AV43" s="33" t="n">
-        <v>14200</v>
+        <v>16100</v>
       </c>
       <c r="AW43" s="29" t="n">
         <v/>
@@ -25975,10 +25985,10 @@
         <v/>
       </c>
       <c r="AY43" s="29" t="n">
-        <v>10000</v>
+        <v>11604</v>
       </c>
       <c r="AZ43" s="34" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="BA43" s="29" t="n">
         <v/>
@@ -26022,7 +26032,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>25092613455</v>
+        <v>28092614585</v>
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
@@ -26047,7 +26057,7 @@
       <c r="F44" s="19" t="inlineStr">
         <is>
           <t>DDP MOW
-P20523626</t>
+P20579726</t>
         </is>
       </c>
       <c r="G44" s="19" t="inlineStr">
@@ -26062,7 +26072,7 @@
       </c>
       <c r="I44" s="19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J44" s="19" t="inlineStr">
@@ -26072,17 +26082,15 @@
       </c>
       <c r="K44" s="19" t="inlineStr">
         <is>
-          <t>121282-25</t>
-        </is>
-      </c>
-      <c r="L44" s="19" t="inlineStr">
-        <is>
-          <t>DEC39-166-519</t>
-        </is>
+          <t>RDAA8046-01</t>
+        </is>
+      </c>
+      <c r="L44" s="19" t="n">
+        <v/>
       </c>
       <c r="M44" s="19" t="inlineStr">
         <is>
-          <t>SHAFT ASSY</t>
+          <t>CMT (TERMINAL ASSY-CAB. MANAGEMENT)</t>
         </is>
       </c>
       <c r="N44" s="20" t="n">
@@ -26095,19 +26103,17 @@
       </c>
       <c r="P44" s="19" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q44" s="35" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="R44" s="19" t="n">
-        <v>27</v>
-      </c>
-      <c r="S44" s="19" t="inlineStr">
-        <is>
-          <t>STK</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="S44" s="19" t="n">
+        <v>18</v>
       </c>
       <c r="T44" s="19" t="n">
         <v/>
@@ -26116,7 +26122,7 @@
         <v/>
       </c>
       <c r="V44" s="35" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="W44" s="19" t="n">
         <v/>
@@ -26128,7 +26134,7 @@
       </c>
       <c r="Y44" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="Z44" s="19" t="inlineStr">
@@ -26138,12 +26144,12 @@
       </c>
       <c r="AA44" s="19" t="inlineStr">
         <is>
-          <t>HANGAR BARN</t>
+          <t>SEATTLE AVIATION SOLUTIONS</t>
         </is>
       </c>
       <c r="AB44" s="19" t="inlineStr">
         <is>
-          <t>KTM3009261621</t>
+          <t>KTM110261615</t>
         </is>
       </c>
       <c r="AC44" s="19" t="inlineStr">
@@ -26155,25 +26161,25 @@
         <v/>
       </c>
       <c r="AE44" s="21" t="n">
-        <v>11604</v>
+        <v>3850</v>
       </c>
       <c r="AF44" s="21" t="n">
-        <v>11604</v>
+        <v>3850</v>
       </c>
       <c r="AG44" s="21" t="n">
-        <v>16100</v>
+        <v>6000</v>
       </c>
       <c r="AH44" s="21" t="n">
-        <v>16100</v>
+        <v>6000</v>
       </c>
       <c r="AI44" s="21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ44" s="21" t="n">
         <v/>
       </c>
       <c r="AK44" s="21" t="n">
-        <v>581.9406</v>
+        <v>193.0775</v>
       </c>
       <c r="AL44" s="21" t="n">
         <v/>
@@ -26182,11 +26188,11 @@
         <v/>
       </c>
       <c r="AN44" s="19" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AO44" s="19" t="inlineStr">
         <is>
-          <t>Не применимо</t>
+          <t>НЕТ МПТ</t>
         </is>
       </c>
       <c r="AP44" s="19" t="inlineStr">
@@ -26196,7 +26202,7 @@
       </c>
       <c r="AQ44" s="19" t="inlineStr">
         <is>
-          <t>Частичная предоплата</t>
+          <t>Постоплата 100%</t>
         </is>
       </c>
       <c r="AR44" s="19" t="n">
@@ -26212,7 +26218,7 @@
         <v/>
       </c>
       <c r="AV44" s="21" t="n">
-        <v>16100</v>
+        <v>6000</v>
       </c>
       <c r="AW44" s="19" t="n">
         <v/>
@@ -26221,10 +26227,10 @@
         <v/>
       </c>
       <c r="AY44" s="19" t="n">
-        <v>11604</v>
+        <v>3850</v>
       </c>
       <c r="AZ44" s="36" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="BA44" s="19" t="n">
         <v/>
@@ -26268,7 +26274,7 @@
     </row>
     <row r="45">
       <c r="A45" s="29" t="n">
-        <v>28092614585</v>
+        <v>29092616005</v>
       </c>
       <c r="B45" s="29" t="inlineStr">
         <is>
@@ -26282,7 +26288,7 @@
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>KDV-3</t>
+          <t>KDV-1</t>
         </is>
       </c>
       <c r="E45" s="40" t="inlineStr">
@@ -26292,8 +26298,8 @@
       </c>
       <c r="F45" s="29" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20579726</t>
+          <t>DAT MOW
+P20569126</t>
         </is>
       </c>
       <c r="G45" s="29" t="inlineStr">
@@ -26308,17 +26314,17 @@
       </c>
       <c r="I45" s="29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J45" s="29" t="inlineStr">
         <is>
-          <t>B762</t>
+          <t>BOEING</t>
         </is>
       </c>
       <c r="K45" s="29" t="inlineStr">
         <is>
-          <t>RDAA8046-01</t>
+          <t>BUL216</t>
         </is>
       </c>
       <c r="L45" s="29" t="n">
@@ -26326,11 +26332,11 @@
       </c>
       <c r="M45" s="29" t="inlineStr">
         <is>
-          <t>CMT (TERMINAL ASSY-CAB. MANAGEMENT)</t>
+          <t>TRANSISTOR</t>
         </is>
       </c>
       <c r="N45" s="31" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O45" s="29" t="inlineStr">
         <is>
@@ -26339,17 +26345,19 @@
       </c>
       <c r="P45" s="29" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q45" s="32" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="R45" s="29" t="n">
-        <v>25</v>
-      </c>
-      <c r="S45" s="29" t="n">
-        <v>18</v>
+        <v>30</v>
+      </c>
+      <c r="S45" s="29" t="inlineStr">
+        <is>
+          <t>STK</t>
+        </is>
       </c>
       <c r="T45" s="29" t="n">
         <v/>
@@ -26358,7 +26366,7 @@
         <v/>
       </c>
       <c r="V45" s="32" t="n">
-        <v>46318</v>
+        <v>46324</v>
       </c>
       <c r="W45" s="29" t="n">
         <v/>
@@ -26370,52 +26378,50 @@
       </c>
       <c r="Y45" s="29" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z45" s="29" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>LUFTHANSA</t>
         </is>
       </c>
       <c r="AA45" s="29" t="inlineStr">
         <is>
-          <t>SEATTLE AVIATION SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="AB45" s="29" t="inlineStr">
-        <is>
-          <t>KTM110261615</t>
-        </is>
+          <t>MOUSER ELECTRONICS</t>
+        </is>
+      </c>
+      <c r="AB45" s="29" t="n">
+        <v/>
       </c>
       <c r="AC45" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#6261</t>
         </is>
       </c>
       <c r="AD45" s="29" t="n">
         <v/>
       </c>
       <c r="AE45" s="33" t="n">
-        <v>3850</v>
+        <v>2</v>
       </c>
       <c r="AF45" s="33" t="n">
-        <v>3850</v>
+        <v>40</v>
       </c>
       <c r="AG45" s="33" t="n">
-        <v>6000</v>
+        <v>16</v>
       </c>
       <c r="AH45" s="33" t="n">
-        <v>6000</v>
+        <v>320</v>
       </c>
       <c r="AI45" s="33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ45" s="33" t="n">
         <v/>
       </c>
       <c r="AK45" s="33" t="n">
-        <v>193.0775</v>
+        <v>0.4</v>
       </c>
       <c r="AL45" s="33" t="n">
         <v/>
@@ -26424,21 +26430,19 @@
         <v/>
       </c>
       <c r="AN45" s="29" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO45" s="29" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP45" s="29" t="inlineStr">
-        <is>
-          <t>Получаем МПТ</t>
-        </is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP45" s="29" t="n">
+        <v/>
       </c>
       <c r="AQ45" s="29" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
+          <t>Частичная предоплата</t>
         </is>
       </c>
       <c r="AR45" s="29" t="n">
@@ -26454,7 +26458,7 @@
         <v/>
       </c>
       <c r="AV45" s="33" t="n">
-        <v>6000</v>
+        <v>320</v>
       </c>
       <c r="AW45" s="29" t="n">
         <v/>
@@ -26463,16 +26467,20 @@
         <v/>
       </c>
       <c r="AY45" s="29" t="n">
-        <v>3850</v>
-      </c>
-      <c r="AZ45" s="34" t="n">
-        <v>46296</v>
+        <v>40</v>
+      </c>
+      <c r="AZ45" s="29" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
       </c>
       <c r="BA45" s="29" t="n">
         <v/>
       </c>
-      <c r="BB45" s="29" t="n">
-        <v/>
+      <c r="BB45" s="29" t="inlineStr">
+        <is>
+          <t>UNCONFIRMED YET</t>
+        </is>
       </c>
       <c r="BC45" s="29" t="n">
         <v/>
@@ -26560,7 +26568,7 @@
       </c>
       <c r="K46" s="19" t="inlineStr">
         <is>
-          <t>BUL216</t>
+          <t>154MKP275KE</t>
         </is>
       </c>
       <c r="L46" s="19" t="n">
@@ -26568,7 +26576,7 @@
       </c>
       <c r="M46" s="19" t="inlineStr">
         <is>
-          <t>TRANSISTOR</t>
+          <t>CAPACITOR FILM</t>
         </is>
       </c>
       <c r="N46" s="20" t="n">
@@ -26632,23 +26640,23 @@
       </c>
       <c r="AC46" s="19" t="inlineStr">
         <is>
-          <t>#6261</t>
+          <t>#6262</t>
         </is>
       </c>
       <c r="AD46" s="19" t="n">
         <v/>
       </c>
       <c r="AE46" s="21" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="AF46" s="21" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="AG46" s="21" t="n">
-        <v>16</v>
+        <v>12.3</v>
       </c>
       <c r="AH46" s="21" t="n">
-        <v>320</v>
+        <v>246</v>
       </c>
       <c r="AI46" s="21" t="n">
         <v>50</v>
@@ -26657,7 +26665,7 @@
         <v/>
       </c>
       <c r="AK46" s="21" t="n">
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="AL46" s="21" t="n">
         <v/>
@@ -26694,7 +26702,7 @@
         <v/>
       </c>
       <c r="AV46" s="21" t="n">
-        <v>320</v>
+        <v>246</v>
       </c>
       <c r="AW46" s="19" t="n">
         <v/>
@@ -26703,7 +26711,7 @@
         <v/>
       </c>
       <c r="AY46" s="19" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="AZ46" s="19" t="inlineStr">
         <is>
@@ -26804,7 +26812,7 @@
       </c>
       <c r="K47" s="29" t="inlineStr">
         <is>
-          <t>154MKP275KE</t>
+          <t>224MKP275KB</t>
         </is>
       </c>
       <c r="L47" s="29" t="n">
@@ -26876,23 +26884,23 @@
       </c>
       <c r="AC47" s="29" t="inlineStr">
         <is>
-          <t>#6262</t>
+          <t>#6263</t>
         </is>
       </c>
       <c r="AD47" s="29" t="n">
         <v/>
       </c>
       <c r="AE47" s="33" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AF47" s="33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AG47" s="33" t="n">
-        <v>12.3</v>
+        <v>13.3</v>
       </c>
       <c r="AH47" s="33" t="n">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="AI47" s="33" t="n">
         <v>50</v>
@@ -26901,7 +26909,7 @@
         <v/>
       </c>
       <c r="AK47" s="33" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AL47" s="33" t="n">
         <v/>
@@ -26938,7 +26946,7 @@
         <v/>
       </c>
       <c r="AV47" s="33" t="n">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="AW47" s="29" t="n">
         <v/>
@@ -26947,7 +26955,7 @@
         <v/>
       </c>
       <c r="AY47" s="29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AZ47" s="29" t="inlineStr">
         <is>
@@ -27048,7 +27056,7 @@
       </c>
       <c r="K48" s="19" t="inlineStr">
         <is>
-          <t>224MKP275KB</t>
+          <t>B32642B0183J</t>
         </is>
       </c>
       <c r="L48" s="19" t="n">
@@ -27120,7 +27128,7 @@
       </c>
       <c r="AC48" s="19" t="inlineStr">
         <is>
-          <t>#6263</t>
+          <t>#6264</t>
         </is>
       </c>
       <c r="AD48" s="19" t="n">
@@ -27242,7 +27250,7 @@
     </row>
     <row r="49">
       <c r="A49" s="29" t="n">
-        <v>29092616005</v>
+        <v>30092609185</v>
       </c>
       <c r="B49" s="29" t="inlineStr">
         <is>
@@ -27256,7 +27264,7 @@
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>KDV-1</t>
+          <t>KDV-3</t>
         </is>
       </c>
       <c r="E49" s="40" t="inlineStr">
@@ -27266,8 +27274,8 @@
       </c>
       <c r="F49" s="29" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20569126</t>
+          <t>DDP MOW
+P20595226</t>
         </is>
       </c>
       <c r="G49" s="29" t="inlineStr">
@@ -27282,17 +27290,17 @@
       </c>
       <c r="I49" s="29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J49" s="29" t="inlineStr">
         <is>
-          <t>BOEING</t>
+          <t>B737</t>
         </is>
       </c>
       <c r="K49" s="29" t="inlineStr">
         <is>
-          <t>B32642B0183J</t>
+          <t>S152-0020-00</t>
         </is>
       </c>
       <c r="L49" s="29" t="n">
@@ -27300,11 +27308,11 @@
       </c>
       <c r="M49" s="29" t="inlineStr">
         <is>
-          <t>CAPACITOR FILM</t>
+          <t>CVR PANEL</t>
         </is>
       </c>
       <c r="N49" s="31" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O49" s="29" t="inlineStr">
         <is>
@@ -27313,11 +27321,11 @@
       </c>
       <c r="P49" s="29" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q49" s="32" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="R49" s="29" t="n">
         <v>30</v>
@@ -27334,7 +27342,7 @@
         <v/>
       </c>
       <c r="V49" s="32" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="W49" s="29" t="n">
         <v/>
@@ -27346,7 +27354,7 @@
       </c>
       <c r="Y49" s="29" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z49" s="29" t="inlineStr">
@@ -27354,42 +27362,42 @@
           <t>LUFTHANSA</t>
         </is>
       </c>
-      <c r="AA49" s="29" t="inlineStr">
-        <is>
-          <t>MOUSER ELECTRONICS</t>
-        </is>
+      <c r="AA49" s="29" t="n">
+        <v/>
       </c>
       <c r="AB49" s="29" t="n">
         <v/>
       </c>
       <c r="AC49" s="29" t="inlineStr">
         <is>
-          <t>#6264</t>
-        </is>
-      </c>
-      <c r="AD49" s="29" t="n">
-        <v/>
+          <t>#6265</t>
+        </is>
+      </c>
+      <c r="AD49" s="29" t="inlineStr">
+        <is>
+          <t>000523364</t>
+        </is>
       </c>
       <c r="AE49" s="33" t="n">
-        <v>0.6</v>
+        <v>8800</v>
       </c>
       <c r="AF49" s="33" t="n">
-        <v>12</v>
+        <v>8800</v>
       </c>
       <c r="AG49" s="33" t="n">
-        <v>13.3</v>
+        <v>12000</v>
       </c>
       <c r="AH49" s="33" t="n">
-        <v>266</v>
+        <v>12000</v>
       </c>
       <c r="AI49" s="33" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="AJ49" s="33" t="n">
         <v/>
       </c>
       <c r="AK49" s="33" t="n">
-        <v>0.12</v>
+        <v>88</v>
       </c>
       <c r="AL49" s="33" t="n">
         <v/>
@@ -27398,19 +27406,21 @@
         <v/>
       </c>
       <c r="AN49" s="29" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AO49" s="29" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP49" s="29" t="n">
-        <v/>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP49" s="29" t="inlineStr">
+        <is>
+          <t>Получаем МПТ</t>
+        </is>
       </c>
       <c r="AQ49" s="29" t="inlineStr">
         <is>
-          <t>Частичная предоплата</t>
+          <t>Постоплата 100%</t>
         </is>
       </c>
       <c r="AR49" s="29" t="n">
@@ -27426,7 +27436,7 @@
         <v/>
       </c>
       <c r="AV49" s="33" t="n">
-        <v>266</v>
+        <v>12000</v>
       </c>
       <c r="AW49" s="29" t="n">
         <v/>
@@ -27435,12 +27445,10 @@
         <v/>
       </c>
       <c r="AY49" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ49" s="29" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
+        <v>8800</v>
+      </c>
+      <c r="AZ49" s="34" t="n">
+        <v>46295</v>
       </c>
       <c r="BA49" s="29" t="n">
         <v/>
@@ -27486,7 +27494,7 @@
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>30092609185</v>
+        <v>30092610505</v>
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
@@ -27500,7 +27508,7 @@
       </c>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>KDV-3</t>
+          <t>KDV-1</t>
         </is>
       </c>
       <c r="E50" s="40" t="inlineStr">
@@ -27510,8 +27518,8 @@
       </c>
       <c r="F50" s="19" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20595226</t>
+          <t>DAT MOW
+P20580226</t>
         </is>
       </c>
       <c r="G50" s="19" t="inlineStr">
@@ -27526,17 +27534,17 @@
       </c>
       <c r="I50" s="19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J50" s="19" t="inlineStr">
         <is>
-          <t>B737</t>
+          <t>B762</t>
         </is>
       </c>
       <c r="K50" s="19" t="inlineStr">
         <is>
-          <t>S152-0020-00</t>
+          <t>GR501BB4-4</t>
         </is>
       </c>
       <c r="L50" s="19" t="n">
@@ -27544,11 +27552,11 @@
       </c>
       <c r="M50" s="19" t="inlineStr">
         <is>
-          <t>CVR PANEL</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="N50" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O50" s="19" t="inlineStr">
         <is>
@@ -27557,14 +27565,14 @@
       </c>
       <c r="P50" s="19" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q50" s="35" t="n">
         <v>46295</v>
       </c>
       <c r="R50" s="19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="S50" s="19" t="inlineStr">
         <is>
@@ -27578,7 +27586,7 @@
         <v/>
       </c>
       <c r="V50" s="35" t="n">
-        <v>46325</v>
+        <v>46320</v>
       </c>
       <c r="W50" s="19" t="n">
         <v/>
@@ -27590,12 +27598,12 @@
       </c>
       <c r="Y50" s="19" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z50" s="19" t="inlineStr">
         <is>
-          <t>LUFTHANSA</t>
+          <t>BLUE OCEAN SOLUTIONS</t>
         </is>
       </c>
       <c r="AA50" s="19" t="n">
@@ -27606,34 +27614,32 @@
       </c>
       <c r="AC50" s="19" t="inlineStr">
         <is>
-          <t>#6265</t>
-        </is>
-      </c>
-      <c r="AD50" s="19" t="inlineStr">
-        <is>
-          <t>000523364</t>
-        </is>
+          <t>№2442</t>
+        </is>
+      </c>
+      <c r="AD50" s="19" t="n">
+        <v/>
       </c>
       <c r="AE50" s="21" t="n">
-        <v>8800</v>
+        <v>205.44</v>
       </c>
       <c r="AF50" s="21" t="n">
-        <v>8800</v>
+        <v>821.76</v>
       </c>
       <c r="AG50" s="21" t="n">
-        <v>12000</v>
+        <v>340</v>
       </c>
       <c r="AH50" s="21" t="n">
-        <v>12000</v>
+        <v>1360</v>
       </c>
       <c r="AI50" s="21" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AJ50" s="21" t="n">
         <v/>
       </c>
       <c r="AK50" s="21" t="n">
-        <v>88</v>
+        <v>41.211264</v>
       </c>
       <c r="AL50" s="21" t="n">
         <v/>
@@ -27642,17 +27648,15 @@
         <v/>
       </c>
       <c r="AN50" s="19" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO50" s="19" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP50" s="19" t="inlineStr">
-        <is>
-          <t>Получаем МПТ</t>
-        </is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP50" s="19" t="n">
+        <v/>
       </c>
       <c r="AQ50" s="19" t="inlineStr">
         <is>
@@ -27672,7 +27676,7 @@
         <v/>
       </c>
       <c r="AV50" s="21" t="n">
-        <v>12000</v>
+        <v>1360</v>
       </c>
       <c r="AW50" s="19" t="n">
         <v/>
@@ -27681,7 +27685,7 @@
         <v/>
       </c>
       <c r="AY50" s="19" t="n">
-        <v>8800</v>
+        <v>821.76</v>
       </c>
       <c r="AZ50" s="36" t="n">
         <v>46295</v>
@@ -27719,10 +27723,10 @@
         <v/>
       </c>
       <c r="BK50" s="19" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL50" s="19" t="n">
-        <v/>
+        <v>821.76</v>
       </c>
       <c r="BM50" s="19" t="n">
         <v/>
@@ -27730,7 +27734,7 @@
     </row>
     <row r="51">
       <c r="A51" s="29" t="n">
-        <v>30092610505</v>
+        <v>30092615555</v>
       </c>
       <c r="B51" s="29" t="inlineStr">
         <is>
@@ -27744,7 +27748,7 @@
       </c>
       <c r="D51" s="29" t="inlineStr">
         <is>
-          <t>KDV-1</t>
+          <t>KDV-3</t>
         </is>
       </c>
       <c r="E51" s="40" t="inlineStr">
@@ -27754,8 +27758,8 @@
       </c>
       <c r="F51" s="29" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20580226</t>
+          <t>DDP MOW
+P20594626</t>
         </is>
       </c>
       <c r="G51" s="29" t="inlineStr">
@@ -27770,17 +27774,17 @@
       </c>
       <c r="I51" s="29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J51" s="29" t="inlineStr">
         <is>
-          <t>B762</t>
+          <t>B738</t>
         </is>
       </c>
       <c r="K51" s="29" t="inlineStr">
         <is>
-          <t>GR501BB4-4</t>
+          <t>2116M23P01</t>
         </is>
       </c>
       <c r="L51" s="29" t="n">
@@ -27788,11 +27792,11 @@
       </c>
       <c r="M51" s="29" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>314 HPC STAGE 3 DISK</t>
         </is>
       </c>
       <c r="N51" s="31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O51" s="29" t="inlineStr">
         <is>
@@ -27801,14 +27805,14 @@
       </c>
       <c r="P51" s="29" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q51" s="32" t="n">
         <v>46295</v>
       </c>
       <c r="R51" s="29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="S51" s="29" t="inlineStr">
         <is>
@@ -27822,7 +27826,7 @@
         <v/>
       </c>
       <c r="V51" s="32" t="n">
-        <v>46320</v>
+        <v>46325</v>
       </c>
       <c r="W51" s="29" t="n">
         <v/>
@@ -27834,73 +27838,83 @@
       </c>
       <c r="Y51" s="29" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z51" s="29" t="inlineStr">
         <is>
-          <t>BLUE OCEAN SOLUTIONS</t>
+          <t>SOHO AERO</t>
         </is>
       </c>
       <c r="AA51" s="29" t="n">
         <v/>
       </c>
-      <c r="AB51" s="29" t="n">
-        <v/>
+      <c r="AB51" s="29" t="inlineStr">
+        <is>
+          <t>LS-261001-1</t>
+        </is>
       </c>
       <c r="AC51" s="29" t="inlineStr">
         <is>
-          <t>№2442</t>
-        </is>
-      </c>
-      <c r="AD51" s="29" t="n">
-        <v/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD51" s="29" t="inlineStr">
+        <is>
+          <t>XAECR005</t>
+        </is>
       </c>
       <c r="AE51" s="33" t="n">
-        <v>205.44</v>
+        <v>85000</v>
       </c>
       <c r="AF51" s="33" t="n">
-        <v>821.76</v>
+        <v>85000</v>
       </c>
       <c r="AG51" s="33" t="n">
-        <v>340</v>
+        <v>140000</v>
       </c>
       <c r="AH51" s="33" t="n">
-        <v>1360</v>
+        <v>140000</v>
       </c>
       <c r="AI51" s="33" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AJ51" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AK51" s="33" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="AL51" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AM51" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AN51" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AJ51" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AK51" s="33" t="n">
-        <v>41.211264</v>
-      </c>
-      <c r="AL51" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AM51" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AN51" s="29" t="n">
-        <v>0.22</v>
-      </c>
       <c r="AO51" s="29" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP51" s="29" t="n">
-        <v/>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP51" s="29" t="inlineStr">
+        <is>
+          <t>Получаем МПТ</t>
+        </is>
       </c>
       <c r="AQ51" s="29" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
-        </is>
-      </c>
-      <c r="AR51" s="29" t="n">
-        <v/>
+          <t>Частичная предоплата</t>
+        </is>
+      </c>
+      <c r="AR51" s="29" t="inlineStr">
+        <is>
+          <t>PLAN 08.10</t>
+        </is>
       </c>
       <c r="AS51" s="33" t="n">
         <v/>
@@ -27912,7 +27926,7 @@
         <v/>
       </c>
       <c r="AV51" s="33" t="n">
-        <v>1360</v>
+        <v>140000</v>
       </c>
       <c r="AW51" s="29" t="n">
         <v/>
@@ -27921,18 +27935,16 @@
         <v/>
       </c>
       <c r="AY51" s="29" t="n">
-        <v>821.76</v>
+        <v>85000</v>
       </c>
       <c r="AZ51" s="34" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="BA51" s="29" t="n">
         <v/>
       </c>
-      <c r="BB51" s="29" t="inlineStr">
-        <is>
-          <t>UNCONFIRMED YET</t>
-        </is>
+      <c r="BB51" s="29" t="n">
+        <v/>
       </c>
       <c r="BC51" s="29" t="n">
         <v/>
@@ -27959,10 +27971,10 @@
         <v/>
       </c>
       <c r="BK51" s="29" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="BL51" s="29" t="n">
-        <v>821.76</v>
+        <v/>
       </c>
       <c r="BM51" s="29" t="n">
         <v/>
@@ -27970,7 +27982,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
-        <v>30092615555</v>
+        <v>1102611065</v>
       </c>
       <c r="B52" s="19" t="inlineStr">
         <is>
@@ -27995,7 +28007,7 @@
       <c r="F52" s="19" t="inlineStr">
         <is>
           <t>DDP MOW
-P20594626</t>
+P20576726</t>
         </is>
       </c>
       <c r="G52" s="19" t="inlineStr">
@@ -28015,12 +28027,12 @@
       </c>
       <c r="J52" s="19" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>B762</t>
         </is>
       </c>
       <c r="K52" s="19" t="inlineStr">
         <is>
-          <t>2116M23P01</t>
+          <t>314U2200-23</t>
         </is>
       </c>
       <c r="L52" s="19" t="n">
@@ -28028,7 +28040,7 @@
       </c>
       <c r="M52" s="19" t="inlineStr">
         <is>
-          <t>314 HPC STAGE 3 DISK</t>
+          <t>PLUG ASSY</t>
         </is>
       </c>
       <c r="N52" s="20" t="n">
@@ -28045,7 +28057,7 @@
         </is>
       </c>
       <c r="Q52" s="35" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="R52" s="19" t="n">
         <v>30</v>
@@ -28062,7 +28074,7 @@
         <v/>
       </c>
       <c r="V52" s="35" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="W52" s="19" t="n">
         <v/>
@@ -28074,54 +28086,50 @@
       </c>
       <c r="Y52" s="19" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="Z52" s="19" t="inlineStr">
         <is>
-          <t>SOHO AERO</t>
+          <t>LUFTHANSA</t>
         </is>
       </c>
       <c r="AA52" s="19" t="n">
         <v/>
       </c>
-      <c r="AB52" s="19" t="inlineStr">
-        <is>
-          <t>LS-261001-1</t>
-        </is>
+      <c r="AB52" s="19" t="n">
+        <v/>
       </c>
       <c r="AC52" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#6266</t>
         </is>
       </c>
       <c r="AD52" s="19" t="inlineStr">
         <is>
-          <t>XAECR005</t>
+          <t>1356-A</t>
         </is>
       </c>
       <c r="AE52" s="21" t="n">
-        <v>85000</v>
+        <v>5500</v>
       </c>
       <c r="AF52" s="21" t="n">
-        <v>85000</v>
+        <v>5500</v>
       </c>
       <c r="AG52" s="21" t="n">
-        <v>140000</v>
+        <v>7500</v>
       </c>
       <c r="AH52" s="21" t="n">
-        <v>140000</v>
+        <v>7500</v>
       </c>
       <c r="AI52" s="21" t="n">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="AJ52" s="21" t="n">
         <v/>
       </c>
-      <c r="AK52" s="21" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
+      <c r="AK52" s="21" t="n">
+        <v>55</v>
       </c>
       <c r="AL52" s="21" t="n">
         <v/>
@@ -28147,10 +28155,8 @@
           <t>Частичная предоплата</t>
         </is>
       </c>
-      <c r="AR52" s="19" t="inlineStr">
-        <is>
-          <t>PLAN 08.10</t>
-        </is>
+      <c r="AR52" s="19" t="n">
+        <v/>
       </c>
       <c r="AS52" s="21" t="n">
         <v/>
@@ -28162,7 +28168,7 @@
         <v/>
       </c>
       <c r="AV52" s="21" t="n">
-        <v>140000</v>
+        <v>7500</v>
       </c>
       <c r="AW52" s="19" t="n">
         <v/>
@@ -28171,7 +28177,7 @@
         <v/>
       </c>
       <c r="AY52" s="19" t="n">
-        <v>85000</v>
+        <v>5500</v>
       </c>
       <c r="AZ52" s="36" t="n">
         <v>46296</v>
@@ -28217,494 +28223,252 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="n">
-        <v>1102611065</v>
-      </c>
-      <c r="B53" s="29" t="inlineStr">
+      <c r="A53" t="n">
+        <v>1102611295</v>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>М</t>
         </is>
       </c>
-      <c r="C53" s="29" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Ray</t>
         </is>
       </c>
-      <c r="D53" s="29" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>KDV-3</t>
         </is>
       </c>
-      <c r="E53" s="40" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>1 NOT PAID</t>
         </is>
       </c>
-      <c r="F53" s="29" t="inlineStr">
-        <is>
-          <t>DDP MOW
-P20576726</t>
-        </is>
-      </c>
-      <c r="G53" s="29" t="inlineStr">
-        <is>
-          <t>Utair</t>
-        </is>
-      </c>
-      <c r="H53" s="29" t="inlineStr">
-        <is>
-          <t>комм</t>
-        </is>
-      </c>
-      <c r="I53" s="29" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J53" s="29" t="inlineStr">
-        <is>
-          <t>B762</t>
-        </is>
-      </c>
-      <c r="K53" s="29" t="inlineStr">
-        <is>
-          <t>314U2200-23</t>
-        </is>
-      </c>
-      <c r="L53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="29" t="inlineStr">
-        <is>
-          <t>PLUG ASSY</t>
-        </is>
-      </c>
-      <c r="N53" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" s="29" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="P53" s="29" t="inlineStr">
-        <is>
-          <t>ROTABLE</t>
-        </is>
-      </c>
-      <c r="Q53" s="32" t="n">
-        <v>46296</v>
-      </c>
-      <c r="R53" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="S53" s="29" t="inlineStr">
-        <is>
-          <t>STK</t>
-        </is>
-      </c>
-      <c r="T53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="32" t="n">
-        <v>46326</v>
-      </c>
-      <c r="W53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="X53" s="29" t="inlineStr">
-        <is>
-          <t>Продажа от поставщика</t>
-        </is>
-      </c>
-      <c r="Y53" s="29" t="inlineStr">
-        <is>
-          <t>SV</t>
-        </is>
-      </c>
-      <c r="Z53" s="29" t="inlineStr">
-        <is>
-          <t>LUFTHANSA</t>
-        </is>
-      </c>
-      <c r="AA53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AB53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AC53" s="29" t="inlineStr">
-        <is>
-          <t>#6266</t>
-        </is>
-      </c>
-      <c r="AD53" s="29" t="inlineStr">
-        <is>
-          <t>1356-A</t>
-        </is>
-      </c>
-      <c r="AE53" s="33" t="n">
-        <v>5500</v>
-      </c>
-      <c r="AF53" s="33" t="n">
-        <v>5500</v>
-      </c>
-      <c r="AG53" s="33" t="n">
-        <v>7500</v>
-      </c>
-      <c r="AH53" s="33" t="n">
-        <v>7500</v>
-      </c>
-      <c r="AI53" s="33" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ53" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AK53" s="33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL53" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AM53" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AN53" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO53" s="29" t="inlineStr">
-        <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP53" s="29" t="inlineStr">
-        <is>
-          <t>Получаем МПТ</t>
-        </is>
-      </c>
-      <c r="AQ53" s="29" t="inlineStr">
-        <is>
-          <t>Частичная предоплата</t>
-        </is>
-      </c>
-      <c r="AR53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AS53" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AT53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AU53" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AV53" s="33" t="n">
-        <v>7500</v>
-      </c>
-      <c r="AW53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AX53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AY53" s="29" t="n">
-        <v>5500</v>
-      </c>
-      <c r="AZ53" s="34" t="n">
-        <v>46296</v>
-      </c>
-      <c r="BA53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BB53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BC53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BD53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BE53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BF53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BG53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BH53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BI53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BJ53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BK53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BL53" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BM53" s="29" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>1102611295</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>М</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ray</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>KDV-3</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>1 NOT PAID</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>DDP MOW
 P20584726</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Utair</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>комм</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>737CL</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>622-8001-350</t>
         </is>
       </c>
-      <c r="L54" t="n">
-        <v/>
-      </c>
-      <c r="M54" t="inlineStr">
+      <c r="L53" t="n">
+        <v/>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>PANEL ASSY</t>
         </is>
       </c>
-      <c r="N54" t="n">
+      <c r="N53" t="n">
         <v>2</v>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>ROTABLE</t>
         </is>
       </c>
-      <c r="Q54" s="38" t="n">
+      <c r="Q53" s="38" t="n">
         <v>46296</v>
       </c>
-      <c r="R54" t="n">
+      <c r="R53" t="n">
         <v>30</v>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>STK</t>
         </is>
       </c>
-      <c r="T54" t="n">
-        <v/>
-      </c>
-      <c r="U54" t="n">
-        <v/>
-      </c>
-      <c r="V54" t="n">
-        <v/>
-      </c>
-      <c r="W54" t="n">
-        <v/>
-      </c>
-      <c r="X54" t="inlineStr">
+      <c r="T53" t="n">
+        <v/>
+      </c>
+      <c r="U53" t="n">
+        <v/>
+      </c>
+      <c r="V53" t="n">
+        <v/>
+      </c>
+      <c r="W53" t="n">
+        <v/>
+      </c>
+      <c r="X53" t="inlineStr">
         <is>
           <t>Продажа от поставщика</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>RP</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>JET TECHNIC</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>JMF GLOBAL</t>
         </is>
       </c>
-      <c r="AB54" t="n">
-        <v/>
-      </c>
-      <c r="AC54" t="inlineStr">
+      <c r="AB53" t="n">
+        <v/>
+      </c>
+      <c r="AC53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AD54" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>873
 1509</t>
         </is>
       </c>
-      <c r="AE54" t="n">
+      <c r="AE53" t="n">
         <v>10000</v>
       </c>
-      <c r="AF54" t="n">
+      <c r="AF53" t="n">
         <v>20000</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AG53" t="n">
         <v>13500</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AH53" t="n">
         <v>27000</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AI53" t="n">
         <v>1000</v>
       </c>
-      <c r="AJ54" t="n">
-        <v/>
-      </c>
-      <c r="AK54" t="n">
+      <c r="AJ53" t="n">
+        <v/>
+      </c>
+      <c r="AK53" t="n">
         <v>1003</v>
       </c>
-      <c r="AL54" t="n">
-        <v/>
-      </c>
-      <c r="AM54" t="n">
-        <v/>
-      </c>
-      <c r="AN54" t="n">
+      <c r="AL53" t="n">
+        <v/>
+      </c>
+      <c r="AM53" t="n">
+        <v/>
+      </c>
+      <c r="AN53" t="n">
         <v>0</v>
       </c>
-      <c r="AO54" t="inlineStr">
+      <c r="AO53" t="inlineStr">
         <is>
           <t>НЕТ МПТ</t>
         </is>
       </c>
-      <c r="AP54" t="inlineStr">
+      <c r="AP53" t="inlineStr">
         <is>
           <t>Получаем МПТ</t>
         </is>
       </c>
-      <c r="AQ54" t="inlineStr">
+      <c r="AQ53" t="inlineStr">
         <is>
           <t>Частичная предоплата</t>
         </is>
       </c>
-      <c r="AR54" t="n">
-        <v/>
-      </c>
-      <c r="AS54" t="n">
-        <v/>
-      </c>
-      <c r="AT54" t="n">
-        <v/>
-      </c>
-      <c r="AU54" t="n">
-        <v/>
-      </c>
-      <c r="AV54" t="n">
+      <c r="AR53" t="n">
+        <v/>
+      </c>
+      <c r="AS53" t="n">
+        <v/>
+      </c>
+      <c r="AT53" t="n">
+        <v/>
+      </c>
+      <c r="AU53" t="n">
+        <v/>
+      </c>
+      <c r="AV53" t="n">
         <v>27000</v>
       </c>
-      <c r="AW54" t="n">
-        <v/>
-      </c>
-      <c r="AX54" t="n">
-        <v/>
-      </c>
-      <c r="AY54" t="n">
+      <c r="AW53" t="n">
+        <v/>
+      </c>
+      <c r="AX53" t="n">
+        <v/>
+      </c>
+      <c r="AY53" t="n">
         <v>20000</v>
       </c>
-      <c r="AZ54" s="38" t="n">
+      <c r="AZ53" s="38" t="n">
         <v>46296</v>
       </c>
-      <c r="BA54" t="n">
-        <v/>
-      </c>
-      <c r="BB54" t="n">
-        <v/>
-      </c>
-      <c r="BC54" t="n">
-        <v/>
-      </c>
-      <c r="BD54" t="n">
-        <v/>
-      </c>
-      <c r="BE54" t="n">
-        <v/>
-      </c>
-      <c r="BF54" t="n">
-        <v/>
-      </c>
-      <c r="BG54" t="n">
-        <v/>
-      </c>
-      <c r="BH54" t="n">
-        <v/>
-      </c>
-      <c r="BI54" t="n">
-        <v/>
-      </c>
-      <c r="BJ54" t="n">
-        <v/>
-      </c>
-      <c r="BK54" t="n">
-        <v/>
-      </c>
-      <c r="BL54" t="n">
-        <v/>
-      </c>
-      <c r="BM54" t="n">
+      <c r="BA53" t="n">
+        <v/>
+      </c>
+      <c r="BB53" t="n">
+        <v/>
+      </c>
+      <c r="BC53" t="n">
+        <v/>
+      </c>
+      <c r="BD53" t="n">
+        <v/>
+      </c>
+      <c r="BE53" t="n">
+        <v/>
+      </c>
+      <c r="BF53" t="n">
+        <v/>
+      </c>
+      <c r="BG53" t="n">
+        <v/>
+      </c>
+      <c r="BH53" t="n">
+        <v/>
+      </c>
+      <c r="BI53" t="n">
+        <v/>
+      </c>
+      <c r="BJ53" t="n">
+        <v/>
+      </c>
+      <c r="BK53" t="n">
+        <v/>
+      </c>
+      <c r="BL53" t="n">
+        <v/>
+      </c>
+      <c r="BM53" t="n">
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BM53"/>
+  <autoFilter ref="A1:BM52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/Utair статус 02.10.2026.xlsx
+++ b/output/Utair статус 02.10.2026.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Отгружено'!$A$1:$BM$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'В работе'!$A$1:$BM$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'В работе'!$A$1:$BM$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -686,7 +686,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дата отчёта: 02.10.2026   |   В работе: 51 поз.   |   Отгружено: 49 поз.</t>
+          <t>Дата отчёта: 02.10.2026   |   В работе: 52 поз.   |   Отгружено: 49 поз.</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>702099</v>
+        <v>704099</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>657488.5</v>
@@ -782,22 +782,22 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>486807.15</v>
+        <v>486997.15</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>33100</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>18971.614419</v>
+        <v>18981.399419</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>702099</v>
+        <v>704099</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>163220.235581</v>
+        <v>165020.450581</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>44610.5</v>
+        <v>46610.5</v>
       </c>
       <c r="H10" s="13" t="n">
         <v>657488.5</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="M33" s="19" t="inlineStr">
         <is>
-          <t>дата поставки в периоде</t>
+          <t>статус → отгружено; дата поставки в периоде</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM53"/>
+  <dimension ref="A1:BM54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15877,18 +15877,18 @@
       <c r="AD2" s="27" t="n"/>
       <c r="AE2" s="27" t="n"/>
       <c r="AF2" s="28" t="n">
-        <v>486807.15</v>
+        <v>486997.15</v>
       </c>
       <c r="AG2" s="27" t="n"/>
       <c r="AH2" s="28" t="n">
-        <v>702099</v>
+        <v>704099</v>
       </c>
       <c r="AI2" s="28" t="n">
         <v>33100</v>
       </c>
       <c r="AJ2" s="27" t="n"/>
       <c r="AK2" s="28" t="n">
-        <v>18971.614419</v>
+        <v>18981.399419</v>
       </c>
       <c r="AL2" s="27" t="n"/>
       <c r="AM2" s="27" t="n"/>
@@ -15898,7 +15898,7 @@
       <c r="AQ2" s="27" t="n"/>
       <c r="AR2" s="27" t="n"/>
       <c r="AS2" s="28" t="n">
-        <v>44610.5</v>
+        <v>46610.5</v>
       </c>
       <c r="AT2" s="27" t="n"/>
       <c r="AU2" s="27" t="n"/>
@@ -19407,7 +19407,7 @@
     </row>
     <row r="17">
       <c r="A17" s="29" t="n">
-        <v>12082610355</v>
+        <v>10082615365</v>
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
@@ -19424,15 +19424,15 @@
           <t>KDV-1</t>
         </is>
       </c>
-      <c r="E17" s="41" t="inlineStr">
-        <is>
-          <t>6 TROUBLE</t>
+      <c r="E17" s="40" t="inlineStr">
+        <is>
+          <t>1 NOT PAID</t>
         </is>
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20339826</t>
+          <t>DDP MOW
+P20318726</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
@@ -19457,21 +19457,19 @@
       </c>
       <c r="K17" s="29" t="inlineStr">
         <is>
-          <t>CF2051</t>
-        </is>
-      </c>
-      <c r="L17" s="29" t="inlineStr">
-        <is>
-          <t>CF-2051</t>
-        </is>
+          <t>137-00-870-14GK</t>
+        </is>
+      </c>
+      <c r="L17" s="29" t="n">
+        <v/>
       </c>
       <c r="M17" s="29" t="inlineStr">
         <is>
-          <t>CAM FOLLOWER</t>
+          <t>SHROUD, IAT AISLE OUTER</t>
         </is>
       </c>
       <c r="N17" s="31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O17" s="29" t="inlineStr">
         <is>
@@ -19484,10 +19482,10 @@
         </is>
       </c>
       <c r="Q17" s="32" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="R17" s="29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="S17" s="29" t="inlineStr">
         <is>
@@ -19501,14 +19499,14 @@
         <v/>
       </c>
       <c r="V17" s="32" t="n">
-        <v>46271</v>
-      </c>
-      <c r="W17" s="29" t="n">
-        <v/>
+        <v>46254</v>
+      </c>
+      <c r="W17" s="32" t="n">
+        <v>46244</v>
       </c>
       <c r="X17" s="29" t="inlineStr">
         <is>
-          <t>Продажа от поставщика</t>
+          <t>Продажа со склада</t>
         </is>
       </c>
       <c r="Y17" s="29" t="inlineStr">
@@ -19516,10 +19514,8 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="Z17" s="29" t="inlineStr">
-        <is>
-          <t>BLUE OCEAN SOLUTIONS</t>
-        </is>
+      <c r="Z17" s="29" t="n">
+        <v/>
       </c>
       <c r="AA17" s="29" t="n">
         <v/>
@@ -19529,23 +19525,23 @@
       </c>
       <c r="AC17" s="29" t="inlineStr">
         <is>
-          <t>№2248 - cancel</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AD17" s="29" t="n">
         <v/>
       </c>
       <c r="AE17" s="33" t="n">
-        <v>671.5</v>
+        <v>190</v>
       </c>
       <c r="AF17" s="33" t="n">
-        <v>4700.5</v>
+        <v>190</v>
       </c>
       <c r="AG17" s="33" t="n">
-        <v>1100</v>
+        <v>2000</v>
       </c>
       <c r="AH17" s="33" t="n">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="AI17" s="33" t="n">
         <v>0</v>
@@ -19554,7 +19550,7 @@
         <v/>
       </c>
       <c r="AK17" s="33" t="n">
-        <v>242.07575</v>
+        <v>9.785</v>
       </c>
       <c r="AL17" s="33" t="n">
         <v/>
@@ -19575,7 +19571,7 @@
       </c>
       <c r="AQ17" s="29" t="inlineStr">
         <is>
-          <t>Частичная предоплата</t>
+          <t>Постоплата 100%</t>
         </is>
       </c>
       <c r="AR17" s="29" t="n">
@@ -19584,14 +19580,14 @@
       <c r="AS17" s="33" t="n">
         <v/>
       </c>
-      <c r="AT17" s="29" t="n">
-        <v/>
+      <c r="AT17" s="32" t="n">
+        <v>46289</v>
       </c>
       <c r="AU17" s="33" t="n">
-        <v/>
+        <v>2000</v>
       </c>
       <c r="AV17" s="33" t="n">
-        <v>7700</v>
+        <v>0</v>
       </c>
       <c r="AW17" s="29" t="n">
         <v/>
@@ -19600,23 +19596,19 @@
         <v/>
       </c>
       <c r="AY17" s="29" t="n">
-        <v>4700.5</v>
+        <v>190</v>
       </c>
       <c r="AZ17" s="34" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="BA17" s="29" t="n">
         <v/>
       </c>
-      <c r="BB17" s="29" t="inlineStr">
-        <is>
-          <t>UNSOLVED</t>
-        </is>
-      </c>
-      <c r="BC17" s="29" t="inlineStr">
-        <is>
-          <t>Sold, new price too high, ищем с Даней</t>
-        </is>
+      <c r="BB17" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BC17" s="29" t="n">
+        <v/>
       </c>
       <c r="BD17" s="29" t="n">
         <v/>
@@ -19651,7 +19643,7 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>13082611355</v>
+        <v>12082610355</v>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
@@ -19665,18 +19657,18 @@
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>KDV-3+RAP</t>
-        </is>
-      </c>
-      <c r="E18" s="39" t="inlineStr">
-        <is>
-          <t>2 PAID</t>
+          <t>KDV-1</t>
+        </is>
+      </c>
+      <c r="E18" s="41" t="inlineStr">
+        <is>
+          <t>6 TROUBLE</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20349026</t>
+          <t>DAT MOW
+P20339826</t>
         </is>
       </c>
       <c r="G18" s="19" t="inlineStr">
@@ -19691,28 +19683,31 @@
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J18" s="19" t="inlineStr">
         <is>
-          <t>B738</t>
-        </is>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>902862</v>
-      </c>
-      <c r="L18" s="19" t="n">
-        <v/>
+          <t>B735</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="inlineStr">
+        <is>
+          <t>CF2051</t>
+        </is>
+      </c>
+      <c r="L18" s="19" t="inlineStr">
+        <is>
+          <t>CF-2051</t>
+        </is>
       </c>
       <c r="M18" s="19" t="inlineStr">
         <is>
-          <t>FIRE DETECTOR
-ASSY</t>
+          <t>CAM FOLLOWER</t>
         </is>
       </c>
       <c r="N18" s="20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O18" s="19" t="inlineStr">
         <is>
@@ -19721,11 +19716,11 @@
       </c>
       <c r="P18" s="19" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q18" s="35" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="R18" s="19" t="n">
         <v>25</v>
@@ -19738,13 +19733,11 @@
       <c r="T18" s="19" t="n">
         <v/>
       </c>
-      <c r="U18" s="19" t="inlineStr">
-        <is>
-          <t>PRIORITY NET</t>
-        </is>
+      <c r="U18" s="19" t="n">
+        <v/>
       </c>
       <c r="V18" s="35" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="W18" s="19" t="n">
         <v/>
@@ -19756,53 +19749,48 @@
       </c>
       <c r="Y18" s="19" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z18" s="19" t="inlineStr">
         <is>
-          <t>LUFTHANSA</t>
+          <t>BLUE OCEAN SOLUTIONS</t>
         </is>
       </c>
       <c r="AA18" s="19" t="n">
         <v/>
       </c>
-      <c r="AB18" s="19" t="inlineStr">
-        <is>
-          <t>JP160926-1</t>
-        </is>
+      <c r="AB18" s="19" t="n">
+        <v/>
       </c>
       <c r="AC18" s="19" t="inlineStr">
         <is>
-          <t>#6134</t>
-        </is>
-      </c>
-      <c r="AD18" s="19" t="inlineStr">
-        <is>
-          <t>3766
-9436 - sold</t>
-        </is>
+          <t>№2248 - cancel</t>
+        </is>
+      </c>
+      <c r="AD18" s="19" t="n">
+        <v/>
       </c>
       <c r="AE18" s="21" t="n">
-        <v>10500</v>
+        <v>671.5</v>
       </c>
       <c r="AF18" s="21" t="n">
-        <v>10500</v>
+        <v>4700.5</v>
       </c>
       <c r="AG18" s="21" t="n">
-        <v>14500</v>
+        <v>1100</v>
       </c>
       <c r="AH18" s="21" t="n">
-        <v>14500</v>
+        <v>7700</v>
       </c>
       <c r="AI18" s="21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ18" s="21" t="n">
         <v/>
       </c>
       <c r="AK18" s="21" t="n">
-        <v>540.75</v>
+        <v>242.07575</v>
       </c>
       <c r="AL18" s="21" t="n">
         <v/>
@@ -19811,21 +19799,19 @@
         <v/>
       </c>
       <c r="AN18" s="19" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO18" s="19" t="inlineStr">
         <is>
-          <t>ЕСТЬ МПТ на Самолеты типов Boeing 737</t>
-        </is>
-      </c>
-      <c r="AP18" s="19" t="inlineStr">
-        <is>
-          <t>Есть МПТ</t>
-        </is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP18" s="19" t="n">
+        <v/>
       </c>
       <c r="AQ18" s="19" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
+          <t>Частичная предоплата</t>
         </is>
       </c>
       <c r="AR18" s="19" t="n">
@@ -19841,43 +19827,41 @@
         <v/>
       </c>
       <c r="AV18" s="21" t="n">
-        <v>14500</v>
-      </c>
-      <c r="AW18" s="36" t="n">
-        <v>46297</v>
+        <v>7700</v>
+      </c>
+      <c r="AW18" s="19" t="n">
+        <v/>
       </c>
       <c r="AX18" s="19" t="n">
-        <v>10500</v>
+        <v/>
       </c>
       <c r="AY18" s="19" t="n">
-        <v>0</v>
+        <v>4700.5</v>
       </c>
       <c r="AZ18" s="36" t="n">
-        <v>46274</v>
+        <v>46246</v>
       </c>
       <c r="BA18" s="19" t="n">
         <v/>
       </c>
       <c r="BB18" s="19" t="inlineStr">
         <is>
-          <t>arrived at DXB and is under customs clearance</t>
+          <t>UNSOLVED</t>
         </is>
       </c>
       <c r="BC18" s="19" t="inlineStr">
         <is>
-          <t>до 05.10</t>
+          <t>Sold, new price too high, ищем с Даней</t>
         </is>
       </c>
       <c r="BD18" s="19" t="n">
         <v/>
       </c>
       <c r="BE18" s="19" t="n">
-        <v>11600</v>
-      </c>
-      <c r="BF18" s="19" t="inlineStr">
-        <is>
-          <t>Ф</t>
-        </is>
+        <v/>
+      </c>
+      <c r="BF18" s="19" t="n">
+        <v/>
       </c>
       <c r="BG18" s="19" t="n">
         <v/>
@@ -19888,10 +19872,8 @@
       <c r="BI18" s="19" t="n">
         <v/>
       </c>
-      <c r="BJ18" s="19" t="inlineStr">
-        <is>
-          <t>160926-1</t>
-        </is>
+      <c r="BJ18" s="19" t="n">
+        <v/>
       </c>
       <c r="BK18" s="19" t="n">
         <v/>
@@ -19905,7 +19887,7 @@
     </row>
     <row r="19">
       <c r="A19" s="29" t="n">
-        <v>19082612405</v>
+        <v>13082611355</v>
       </c>
       <c r="B19" s="29" t="inlineStr">
         <is>
@@ -19930,7 +19912,7 @@
       <c r="F19" s="29" t="inlineStr">
         <is>
           <t>DDP MOW
-P20368026</t>
+P20349026</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
@@ -19950,21 +19932,19 @@
       </c>
       <c r="J19" s="29" t="inlineStr">
         <is>
-          <t>B737</t>
-        </is>
-      </c>
-      <c r="K19" s="29" t="inlineStr">
-        <is>
-          <t>102LA2AG</t>
-        </is>
+          <t>B738</t>
+        </is>
+      </c>
+      <c r="K19" s="29" t="n">
+        <v>902862</v>
       </c>
       <c r="L19" s="29" t="n">
         <v/>
       </c>
       <c r="M19" s="29" t="inlineStr">
         <is>
-          <t>SENSOR-TOTAL AIR
-TEMPERATURE</t>
+          <t>FIRE DETECTOR
+ASSY</t>
         </is>
       </c>
       <c r="N19" s="31" t="n">
@@ -19981,7 +19961,7 @@
         </is>
       </c>
       <c r="Q19" s="32" t="n">
-        <v>46253</v>
+        <v>46247</v>
       </c>
       <c r="R19" s="29" t="n">
         <v>25</v>
@@ -19996,11 +19976,11 @@
       </c>
       <c r="U19" s="29" t="inlineStr">
         <is>
-          <t>POST AUG-26</t>
+          <t>PRIORITY NET</t>
         </is>
       </c>
       <c r="V19" s="32" t="n">
-        <v>46278</v>
+        <v>46272</v>
       </c>
       <c r="W19" s="29" t="n">
         <v/>
@@ -20012,54 +19992,53 @@
       </c>
       <c r="Y19" s="29" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z19" s="29" t="inlineStr">
         <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="AA19" s="29" t="inlineStr">
-        <is>
-          <t>FLIGHT AEROTECH</t>
-        </is>
+          <t>LUFTHANSA</t>
+        </is>
+      </c>
+      <c r="AA19" s="29" t="n">
+        <v/>
       </c>
       <c r="AB19" s="29" t="inlineStr">
         <is>
-          <t>KTM51908251513</t>
+          <t>JP160926-1</t>
         </is>
       </c>
       <c r="AC19" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#6134</t>
         </is>
       </c>
       <c r="AD19" s="29" t="inlineStr">
         <is>
-          <t>A28158</t>
+          <t>3766
+9436 - sold</t>
         </is>
       </c>
       <c r="AE19" s="33" t="n">
-        <v>12000</v>
+        <v>10500</v>
       </c>
       <c r="AF19" s="33" t="n">
-        <v>12000</v>
+        <v>10500</v>
       </c>
       <c r="AG19" s="33" t="n">
-        <v>16500</v>
+        <v>14500</v>
       </c>
       <c r="AH19" s="33" t="n">
-        <v>16500</v>
+        <v>14500</v>
       </c>
       <c r="AI19" s="33" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" s="33" t="n">
         <v/>
       </c>
       <c r="AK19" s="33" t="n">
-        <v>618</v>
+        <v>540.75</v>
       </c>
       <c r="AL19" s="33" t="n">
         <v/>
@@ -20082,7 +20061,7 @@
       </c>
       <c r="AQ19" s="29" t="inlineStr">
         <is>
-          <t>Частичная предоплата</t>
+          <t>Постоплата 100%</t>
         </is>
       </c>
       <c r="AR19" s="29" t="n">
@@ -20098,38 +20077,38 @@
         <v/>
       </c>
       <c r="AV19" s="33" t="n">
-        <v>16500</v>
+        <v>14500</v>
       </c>
       <c r="AW19" s="34" t="n">
-        <v>46261</v>
+        <v>46297</v>
       </c>
       <c r="AX19" s="29" t="n">
-        <v>12000</v>
+        <v>10500</v>
       </c>
       <c r="AY19" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AZ19" s="34" t="n">
-        <v>46253</v>
+        <v>46274</v>
       </c>
       <c r="BA19" s="29" t="n">
         <v/>
       </c>
       <c r="BB19" s="29" t="inlineStr">
         <is>
-          <t>Dubai now</t>
+          <t>arrived at DXB and is under customs clearance</t>
         </is>
       </c>
       <c r="BC19" s="29" t="inlineStr">
         <is>
-          <t>до 01.10</t>
+          <t>до 05.10</t>
         </is>
       </c>
       <c r="BD19" s="29" t="n">
         <v/>
       </c>
       <c r="BE19" s="29" t="n">
-        <v>13200</v>
+        <v>11600</v>
       </c>
       <c r="BF19" s="29" t="inlineStr">
         <is>
@@ -20147,7 +20126,7 @@
       </c>
       <c r="BJ19" s="29" t="inlineStr">
         <is>
-          <t>KT MNT CONSOLE-5</t>
+          <t>160926-1</t>
         </is>
       </c>
       <c r="BK19" s="29" t="n">
@@ -20162,7 +20141,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>24082615515</v>
+        <v>19082612405</v>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
@@ -20176,18 +20155,18 @@
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>KDV-1</t>
-        </is>
-      </c>
-      <c r="E20" s="41" t="inlineStr">
-        <is>
-          <t>6 TROUBLE</t>
+          <t>KDV-3+RAP</t>
+        </is>
+      </c>
+      <c r="E20" s="39" t="inlineStr">
+        <is>
+          <t>2 PAID</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20388326</t>
+          <t>DDP MOW
+P20368026</t>
         </is>
       </c>
       <c r="G20" s="19" t="inlineStr">
@@ -20202,31 +20181,30 @@
       </c>
       <c r="I20" s="19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J20" s="19" t="inlineStr">
         <is>
-          <t>B734</t>
+          <t>B737</t>
         </is>
       </c>
       <c r="K20" s="19" t="inlineStr">
         <is>
-          <t>T30L9M4</t>
-        </is>
-      </c>
-      <c r="L20" s="19" t="inlineStr">
-        <is>
-          <t>T30L-9</t>
-        </is>
+          <t>102LA2AG</t>
+        </is>
+      </c>
+      <c r="L20" s="19" t="n">
+        <v/>
       </c>
       <c r="M20" s="19" t="inlineStr">
         <is>
-          <t>TIE WRAP LONG</t>
+          <t>SENSOR-TOTAL AIR
+TEMPERATURE</t>
         </is>
       </c>
       <c r="N20" s="20" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
@@ -20235,14 +20213,14 @@
       </c>
       <c r="P20" s="19" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q20" s="35" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="R20" s="19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="S20" s="19" t="inlineStr">
         <is>
@@ -20252,11 +20230,13 @@
       <c r="T20" s="19" t="n">
         <v/>
       </c>
-      <c r="U20" s="19" t="n">
-        <v/>
+      <c r="U20" s="19" t="inlineStr">
+        <is>
+          <t>POST AUG-26</t>
+        </is>
       </c>
       <c r="V20" s="35" t="n">
-        <v>46288</v>
+        <v>46278</v>
       </c>
       <c r="W20" s="19" t="n">
         <v/>
@@ -20268,69 +20248,77 @@
       </c>
       <c r="Y20" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="Z20" s="19" t="inlineStr">
         <is>
-          <t>BLUE OCEAN SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="AA20" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AB20" s="19" t="n">
-        <v/>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="AA20" s="19" t="inlineStr">
+        <is>
+          <t>FLIGHT AEROTECH</t>
+        </is>
+      </c>
+      <c r="AB20" s="19" t="inlineStr">
+        <is>
+          <t>KTM51908251513</t>
+        </is>
       </c>
       <c r="AC20" s="19" t="inlineStr">
         <is>
-          <t>№2318</t>
-        </is>
-      </c>
-      <c r="AD20" s="19" t="n">
-        <v/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD20" s="19" t="inlineStr">
+        <is>
+          <t>A28158</t>
+        </is>
       </c>
       <c r="AE20" s="21" t="n">
-        <v>1.4</v>
+        <v>12000</v>
       </c>
       <c r="AF20" s="21" t="n">
-        <v>112</v>
+        <v>12000</v>
       </c>
       <c r="AG20" s="21" t="n">
-        <v>4</v>
+        <v>16500</v>
       </c>
       <c r="AH20" s="21" t="n">
-        <v>320</v>
+        <v>16500</v>
       </c>
       <c r="AI20" s="21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ20" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AK20" s="21" t="n">
+        <v>618</v>
+      </c>
+      <c r="AL20" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AM20" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AN20" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ20" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AK20" s="21" t="n">
-        <v>5.768</v>
-      </c>
-      <c r="AL20" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AM20" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AN20" s="19" t="n">
-        <v>0.22</v>
-      </c>
       <c r="AO20" s="19" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP20" s="19" t="n">
-        <v/>
+          <t>ЕСТЬ МПТ на Самолеты типов Boeing 737</t>
+        </is>
+      </c>
+      <c r="AP20" s="19" t="inlineStr">
+        <is>
+          <t>Есть МПТ</t>
+        </is>
       </c>
       <c r="AQ20" s="19" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
+          <t>Частичная предоплата</t>
         </is>
       </c>
       <c r="AR20" s="19" t="n">
@@ -20346,41 +20334,43 @@
         <v/>
       </c>
       <c r="AV20" s="21" t="n">
-        <v>320</v>
-      </c>
-      <c r="AW20" s="19" t="n">
-        <v/>
+        <v>16500</v>
+      </c>
+      <c r="AW20" s="36" t="n">
+        <v>46261</v>
       </c>
       <c r="AX20" s="19" t="n">
-        <v/>
+        <v>12000</v>
       </c>
       <c r="AY20" s="19" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="AZ20" s="36" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="BA20" s="19" t="n">
         <v/>
       </c>
       <c r="BB20" s="19" t="inlineStr">
         <is>
-          <t>UNSOLVED</t>
+          <t>Dubai now</t>
         </is>
       </c>
       <c r="BC20" s="19" t="inlineStr">
         <is>
-          <t>UNSOLVED, MOQ - 1000ea</t>
+          <t>до 01.10</t>
         </is>
       </c>
       <c r="BD20" s="19" t="n">
         <v/>
       </c>
       <c r="BE20" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BF20" s="19" t="n">
-        <v/>
+        <v>13200</v>
+      </c>
+      <c r="BF20" s="19" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
       </c>
       <c r="BG20" s="19" t="n">
         <v/>
@@ -20391,8 +20381,10 @@
       <c r="BI20" s="19" t="n">
         <v/>
       </c>
-      <c r="BJ20" s="19" t="n">
-        <v/>
+      <c r="BJ20" s="19" t="inlineStr">
+        <is>
+          <t>KT MNT CONSOLE-5</t>
+        </is>
       </c>
       <c r="BK20" s="19" t="n">
         <v/>
@@ -20406,7 +20398,7 @@
     </row>
     <row r="21">
       <c r="A21" s="29" t="n">
-        <v>26082610155</v>
+        <v>24082615515</v>
       </c>
       <c r="B21" s="29" t="inlineStr">
         <is>
@@ -20431,7 +20423,7 @@
       <c r="F21" s="29" t="inlineStr">
         <is>
           <t>DAT MOW
-P20416026</t>
+P20388326</t>
         </is>
       </c>
       <c r="G21" s="29" t="inlineStr">
@@ -20451,24 +20443,26 @@
       </c>
       <c r="J21" s="29" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>B734</t>
         </is>
       </c>
       <c r="K21" s="29" t="inlineStr">
         <is>
-          <t>MS27502B19C</t>
-        </is>
-      </c>
-      <c r="L21" s="29" t="n">
-        <v/>
+          <t>T30L9M4</t>
+        </is>
+      </c>
+      <c r="L21" s="29" t="inlineStr">
+        <is>
+          <t>T30L-9</t>
+        </is>
       </c>
       <c r="M21" s="29" t="inlineStr">
         <is>
-          <t>COVER, ELECTRICAL CONNECTOR</t>
+          <t>TIE WRAP LONG</t>
         </is>
       </c>
       <c r="N21" s="31" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="O21" s="29" t="inlineStr">
         <is>
@@ -20481,7 +20475,7 @@
         </is>
       </c>
       <c r="Q21" s="32" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="R21" s="29" t="n">
         <v>30</v>
@@ -20498,7 +20492,7 @@
         <v/>
       </c>
       <c r="V21" s="32" t="n">
-        <v>46290</v>
+        <v>46288</v>
       </c>
       <c r="W21" s="29" t="n">
         <v/>
@@ -20526,23 +20520,23 @@
       </c>
       <c r="AC21" s="29" t="inlineStr">
         <is>
-          <t>№2334</t>
+          <t>№2318</t>
         </is>
       </c>
       <c r="AD21" s="29" t="n">
         <v/>
       </c>
       <c r="AE21" s="33" t="n">
-        <v>50</v>
+        <v>1.4</v>
       </c>
       <c r="AF21" s="33" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="AG21" s="33" t="n">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="AH21" s="33" t="n">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="AI21" s="33" t="n">
         <v>0</v>
@@ -20551,7 +20545,7 @@
         <v/>
       </c>
       <c r="AK21" s="33" t="n">
-        <v>5.15</v>
+        <v>5.768</v>
       </c>
       <c r="AL21" s="33" t="n">
         <v/>
@@ -20588,7 +20582,7 @@
         <v/>
       </c>
       <c r="AV21" s="33" t="n">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="AW21" s="29" t="n">
         <v/>
@@ -20597,10 +20591,10 @@
         <v/>
       </c>
       <c r="AY21" s="29" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="AZ21" s="34" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="BA21" s="29" t="n">
         <v/>
@@ -20612,7 +20606,7 @@
       </c>
       <c r="BC21" s="29" t="inlineStr">
         <is>
-          <t>У оманца солд. Но вроде ищет ,пока не отменяю + Дане положила на поиск. Ютэйр предупрежден</t>
+          <t>UNSOLVED, MOQ - 1000ea</t>
         </is>
       </c>
       <c r="BD21" s="29" t="n">
@@ -20648,7 +20642,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>27082616305</v>
+        <v>26082610155</v>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
@@ -20662,18 +20656,18 @@
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>KDV-3+RAP</t>
-        </is>
-      </c>
-      <c r="E22" s="40" t="inlineStr">
-        <is>
-          <t>1 NOT PAID</t>
+          <t>KDV-1</t>
+        </is>
+      </c>
+      <c r="E22" s="41" t="inlineStr">
+        <is>
+          <t>6 TROUBLE</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20426126</t>
+          <t>DAT MOW
+P20416026</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
@@ -20688,17 +20682,17 @@
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J22" s="19" t="inlineStr">
         <is>
-          <t>ATR72</t>
+          <t>B738</t>
         </is>
       </c>
       <c r="K22" s="19" t="inlineStr">
         <is>
-          <t>82425-00-0060</t>
+          <t>MS27502B19C</t>
         </is>
       </c>
       <c r="L22" s="19" t="n">
@@ -20706,12 +20700,11 @@
       </c>
       <c r="M22" s="19" t="inlineStr">
         <is>
-          <t>NAVIGATION
-PROCESSOR UNIT</t>
+          <t>COVER, ELECTRICAL CONNECTOR</t>
         </is>
       </c>
       <c r="N22" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22" s="19" t="inlineStr">
         <is>
@@ -20720,11 +20713,11 @@
       </c>
       <c r="P22" s="19" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q22" s="35" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="R22" s="19" t="n">
         <v>30</v>
@@ -20741,7 +20734,7 @@
         <v/>
       </c>
       <c r="V22" s="35" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="W22" s="19" t="n">
         <v/>
@@ -20753,54 +20746,48 @@
       </c>
       <c r="Y22" s="19" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z22" s="19" t="inlineStr">
         <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="AA22" s="19" t="inlineStr">
-        <is>
-          <t>PIONEER</t>
-        </is>
-      </c>
-      <c r="AB22" s="19" t="inlineStr">
-        <is>
-          <t>KTM409261005</t>
-        </is>
+          <t>BLUE OCEAN SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="AA22" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AB22" s="19" t="n">
+        <v/>
       </c>
       <c r="AC22" s="19" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD22" s="19" t="inlineStr">
-        <is>
-          <t>32651633</t>
-        </is>
+          <t>№2334</t>
+        </is>
+      </c>
+      <c r="AD22" s="19" t="n">
+        <v/>
       </c>
       <c r="AE22" s="21" t="n">
-        <v>38500</v>
+        <v>50</v>
       </c>
       <c r="AF22" s="21" t="n">
-        <v>38500</v>
+        <v>100</v>
       </c>
       <c r="AG22" s="21" t="n">
-        <v>48900</v>
+        <v>128</v>
       </c>
       <c r="AH22" s="21" t="n">
-        <v>48900</v>
+        <v>256</v>
       </c>
       <c r="AI22" s="21" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="AJ22" s="21" t="n">
         <v/>
       </c>
       <c r="AK22" s="21" t="n">
-        <v>1982.75</v>
+        <v>5.15</v>
       </c>
       <c r="AL22" s="21" t="n">
         <v/>
@@ -20809,17 +20796,15 @@
         <v/>
       </c>
       <c r="AN22" s="19" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO22" s="19" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP22" s="19" t="inlineStr">
-        <is>
-          <t>Получаем МПТ</t>
-        </is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP22" s="19" t="n">
+        <v/>
       </c>
       <c r="AQ22" s="19" t="inlineStr">
         <is>
@@ -20839,7 +20824,7 @@
         <v/>
       </c>
       <c r="AV22" s="21" t="n">
-        <v>48900</v>
+        <v>256</v>
       </c>
       <c r="AW22" s="19" t="n">
         <v/>
@@ -20848,19 +20833,23 @@
         <v/>
       </c>
       <c r="AY22" s="19" t="n">
-        <v>38500</v>
+        <v>100</v>
       </c>
       <c r="AZ22" s="36" t="n">
-        <v>46269</v>
+        <v>46260</v>
       </c>
       <c r="BA22" s="19" t="n">
         <v/>
       </c>
-      <c r="BB22" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BC22" s="19" t="n">
-        <v/>
+      <c r="BB22" s="19" t="inlineStr">
+        <is>
+          <t>UNSOLVED</t>
+        </is>
+      </c>
+      <c r="BC22" s="19" t="inlineStr">
+        <is>
+          <t>У оманца солд. Но вроде ищет ,пока не отменяю + Дане положила на поиск. Ютэйр предупрежден</t>
+        </is>
       </c>
       <c r="BD22" s="19" t="n">
         <v/>
@@ -20895,7 +20884,7 @@
     </row>
     <row r="23">
       <c r="A23" s="29" t="n">
-        <v>4092612345</v>
+        <v>27082616305</v>
       </c>
       <c r="B23" s="29" t="inlineStr">
         <is>
@@ -20909,7 +20898,7 @@
       </c>
       <c r="D23" s="29" t="inlineStr">
         <is>
-          <t>KDV-3</t>
+          <t>KDV-3+RAP</t>
         </is>
       </c>
       <c r="E23" s="40" t="inlineStr">
@@ -20920,7 +20909,7 @@
       <c r="F23" s="29" t="inlineStr">
         <is>
           <t>DDP MOW
-P20461626</t>
+P20426126</t>
         </is>
       </c>
       <c r="G23" s="29" t="inlineStr">
@@ -20940,22 +20929,21 @@
       </c>
       <c r="J23" s="29" t="inlineStr">
         <is>
-          <t>737ALL</t>
+          <t>ATR72</t>
         </is>
       </c>
       <c r="K23" s="29" t="inlineStr">
         <is>
-          <t>RD-AX7308-01</t>
-        </is>
-      </c>
-      <c r="L23" s="29" t="inlineStr">
-        <is>
-          <t>RDAX7308-01</t>
-        </is>
+          <t>82425-00-0060</t>
+        </is>
+      </c>
+      <c r="L23" s="29" t="n">
+        <v/>
       </c>
       <c r="M23" s="29" t="inlineStr">
         <is>
-          <t>REPRODUCER</t>
+          <t>NAVIGATION
+PROCESSOR UNIT</t>
         </is>
       </c>
       <c r="N23" s="31" t="n">
@@ -20972,13 +20960,15 @@
         </is>
       </c>
       <c r="Q23" s="32" t="n">
-        <v>46269</v>
+        <v>46261</v>
       </c>
       <c r="R23" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="S23" s="29" t="n">
-        <v>8</v>
+      <c r="S23" s="29" t="inlineStr">
+        <is>
+          <t>STK</t>
+        </is>
       </c>
       <c r="T23" s="29" t="n">
         <v/>
@@ -20987,7 +20977,7 @@
         <v/>
       </c>
       <c r="V23" s="32" t="n">
-        <v>46299</v>
+        <v>46291</v>
       </c>
       <c r="W23" s="29" t="n">
         <v/>
@@ -20999,48 +20989,54 @@
       </c>
       <c r="Y23" s="29" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="Z23" s="29" t="inlineStr">
         <is>
-          <t>LUFTHANSA</t>
-        </is>
-      </c>
-      <c r="AA23" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AB23" s="29" t="n">
-        <v/>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="AA23" s="29" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+      <c r="AB23" s="29" t="inlineStr">
+        <is>
+          <t>KTM409261005</t>
+        </is>
       </c>
       <c r="AC23" s="29" t="inlineStr">
         <is>
-          <t>#6116</t>
-        </is>
-      </c>
-      <c r="AD23" s="29" t="n">
-        <v/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD23" s="29" t="inlineStr">
+        <is>
+          <t>32651633</t>
+        </is>
       </c>
       <c r="AE23" s="33" t="n">
-        <v>1610</v>
+        <v>38500</v>
       </c>
       <c r="AF23" s="33" t="n">
-        <v>1610</v>
+        <v>38500</v>
       </c>
       <c r="AG23" s="33" t="n">
-        <v>2800</v>
+        <v>48900</v>
       </c>
       <c r="AH23" s="33" t="n">
-        <v>2800</v>
+        <v>48900</v>
       </c>
       <c r="AI23" s="33" t="n">
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="AJ23" s="33" t="n">
         <v/>
       </c>
       <c r="AK23" s="33" t="n">
-        <v>82.91500000000001</v>
+        <v>1982.75</v>
       </c>
       <c r="AL23" s="33" t="n">
         <v/>
@@ -21079,7 +21075,7 @@
         <v/>
       </c>
       <c r="AV23" s="33" t="n">
-        <v>2800</v>
+        <v>48900</v>
       </c>
       <c r="AW23" s="29" t="n">
         <v/>
@@ -21088,20 +21084,16 @@
         <v/>
       </c>
       <c r="AY23" s="29" t="n">
-        <v>1610</v>
-      </c>
-      <c r="AZ23" s="29" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
+        <v>38500</v>
+      </c>
+      <c r="AZ23" s="34" t="n">
+        <v>46269</v>
       </c>
       <c r="BA23" s="29" t="n">
         <v/>
       </c>
-      <c r="BB23" s="29" t="inlineStr">
-        <is>
-          <t>UNCONFIRMED YET</t>
-        </is>
+      <c r="BB23" s="29" t="n">
+        <v/>
       </c>
       <c r="BC23" s="29" t="n">
         <v/>
@@ -21139,7 +21131,7 @@
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>7092610195</v>
+        <v>4092612345</v>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
@@ -21164,7 +21156,7 @@
       <c r="F24" s="19" t="inlineStr">
         <is>
           <t>DDP MOW
-P20456326</t>
+P20461626</t>
         </is>
       </c>
       <c r="G24" s="19" t="inlineStr">
@@ -21184,22 +21176,22 @@
       </c>
       <c r="J24" s="19" t="inlineStr">
         <is>
-          <t>737CL</t>
+          <t>737ALL</t>
         </is>
       </c>
       <c r="K24" s="19" t="inlineStr">
         <is>
-          <t>E-329E</t>
+          <t>RD-AX7308-01</t>
         </is>
       </c>
       <c r="L24" s="19" t="inlineStr">
         <is>
-          <t>E329E</t>
+          <t>RDAX7308-01</t>
         </is>
       </c>
       <c r="M24" s="19" t="inlineStr">
         <is>
-          <t>RELAY</t>
+          <t>REPRODUCER</t>
         </is>
       </c>
       <c r="N24" s="20" t="n">
@@ -21216,13 +21208,13 @@
         </is>
       </c>
       <c r="Q24" s="35" t="n">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="R24" s="19" t="n">
         <v>30</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T24" s="19" t="n">
         <v/>
@@ -21231,7 +21223,7 @@
         <v/>
       </c>
       <c r="V24" s="35" t="n">
-        <v>46302</v>
+        <v>46299</v>
       </c>
       <c r="W24" s="19" t="n">
         <v/>
@@ -21259,32 +21251,32 @@
       </c>
       <c r="AC24" s="19" t="inlineStr">
         <is>
-          <t>#6122</t>
+          <t>#6116</t>
         </is>
       </c>
       <c r="AD24" s="19" t="n">
         <v/>
       </c>
       <c r="AE24" s="21" t="n">
-        <v>1500</v>
+        <v>1610</v>
       </c>
       <c r="AF24" s="21" t="n">
-        <v>1500</v>
+        <v>1610</v>
       </c>
       <c r="AG24" s="21" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="AH24" s="21" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="AI24" s="21" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AJ24" s="21" t="n">
         <v/>
       </c>
       <c r="AK24" s="21" t="n">
-        <v>77.25</v>
+        <v>82.91500000000001</v>
       </c>
       <c r="AL24" s="21" t="n">
         <v/>
@@ -21323,7 +21315,7 @@
         <v/>
       </c>
       <c r="AV24" s="21" t="n">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="AW24" s="19" t="n">
         <v/>
@@ -21332,7 +21324,7 @@
         <v/>
       </c>
       <c r="AY24" s="19" t="n">
-        <v>1500</v>
+        <v>1610</v>
       </c>
       <c r="AZ24" s="19" t="inlineStr">
         <is>
@@ -21383,7 +21375,7 @@
     </row>
     <row r="25">
       <c r="A25" s="29" t="n">
-        <v>9092611085</v>
+        <v>7092610195</v>
       </c>
       <c r="B25" s="29" t="inlineStr">
         <is>
@@ -21408,7 +21400,7 @@
       <c r="F25" s="29" t="inlineStr">
         <is>
           <t>DDP MOW
-P20478226</t>
+P20456326</t>
         </is>
       </c>
       <c r="G25" s="29" t="inlineStr">
@@ -21428,22 +21420,22 @@
       </c>
       <c r="J25" s="29" t="inlineStr">
         <is>
-          <t>737ALL</t>
+          <t>737CL</t>
         </is>
       </c>
       <c r="K25" s="29" t="inlineStr">
         <is>
-          <t>CGAB1400-00</t>
+          <t>E-329E</t>
         </is>
       </c>
       <c r="L25" s="29" t="inlineStr">
         <is>
-          <t>CGAB1400-01</t>
+          <t>E329E</t>
         </is>
       </c>
       <c r="M25" s="29" t="inlineStr">
         <is>
-          <t>SMOKE DETECTOR</t>
+          <t>RELAY</t>
         </is>
       </c>
       <c r="N25" s="31" t="n">
@@ -21460,13 +21452,13 @@
         </is>
       </c>
       <c r="Q25" s="32" t="n">
-        <v>46274</v>
+        <v>46272</v>
       </c>
       <c r="R25" s="29" t="n">
         <v>30</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T25" s="29" t="n">
         <v/>
@@ -21475,7 +21467,7 @@
         <v/>
       </c>
       <c r="V25" s="32" t="n">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="W25" s="29" t="n">
         <v/>
@@ -21503,23 +21495,23 @@
       </c>
       <c r="AC25" s="29" t="inlineStr">
         <is>
-          <t>#6133</t>
+          <t>#6122</t>
         </is>
       </c>
       <c r="AD25" s="29" t="n">
         <v/>
       </c>
       <c r="AE25" s="33" t="n">
-        <v>1610</v>
+        <v>1500</v>
       </c>
       <c r="AF25" s="33" t="n">
-        <v>1610</v>
+        <v>1500</v>
       </c>
       <c r="AG25" s="33" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="AH25" s="33" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="AI25" s="33" t="n">
         <v>150</v>
@@ -21528,7 +21520,7 @@
         <v/>
       </c>
       <c r="AK25" s="33" t="n">
-        <v>80.7415</v>
+        <v>77.25</v>
       </c>
       <c r="AL25" s="33" t="n">
         <v/>
@@ -21567,7 +21559,7 @@
         <v/>
       </c>
       <c r="AV25" s="33" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="AW25" s="29" t="n">
         <v/>
@@ -21576,7 +21568,7 @@
         <v/>
       </c>
       <c r="AY25" s="29" t="n">
-        <v>1610</v>
+        <v>1500</v>
       </c>
       <c r="AZ25" s="29" t="inlineStr">
         <is>
@@ -21627,7 +21619,7 @@
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>10092610465</v>
+        <v>9092611085</v>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
@@ -21652,7 +21644,7 @@
       <c r="F26" s="19" t="inlineStr">
         <is>
           <t>DDP MOW
-P20486326</t>
+P20478226</t>
         </is>
       </c>
       <c r="G26" s="19" t="inlineStr">
@@ -21672,20 +21664,22 @@
       </c>
       <c r="J26" s="19" t="inlineStr">
         <is>
-          <t>ATR72</t>
+          <t>737ALL</t>
         </is>
       </c>
       <c r="K26" s="19" t="inlineStr">
         <is>
-          <t>301-2640</t>
-        </is>
-      </c>
-      <c r="L26" s="19" t="n">
-        <v/>
+          <t>CGAB1400-00</t>
+        </is>
+      </c>
+      <c r="L26" s="19" t="inlineStr">
+        <is>
+          <t>CGAB1400-01</t>
+        </is>
       </c>
       <c r="M26" s="19" t="inlineStr">
         <is>
-          <t>ATTENDANT PANEL</t>
+          <t>SMOKE DETECTOR</t>
         </is>
       </c>
       <c r="N26" s="20" t="n">
@@ -21702,13 +21696,13 @@
         </is>
       </c>
       <c r="Q26" s="35" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="R26" s="19" t="n">
         <v>30</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T26" s="19" t="n">
         <v/>
@@ -21717,7 +21711,7 @@
         <v/>
       </c>
       <c r="V26" s="35" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="W26" s="19" t="n">
         <v/>
@@ -21729,52 +21723,48 @@
       </c>
       <c r="Y26" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="Z26" s="19" t="inlineStr">
         <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="AA26" s="19" t="inlineStr">
-        <is>
-          <t>ALOIA AEROSPACE</t>
-        </is>
-      </c>
-      <c r="AB26" s="19" t="inlineStr">
-        <is>
-          <t>KTM1009261616</t>
-        </is>
+          <t>LUFTHANSA</t>
+        </is>
+      </c>
+      <c r="AA26" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AB26" s="19" t="n">
+        <v/>
       </c>
       <c r="AC26" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>#6133</t>
         </is>
       </c>
       <c r="AD26" s="19" t="n">
         <v/>
       </c>
       <c r="AE26" s="21" t="n">
-        <v>11500</v>
+        <v>1610</v>
       </c>
       <c r="AF26" s="21" t="n">
-        <v>11500</v>
+        <v>1610</v>
       </c>
       <c r="AG26" s="21" t="n">
-        <v>18900</v>
+        <v>2500</v>
       </c>
       <c r="AH26" s="21" t="n">
-        <v>18900</v>
+        <v>2500</v>
       </c>
       <c r="AI26" s="21" t="n">
-        <v>2000</v>
+        <v>150</v>
       </c>
       <c r="AJ26" s="21" t="n">
         <v/>
       </c>
       <c r="AK26" s="21" t="n">
-        <v>576.725</v>
+        <v>80.7415</v>
       </c>
       <c r="AL26" s="21" t="n">
         <v/>
@@ -21813,25 +21803,29 @@
         <v/>
       </c>
       <c r="AV26" s="21" t="n">
-        <v>18900</v>
-      </c>
-      <c r="AW26" s="36" t="n">
-        <v>46289</v>
+        <v>2500</v>
+      </c>
+      <c r="AW26" s="19" t="n">
+        <v/>
       </c>
       <c r="AX26" s="19" t="n">
-        <v>11500</v>
+        <v/>
       </c>
       <c r="AY26" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" s="36" t="n">
-        <v>46275</v>
+        <v>1610</v>
+      </c>
+      <c r="AZ26" s="19" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
       </c>
       <c r="BA26" s="19" t="n">
         <v/>
       </c>
-      <c r="BB26" s="19" t="n">
-        <v/>
+      <c r="BB26" s="19" t="inlineStr">
+        <is>
+          <t>UNCONFIRMED YET</t>
+        </is>
       </c>
       <c r="BC26" s="19" t="n">
         <v/>
@@ -21869,7 +21863,7 @@
     </row>
     <row r="27">
       <c r="A27" s="29" t="n">
-        <v>11092612015</v>
+        <v>10092610465</v>
       </c>
       <c r="B27" s="29" t="inlineStr">
         <is>
@@ -21893,8 +21887,8 @@
       </c>
       <c r="F27" s="29" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20479926</t>
+          <t>DDP MOW
+P20486326</t>
         </is>
       </c>
       <c r="G27" s="29" t="inlineStr">
@@ -21914,12 +21908,12 @@
       </c>
       <c r="J27" s="29" t="inlineStr">
         <is>
-          <t>B737CL</t>
+          <t>ATR72</t>
         </is>
       </c>
       <c r="K27" s="29" t="inlineStr">
         <is>
-          <t>0851CM-2</t>
+          <t>301-2640</t>
         </is>
       </c>
       <c r="L27" s="29" t="n">
@@ -21927,7 +21921,7 @@
       </c>
       <c r="M27" s="29" t="inlineStr">
         <is>
-          <t>ELEVATOR PITOT PROBE</t>
+          <t>ATTENDANT PANEL</t>
         </is>
       </c>
       <c r="N27" s="31" t="n">
@@ -21944,15 +21938,13 @@
         </is>
       </c>
       <c r="Q27" s="32" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="R27" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="S27" s="29" t="inlineStr">
-        <is>
-          <t>7-12 дней</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>13</v>
       </c>
       <c r="T27" s="29" t="n">
         <v/>
@@ -21961,7 +21953,7 @@
         <v/>
       </c>
       <c r="V27" s="32" t="n">
-        <v>46318</v>
+        <v>46305</v>
       </c>
       <c r="W27" s="29" t="n">
         <v/>
@@ -21973,7 +21965,7 @@
       </c>
       <c r="Y27" s="29" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z27" s="29" t="inlineStr">
@@ -21983,12 +21975,12 @@
       </c>
       <c r="AA27" s="29" t="inlineStr">
         <is>
-          <t>GENERAL AIRFRAME SUPPORT</t>
+          <t>ALOIA AEROSPACE</t>
         </is>
       </c>
       <c r="AB27" s="29" t="inlineStr">
         <is>
-          <t>KTM1109261552</t>
+          <t>KTM1009261616</t>
         </is>
       </c>
       <c r="AC27" s="29" t="inlineStr">
@@ -22000,25 +21992,25 @@
         <v/>
       </c>
       <c r="AE27" s="33" t="n">
-        <v>3895</v>
+        <v>11500</v>
       </c>
       <c r="AF27" s="33" t="n">
-        <v>3895</v>
+        <v>11500</v>
       </c>
       <c r="AG27" s="33" t="n">
-        <v>8500</v>
+        <v>18900</v>
       </c>
       <c r="AH27" s="33" t="n">
-        <v>8500</v>
+        <v>18900</v>
       </c>
       <c r="AI27" s="33" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="AJ27" s="33" t="n">
         <v/>
       </c>
       <c r="AK27" s="33" t="n">
-        <v>195.33425</v>
+        <v>576.725</v>
       </c>
       <c r="AL27" s="33" t="n">
         <v/>
@@ -22031,17 +22023,17 @@
       </c>
       <c r="AO27" s="29" t="inlineStr">
         <is>
-          <t>ЕСТЬ МПТ на Самолеты типа Boeing 737</t>
+          <t>НЕТ МПТ</t>
         </is>
       </c>
       <c r="AP27" s="29" t="inlineStr">
         <is>
-          <t>Есть МПТ</t>
+          <t>Получаем МПТ</t>
         </is>
       </c>
       <c r="AQ27" s="29" t="inlineStr">
         <is>
-          <t>Частичная предоплата</t>
+          <t>Постоплата 100%</t>
         </is>
       </c>
       <c r="AR27" s="29" t="n">
@@ -22057,19 +22049,19 @@
         <v/>
       </c>
       <c r="AV27" s="33" t="n">
-        <v>8500</v>
-      </c>
-      <c r="AW27" s="29" t="n">
-        <v/>
+        <v>18900</v>
+      </c>
+      <c r="AW27" s="34" t="n">
+        <v>46289</v>
       </c>
       <c r="AX27" s="29" t="n">
-        <v/>
+        <v>11500</v>
       </c>
       <c r="AY27" s="29" t="n">
-        <v>3895</v>
+        <v>0</v>
       </c>
       <c r="AZ27" s="34" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="BA27" s="29" t="n">
         <v/>
@@ -22113,7 +22105,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>11092613005</v>
+        <v>11092612015</v>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
@@ -22130,15 +22122,15 @@
           <t>KDV-3</t>
         </is>
       </c>
-      <c r="E28" s="39" t="inlineStr">
-        <is>
-          <t>2 PAID</t>
+      <c r="E28" s="40" t="inlineStr">
+        <is>
+          <t>1 NOT PAID</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20501426</t>
+          <t>DAT MOW
+P20479926</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
@@ -22163,7 +22155,7 @@
       </c>
       <c r="K28" s="19" t="inlineStr">
         <is>
-          <t>3604524-54</t>
+          <t>0851CM-2</t>
         </is>
       </c>
       <c r="L28" s="19" t="n">
@@ -22171,12 +22163,11 @@
       </c>
       <c r="M28" s="19" t="inlineStr">
         <is>
-          <t>COMBUSTOR UNIT
-ASSY</t>
+          <t>ELEVATOR PITOT PROBE</t>
         </is>
       </c>
       <c r="N28" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O28" s="19" t="inlineStr">
         <is>
@@ -22192,11 +22183,11 @@
         <v>46276</v>
       </c>
       <c r="R28" s="19" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="S28" s="19" t="inlineStr">
         <is>
-          <t>STK</t>
+          <t>7-12 дней</t>
         </is>
       </c>
       <c r="T28" s="19" t="n">
@@ -22206,7 +22197,7 @@
         <v/>
       </c>
       <c r="V28" s="35" t="n">
-        <v>46301</v>
+        <v>46318</v>
       </c>
       <c r="W28" s="19" t="n">
         <v/>
@@ -22218,7 +22209,7 @@
       </c>
       <c r="Y28" s="19" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="Z28" s="19" t="inlineStr">
@@ -22228,12 +22219,12 @@
       </c>
       <c r="AA28" s="19" t="inlineStr">
         <is>
-          <t>SETNA IO</t>
+          <t>GENERAL AIRFRAME SUPPORT</t>
         </is>
       </c>
       <c r="AB28" s="19" t="inlineStr">
         <is>
-          <t>KTM1109261011</t>
+          <t>KTM1109261552</t>
         </is>
       </c>
       <c r="AC28" s="19" t="inlineStr">
@@ -22245,25 +22236,25 @@
         <v/>
       </c>
       <c r="AE28" s="21" t="n">
-        <v>5000</v>
+        <v>3895</v>
       </c>
       <c r="AF28" s="21" t="n">
-        <v>15000</v>
+        <v>3895</v>
       </c>
       <c r="AG28" s="21" t="n">
-        <v>9100</v>
+        <v>8500</v>
       </c>
       <c r="AH28" s="21" t="n">
-        <v>27300</v>
+        <v>8500</v>
       </c>
       <c r="AI28" s="21" t="n">
-        <v>3900</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" s="21" t="n">
         <v/>
       </c>
       <c r="AK28" s="21" t="n">
-        <v>752.25</v>
+        <v>195.33425</v>
       </c>
       <c r="AL28" s="21" t="n">
         <v/>
@@ -22276,7 +22267,7 @@
       </c>
       <c r="AO28" s="19" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
+          <t>ЕСТЬ МПТ на Самолеты типа Boeing 737</t>
         </is>
       </c>
       <c r="AP28" s="19" t="inlineStr">
@@ -22302,16 +22293,16 @@
         <v/>
       </c>
       <c r="AV28" s="21" t="n">
-        <v>27300</v>
-      </c>
-      <c r="AW28" s="36" t="n">
-        <v>46289</v>
+        <v>8500</v>
+      </c>
+      <c r="AW28" s="19" t="n">
+        <v/>
       </c>
       <c r="AX28" s="19" t="n">
-        <v>15000</v>
+        <v/>
       </c>
       <c r="AY28" s="19" t="n">
-        <v>0</v>
+        <v>3895</v>
       </c>
       <c r="AZ28" s="36" t="n">
         <v>46276</v>
@@ -22358,7 +22349,7 @@
     </row>
     <row r="29">
       <c r="A29" s="29" t="n">
-        <v>1109269415</v>
+        <v>11092613005</v>
       </c>
       <c r="B29" s="29" t="inlineStr">
         <is>
@@ -22372,18 +22363,18 @@
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
-          <t>KDV-1</t>
-        </is>
-      </c>
-      <c r="E29" s="40" t="inlineStr">
-        <is>
-          <t>1 NOT PAID</t>
+          <t>KDV-3</t>
+        </is>
+      </c>
+      <c r="E29" s="39" t="inlineStr">
+        <is>
+          <t>2 PAID</t>
         </is>
       </c>
       <c r="F29" s="29" t="inlineStr">
         <is>
           <t>DDP MOW
-P20497326</t>
+P20501426</t>
         </is>
       </c>
       <c r="G29" s="29" t="inlineStr">
@@ -22398,17 +22389,17 @@
       </c>
       <c r="I29" s="29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J29" s="29" t="inlineStr">
         <is>
-          <t>737CL</t>
+          <t>B737CL</t>
         </is>
       </c>
       <c r="K29" s="29" t="inlineStr">
         <is>
-          <t>1002992-309</t>
+          <t>3604524-54</t>
         </is>
       </c>
       <c r="L29" s="29" t="n">
@@ -22416,11 +22407,12 @@
       </c>
       <c r="M29" s="29" t="inlineStr">
         <is>
-          <t>PIVOT COVER</t>
+          <t>COMBUSTOR UNIT
+ASSY</t>
         </is>
       </c>
       <c r="N29" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O29" s="29" t="inlineStr">
         <is>
@@ -22429,14 +22421,14 @@
       </c>
       <c r="P29" s="29" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q29" s="32" t="n">
         <v>46276</v>
       </c>
       <c r="R29" s="29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="S29" s="29" t="inlineStr">
         <is>
@@ -22446,13 +22438,11 @@
       <c r="T29" s="29" t="n">
         <v/>
       </c>
-      <c r="U29" s="29" t="inlineStr">
-        <is>
-          <t>PRIORITY NET</t>
-        </is>
+      <c r="U29" s="29" t="n">
+        <v/>
       </c>
       <c r="V29" s="32" t="n">
-        <v>46306</v>
+        <v>46301</v>
       </c>
       <c r="W29" s="29" t="n">
         <v/>
@@ -22464,50 +22454,52 @@
       </c>
       <c r="Y29" s="29" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z29" s="29" t="inlineStr">
         <is>
-          <t>LUFTHANSA</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="AA29" s="29" t="inlineStr">
         <is>
-          <t>SATAIR</t>
-        </is>
-      </c>
-      <c r="AB29" s="29" t="n">
-        <v/>
+          <t>SETNA IO</t>
+        </is>
+      </c>
+      <c r="AB29" s="29" t="inlineStr">
+        <is>
+          <t>KTM1109261011</t>
+        </is>
       </c>
       <c r="AC29" s="29" t="inlineStr">
         <is>
-          <t>#6148</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AD29" s="29" t="n">
         <v/>
       </c>
       <c r="AE29" s="33" t="n">
-        <v>99</v>
+        <v>5000</v>
       </c>
       <c r="AF29" s="33" t="n">
-        <v>198</v>
+        <v>15000</v>
       </c>
       <c r="AG29" s="33" t="n">
-        <v>185</v>
+        <v>9100</v>
       </c>
       <c r="AH29" s="33" t="n">
-        <v>370</v>
+        <v>27300</v>
       </c>
       <c r="AI29" s="33" t="n">
-        <v>50</v>
+        <v>3900</v>
       </c>
       <c r="AJ29" s="33" t="n">
         <v/>
       </c>
       <c r="AK29" s="33" t="n">
-        <v>9.9297</v>
+        <v>752.25</v>
       </c>
       <c r="AL29" s="33" t="n">
         <v/>
@@ -22516,19 +22508,21 @@
         <v/>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AO29" s="29" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP29" s="29" t="n">
-        <v/>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP29" s="29" t="inlineStr">
+        <is>
+          <t>Есть МПТ</t>
+        </is>
       </c>
       <c r="AQ29" s="29" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
+          <t>Частичная предоплата</t>
         </is>
       </c>
       <c r="AR29" s="29" t="n">
@@ -22544,16 +22538,16 @@
         <v/>
       </c>
       <c r="AV29" s="33" t="n">
-        <v>370</v>
-      </c>
-      <c r="AW29" s="29" t="n">
-        <v/>
+        <v>27300</v>
+      </c>
+      <c r="AW29" s="34" t="n">
+        <v>46289</v>
       </c>
       <c r="AX29" s="29" t="n">
-        <v/>
+        <v>15000</v>
       </c>
       <c r="AY29" s="29" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="AZ29" s="34" t="n">
         <v>46276</v>
@@ -22561,10 +22555,8 @@
       <c r="BA29" s="29" t="n">
         <v/>
       </c>
-      <c r="BB29" s="29" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
+      <c r="BB29" s="29" t="n">
+        <v/>
       </c>
       <c r="BC29" s="29" t="n">
         <v/>
@@ -22602,7 +22594,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>1109269585</v>
+        <v>1109269415</v>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
@@ -22627,7 +22619,7 @@
       <c r="F30" s="19" t="inlineStr">
         <is>
           <t>DDP MOW
-P20498826</t>
+P20497326</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
@@ -22647,12 +22639,12 @@
       </c>
       <c r="J30" s="19" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>737CL</t>
         </is>
       </c>
       <c r="K30" s="19" t="inlineStr">
         <is>
-          <t>BACR15BA2AD5C</t>
+          <t>1002992-309</t>
         </is>
       </c>
       <c r="L30" s="19" t="n">
@@ -22660,11 +22652,11 @@
       </c>
       <c r="M30" s="19" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>PIVOT COVER</t>
         </is>
       </c>
       <c r="N30" s="20" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="O30" s="19" t="inlineStr">
         <is>
@@ -22680,7 +22672,7 @@
         <v>46276</v>
       </c>
       <c r="R30" s="19" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S30" s="19" t="inlineStr">
         <is>
@@ -22690,11 +22682,13 @@
       <c r="T30" s="19" t="n">
         <v/>
       </c>
-      <c r="U30" s="19" t="n">
-        <v/>
+      <c r="U30" s="19" t="inlineStr">
+        <is>
+          <t>PRIORITY NET</t>
+        </is>
       </c>
       <c r="V30" s="35" t="n">
-        <v>46311</v>
+        <v>46306</v>
       </c>
       <c r="W30" s="19" t="n">
         <v/>
@@ -22711,43 +22705,45 @@
       </c>
       <c r="Z30" s="19" t="inlineStr">
         <is>
-          <t>BLUE OCEAN SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="AA30" s="19" t="n">
-        <v/>
+          <t>LUFTHANSA</t>
+        </is>
+      </c>
+      <c r="AA30" s="19" t="inlineStr">
+        <is>
+          <t>SATAIR</t>
+        </is>
       </c>
       <c r="AB30" s="19" t="n">
         <v/>
       </c>
       <c r="AC30" s="19" t="inlineStr">
         <is>
-          <t>№2373</t>
+          <t>#6148</t>
         </is>
       </c>
       <c r="AD30" s="19" t="n">
         <v/>
       </c>
       <c r="AE30" s="21" t="n">
-        <v>1.6</v>
+        <v>99</v>
       </c>
       <c r="AF30" s="21" t="n">
-        <v>102.4</v>
+        <v>198</v>
       </c>
       <c r="AG30" s="21" t="n">
-        <v>5</v>
+        <v>185</v>
       </c>
       <c r="AH30" s="21" t="n">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="AI30" s="21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ30" s="21" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AK30" s="21" t="n">
-        <v>5.2736</v>
+        <v>9.9297</v>
       </c>
       <c r="AL30" s="21" t="n">
         <v/>
@@ -22784,7 +22780,7 @@
         <v/>
       </c>
       <c r="AV30" s="21" t="n">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="AW30" s="19" t="n">
         <v/>
@@ -22793,7 +22789,7 @@
         <v/>
       </c>
       <c r="AY30" s="19" t="n">
-        <v>102.4</v>
+        <v>198</v>
       </c>
       <c r="AZ30" s="36" t="n">
         <v>46276</v>
@@ -22803,24 +22799,20 @@
       </c>
       <c r="BB30" s="19" t="inlineStr">
         <is>
-          <t>BOS WHS</t>
-        </is>
-      </c>
-      <c r="BC30" s="19" t="inlineStr">
-        <is>
-          <t>до 21.10</t>
-        </is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="BC30" s="19" t="n">
+        <v/>
       </c>
       <c r="BD30" s="19" t="n">
         <v/>
       </c>
       <c r="BE30" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF30" s="19" t="inlineStr">
-        <is>
-          <t>Ф</t>
-        </is>
+        <v/>
+      </c>
+      <c r="BF30" s="19" t="n">
+        <v/>
       </c>
       <c r="BG30" s="19" t="n">
         <v/>
@@ -22832,13 +22824,13 @@
         <v/>
       </c>
       <c r="BJ30" s="19" t="n">
-        <v>30092026</v>
+        <v/>
       </c>
       <c r="BK30" s="19" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="BL30" s="19" t="n">
-        <v>102.4</v>
+        <v/>
       </c>
       <c r="BM30" s="19" t="n">
         <v/>
@@ -22846,7 +22838,7 @@
     </row>
     <row r="31">
       <c r="A31" s="29" t="n">
-        <v>16092610575</v>
+        <v>1109269585</v>
       </c>
       <c r="B31" s="29" t="inlineStr">
         <is>
@@ -22860,7 +22852,7 @@
       </c>
       <c r="D31" s="29" t="inlineStr">
         <is>
-          <t>KDV-3</t>
+          <t>KDV-1</t>
         </is>
       </c>
       <c r="E31" s="40" t="inlineStr">
@@ -22870,8 +22862,8 @@
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20515326</t>
+          <t>DDP MOW
+P20498826</t>
         </is>
       </c>
       <c r="G31" s="29" t="inlineStr">
@@ -22886,17 +22878,17 @@
       </c>
       <c r="I31" s="29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J31" s="29" t="inlineStr">
         <is>
-          <t>737CL</t>
+          <t>B738</t>
         </is>
       </c>
       <c r="K31" s="29" t="inlineStr">
         <is>
-          <t>65C27506-3</t>
+          <t>BACR15BA2AD5C</t>
         </is>
       </c>
       <c r="L31" s="29" t="n">
@@ -22904,11 +22896,11 @@
       </c>
       <c r="M31" s="29" t="inlineStr">
         <is>
-          <t>TRANSMISSION ASSY, RH, #6</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="N31" s="31" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="O31" s="29" t="inlineStr">
         <is>
@@ -22917,14 +22909,14 @@
       </c>
       <c r="P31" s="29" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q31" s="32" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="R31" s="29" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S31" s="29" t="inlineStr">
         <is>
@@ -22950,12 +22942,12 @@
       </c>
       <c r="Y31" s="29" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z31" s="29" t="inlineStr">
         <is>
-          <t>LUFTHANSA</t>
+          <t>BLUE OCEAN SOLUTIONS</t>
         </is>
       </c>
       <c r="AA31" s="29" t="n">
@@ -22966,32 +22958,32 @@
       </c>
       <c r="AC31" s="29" t="inlineStr">
         <is>
-          <t>#6187</t>
+          <t>№2373</t>
         </is>
       </c>
       <c r="AD31" s="29" t="n">
         <v/>
       </c>
       <c r="AE31" s="33" t="n">
-        <v>4030</v>
+        <v>1.6</v>
       </c>
       <c r="AF31" s="33" t="n">
-        <v>4030</v>
+        <v>102.4</v>
       </c>
       <c r="AG31" s="33" t="n">
-        <v>5700</v>
+        <v>5</v>
       </c>
       <c r="AH31" s="33" t="n">
-        <v>5700</v>
+        <v>320</v>
       </c>
       <c r="AI31" s="33" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AJ31" s="33" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK31" s="33" t="n">
-        <v>202.1045</v>
+        <v>5.2736</v>
       </c>
       <c r="AL31" s="33" t="n">
         <v/>
@@ -23000,87 +22992,89 @@
         <v/>
       </c>
       <c r="AN31" s="29" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AO31" s="29" t="inlineStr">
+        <is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP31" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AQ31" s="29" t="inlineStr">
+        <is>
+          <t>Постоплата 100%</t>
+        </is>
+      </c>
+      <c r="AR31" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AS31" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AT31" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AU31" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AV31" s="33" t="n">
+        <v>320</v>
+      </c>
+      <c r="AW31" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AX31" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AY31" s="29" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="AZ31" s="34" t="n">
+        <v>46276</v>
+      </c>
+      <c r="BA31" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BB31" s="29" t="inlineStr">
+        <is>
+          <t>BOS WHS</t>
+        </is>
+      </c>
+      <c r="BC31" s="29" t="inlineStr">
+        <is>
+          <t>до 21.10</t>
+        </is>
+      </c>
+      <c r="BD31" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BE31" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF31" s="29" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
+      <c r="BG31" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BH31" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BI31" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BJ31" s="29" t="n">
+        <v>30092026</v>
+      </c>
+      <c r="BK31" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AO31" s="29" t="inlineStr">
-        <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AQ31" s="29" t="inlineStr">
-        <is>
-          <t>Постоплата 100%</t>
-        </is>
-      </c>
-      <c r="AR31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AS31" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AT31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AU31" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AV31" s="33" t="n">
-        <v>5700</v>
-      </c>
-      <c r="AW31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AX31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AY31" s="29" t="n">
-        <v>4030</v>
-      </c>
-      <c r="AZ31" s="29" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="BA31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BB31" s="29" t="inlineStr">
-        <is>
-          <t>UNCONFIRMED YET</t>
-        </is>
-      </c>
-      <c r="BC31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BD31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BE31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BF31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BG31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BH31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BI31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BJ31" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BK31" s="29" t="n">
-        <v/>
-      </c>
       <c r="BL31" s="29" t="n">
-        <v/>
+        <v>102.4</v>
       </c>
       <c r="BM31" s="29" t="n">
         <v/>
@@ -23088,332 +23082,322 @@
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
+        <v>16092610575</v>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>М</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>Ray</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>KDV-3</t>
+        </is>
+      </c>
+      <c r="E32" s="40" t="inlineStr">
+        <is>
+          <t>1 NOT PAID</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>DAT MOW
+P20515326</t>
+        </is>
+      </c>
+      <c r="G32" s="19" t="inlineStr">
+        <is>
+          <t>Utair</t>
+        </is>
+      </c>
+      <c r="H32" s="19" t="inlineStr">
+        <is>
+          <t>комм</t>
+        </is>
+      </c>
+      <c r="I32" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>737CL</t>
+        </is>
+      </c>
+      <c r="K32" s="19" t="inlineStr">
+        <is>
+          <t>65C27506-3</t>
+        </is>
+      </c>
+      <c r="L32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="M32" s="19" t="inlineStr">
+        <is>
+          <t>TRANSMISSION ASSY, RH, #6</t>
+        </is>
+      </c>
+      <c r="N32" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="19" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="P32" s="19" t="inlineStr">
+        <is>
+          <t>ROTABLE</t>
+        </is>
+      </c>
+      <c r="Q32" s="35" t="n">
+        <v>46281</v>
+      </c>
+      <c r="R32" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="S32" s="19" t="inlineStr">
+        <is>
+          <t>STK</t>
+        </is>
+      </c>
+      <c r="T32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="35" t="n">
+        <v>46311</v>
+      </c>
+      <c r="W32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="X32" s="19" t="inlineStr">
+        <is>
+          <t>Продажа от поставщика</t>
+        </is>
+      </c>
+      <c r="Y32" s="19" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="Z32" s="19" t="inlineStr">
+        <is>
+          <t>LUFTHANSA</t>
+        </is>
+      </c>
+      <c r="AA32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AB32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AC32" s="19" t="inlineStr">
+        <is>
+          <t>#6187</t>
+        </is>
+      </c>
+      <c r="AD32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AE32" s="21" t="n">
+        <v>4030</v>
+      </c>
+      <c r="AF32" s="21" t="n">
+        <v>4030</v>
+      </c>
+      <c r="AG32" s="21" t="n">
+        <v>5700</v>
+      </c>
+      <c r="AH32" s="21" t="n">
+        <v>5700</v>
+      </c>
+      <c r="AI32" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="AJ32" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AK32" s="21" t="n">
+        <v>202.1045</v>
+      </c>
+      <c r="AL32" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AM32" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AN32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="19" t="inlineStr">
+        <is>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AQ32" s="19" t="inlineStr">
+        <is>
+          <t>Постоплата 100%</t>
+        </is>
+      </c>
+      <c r="AR32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AS32" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AT32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AU32" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AV32" s="21" t="n">
+        <v>5700</v>
+      </c>
+      <c r="AW32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AX32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AY32" s="19" t="n">
+        <v>4030</v>
+      </c>
+      <c r="AZ32" s="19" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="BA32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BB32" s="19" t="inlineStr">
+        <is>
+          <t>UNCONFIRMED YET</t>
+        </is>
+      </c>
+      <c r="BC32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BD32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BE32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BF32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BG32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BH32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BI32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BJ32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BK32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BL32" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BM32" s="19" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="n">
         <v>16092612555</v>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>М</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="C33" s="29" t="inlineStr">
         <is>
           <t>Ray</t>
         </is>
       </c>
-      <c r="D32" s="19" t="inlineStr">
+      <c r="D33" s="29" t="inlineStr">
         <is>
           <t>KDV-3</t>
         </is>
       </c>
-      <c r="E32" s="40" t="inlineStr">
+      <c r="E33" s="40" t="inlineStr">
         <is>
           <t>1 NOT PAID</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F33" s="29" t="inlineStr">
         <is>
           <t>DDP MOW
 P20518126</t>
         </is>
       </c>
-      <c r="G32" s="19" t="inlineStr">
+      <c r="G33" s="29" t="inlineStr">
         <is>
           <t>Utair</t>
         </is>
       </c>
-      <c r="H32" s="19" t="inlineStr">
+      <c r="H33" s="29" t="inlineStr">
         <is>
           <t>комм</t>
         </is>
       </c>
-      <c r="I32" s="19" t="inlineStr">
+      <c r="I33" s="29" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J32" s="19" t="inlineStr">
+      <c r="J33" s="29" t="inlineStr">
         <is>
           <t>B738</t>
         </is>
       </c>
-      <c r="K32" s="19" t="inlineStr">
+      <c r="K33" s="29" t="inlineStr">
         <is>
           <t>901950-02</t>
         </is>
       </c>
-      <c r="L32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="M32" s="19" t="inlineStr">
+      <c r="L33" s="29" t="n">
+        <v/>
+      </c>
+      <c r="M33" s="29" t="inlineStr">
         <is>
           <t>FIRE &amp; OVERHEAT
 DETECTION CTR
 UNIT</t>
         </is>
       </c>
-      <c r="N32" s="20" t="n">
+      <c r="N33" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="O32" s="19" t="inlineStr">
+      <c r="O33" s="29" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="P32" s="19" t="inlineStr">
+      <c r="P33" s="29" t="inlineStr">
         <is>
           <t>ROTABLE</t>
-        </is>
-      </c>
-      <c r="Q32" s="35" t="n">
-        <v>46281</v>
-      </c>
-      <c r="R32" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="S32" s="19" t="inlineStr">
-        <is>
-          <t>STK</t>
-        </is>
-      </c>
-      <c r="T32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="35" t="n">
-        <v>46311</v>
-      </c>
-      <c r="W32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="X32" s="19" t="inlineStr">
-        <is>
-          <t>Продажа от поставщика</t>
-        </is>
-      </c>
-      <c r="Y32" s="19" t="inlineStr">
-        <is>
-          <t>RP</t>
-        </is>
-      </c>
-      <c r="Z32" s="19" t="inlineStr">
-        <is>
-          <t>LUFTHANSA</t>
-        </is>
-      </c>
-      <c r="AA32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AB32" s="19" t="inlineStr">
-        <is>
-          <t>JP230926-1</t>
-        </is>
-      </c>
-      <c r="AC32" s="19" t="inlineStr">
-        <is>
-          <t>#6188</t>
-        </is>
-      </c>
-      <c r="AD32" s="19" t="inlineStr">
-        <is>
-          <t>2859</t>
-        </is>
-      </c>
-      <c r="AE32" s="21" t="n">
-        <v>2710</v>
-      </c>
-      <c r="AF32" s="21" t="n">
-        <v>2710</v>
-      </c>
-      <c r="AG32" s="21" t="n">
-        <v>4000</v>
-      </c>
-      <c r="AH32" s="21" t="n">
-        <v>4000</v>
-      </c>
-      <c r="AI32" s="21" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ32" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AK32" s="21" t="n">
-        <v>135.9065</v>
-      </c>
-      <c r="AL32" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AM32" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AN32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" s="19" t="inlineStr">
-        <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP32" s="19" t="inlineStr">
-        <is>
-          <t>Есть МПТ</t>
-        </is>
-      </c>
-      <c r="AQ32" s="19" t="inlineStr">
-        <is>
-          <t>Постоплата 100%</t>
-        </is>
-      </c>
-      <c r="AR32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AS32" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AT32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AU32" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AV32" s="21" t="n">
-        <v>4000</v>
-      </c>
-      <c r="AW32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AX32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AY32" s="19" t="n">
-        <v>2710</v>
-      </c>
-      <c r="AZ32" s="19" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="BA32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BB32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BC32" s="19" t="inlineStr">
-        <is>
-          <t>до 11.10</t>
-        </is>
-      </c>
-      <c r="BD32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BE32" s="19" t="n">
-        <v>3200</v>
-      </c>
-      <c r="BF32" s="19" t="inlineStr">
-        <is>
-          <t>Ф</t>
-        </is>
-      </c>
-      <c r="BG32" s="19" t="inlineStr">
-        <is>
-          <t>230926-1 /// AXIS</t>
-        </is>
-      </c>
-      <c r="BH32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BI32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BJ32" s="19" t="inlineStr">
-        <is>
-          <t>230926-1</t>
-        </is>
-      </c>
-      <c r="BK32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BL32" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BM32" s="19" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="29" t="n">
-        <v>16092613402</v>
-      </c>
-      <c r="B33" s="29" t="inlineStr">
-        <is>
-          <t>М</t>
-        </is>
-      </c>
-      <c r="C33" s="29" t="inlineStr">
-        <is>
-          <t>Ray</t>
-        </is>
-      </c>
-      <c r="D33" s="29" t="inlineStr">
-        <is>
-          <t>KDV-1</t>
-        </is>
-      </c>
-      <c r="E33" s="41" t="inlineStr">
-        <is>
-          <t>6 TROUBLE</t>
-        </is>
-      </c>
-      <c r="F33" s="29" t="inlineStr">
-        <is>
-          <t>DAT MOW
-P20518726</t>
-        </is>
-      </c>
-      <c r="G33" s="29" t="inlineStr">
-        <is>
-          <t>Utair</t>
-        </is>
-      </c>
-      <c r="H33" s="29" t="inlineStr">
-        <is>
-          <t>комм</t>
-        </is>
-      </c>
-      <c r="I33" s="29" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J33" s="29" t="n">
-        <v/>
-      </c>
-      <c r="K33" s="29" t="inlineStr">
-        <is>
-          <t>BACR13CF2AB</t>
-        </is>
-      </c>
-      <c r="L33" s="29" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="29" t="inlineStr">
-        <is>
-          <t>RELAY</t>
-        </is>
-      </c>
-      <c r="N33" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="O33" s="29" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="P33" s="29" t="inlineStr">
-        <is>
-          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q33" s="32" t="n">
@@ -23446,65 +23430,71 @@
       </c>
       <c r="Y33" s="29" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="Z33" s="29" t="inlineStr">
         <is>
-          <t>BLUE OCEAN SOLUTIONS</t>
+          <t>LUFTHANSA</t>
         </is>
       </c>
       <c r="AA33" s="29" t="n">
         <v/>
       </c>
-      <c r="AB33" s="29" t="n">
-        <v/>
+      <c r="AB33" s="29" t="inlineStr">
+        <is>
+          <t>JP230926-1</t>
+        </is>
       </c>
       <c r="AC33" s="29" t="inlineStr">
         <is>
-          <t>№2389</t>
-        </is>
-      </c>
-      <c r="AD33" s="29" t="n">
-        <v/>
+          <t>#6188</t>
+        </is>
+      </c>
+      <c r="AD33" s="29" t="inlineStr">
+        <is>
+          <t>2859</t>
+        </is>
       </c>
       <c r="AE33" s="33" t="n">
-        <v>133</v>
+        <v>2710</v>
       </c>
       <c r="AF33" s="33" t="n">
-        <v>266</v>
+        <v>2710</v>
       </c>
       <c r="AG33" s="33" t="n">
-        <v>220</v>
+        <v>4000</v>
       </c>
       <c r="AH33" s="33" t="n">
-        <v>440</v>
+        <v>4000</v>
       </c>
       <c r="AI33" s="33" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ33" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AK33" s="33" t="n">
+        <v>135.9065</v>
+      </c>
+      <c r="AL33" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AM33" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AN33" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AJ33" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AK33" s="33" t="n">
-        <v>13.3399</v>
-      </c>
-      <c r="AL33" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AM33" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AN33" s="29" t="n">
-        <v>0.22</v>
-      </c>
       <c r="AO33" s="29" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP33" s="29" t="n">
-        <v/>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP33" s="29" t="inlineStr">
+        <is>
+          <t>Есть МПТ</t>
+        </is>
       </c>
       <c r="AQ33" s="29" t="inlineStr">
         <is>
@@ -23524,7 +23514,7 @@
         <v/>
       </c>
       <c r="AV33" s="33" t="n">
-        <v>440</v>
+        <v>4000</v>
       </c>
       <c r="AW33" s="29" t="n">
         <v/>
@@ -23533,35 +23523,39 @@
         <v/>
       </c>
       <c r="AY33" s="29" t="n">
-        <v>266</v>
-      </c>
-      <c r="AZ33" s="34" t="n">
-        <v>46281</v>
+        <v>2710</v>
+      </c>
+      <c r="AZ33" s="29" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
       </c>
       <c r="BA33" s="29" t="n">
         <v/>
       </c>
-      <c r="BB33" s="29" t="inlineStr">
-        <is>
-          <t>UNSOLVED</t>
-        </is>
+      <c r="BB33" s="29" t="n">
+        <v/>
       </c>
       <c r="BC33" s="29" t="inlineStr">
         <is>
-          <t>Stock out</t>
+          <t>до 11.10</t>
         </is>
       </c>
       <c r="BD33" s="29" t="n">
         <v/>
       </c>
       <c r="BE33" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BF33" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BG33" s="29" t="n">
-        <v/>
+        <v>3200</v>
+      </c>
+      <c r="BF33" s="29" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
+      </c>
+      <c r="BG33" s="29" t="inlineStr">
+        <is>
+          <t>230926-1 /// AXIS</t>
+        </is>
       </c>
       <c r="BH33" s="29" t="n">
         <v/>
@@ -23569,8 +23563,10 @@
       <c r="BI33" s="29" t="n">
         <v/>
       </c>
-      <c r="BJ33" s="29" t="n">
-        <v/>
+      <c r="BJ33" s="29" t="inlineStr">
+        <is>
+          <t>230926-1</t>
+        </is>
       </c>
       <c r="BK33" s="29" t="n">
         <v/>
@@ -23601,9 +23597,9 @@
           <t>KDV-1</t>
         </is>
       </c>
-      <c r="E34" s="40" t="inlineStr">
-        <is>
-          <t>1 NOT PAID</t>
+      <c r="E34" s="41" t="inlineStr">
+        <is>
+          <t>6 TROUBLE</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -23632,7 +23628,7 @@
       </c>
       <c r="K34" s="19" t="inlineStr">
         <is>
-          <t>BACR15FT6AD12C</t>
+          <t>BACR13CF2AB</t>
         </is>
       </c>
       <c r="L34" s="19" t="n">
@@ -23640,11 +23636,11 @@
       </c>
       <c r="M34" s="19" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>RELAY</t>
         </is>
       </c>
       <c r="N34" s="20" t="n">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="O34" s="19" t="inlineStr">
         <is>
@@ -23702,32 +23698,32 @@
       </c>
       <c r="AC34" s="19" t="inlineStr">
         <is>
-          <t>№2387</t>
+          <t>№2389</t>
         </is>
       </c>
       <c r="AD34" s="19" t="n">
         <v/>
       </c>
       <c r="AE34" s="21" t="n">
-        <v>0.4</v>
+        <v>133</v>
       </c>
       <c r="AF34" s="21" t="n">
-        <v>100</v>
+        <v>266</v>
       </c>
       <c r="AG34" s="21" t="n">
-        <v>1.1</v>
+        <v>220</v>
       </c>
       <c r="AH34" s="21" t="n">
-        <v>275</v>
+        <v>440</v>
       </c>
       <c r="AI34" s="21" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" s="21" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="AK34" s="21" t="n">
-        <v>5.015</v>
+        <v>13.3399</v>
       </c>
       <c r="AL34" s="21" t="n">
         <v/>
@@ -23764,7 +23760,7 @@
         <v/>
       </c>
       <c r="AV34" s="21" t="n">
-        <v>275</v>
+        <v>440</v>
       </c>
       <c r="AW34" s="19" t="n">
         <v/>
@@ -23773,7 +23769,7 @@
         <v/>
       </c>
       <c r="AY34" s="19" t="n">
-        <v>100</v>
+        <v>266</v>
       </c>
       <c r="AZ34" s="36" t="n">
         <v>46281</v>
@@ -23783,11 +23779,13 @@
       </c>
       <c r="BB34" s="19" t="inlineStr">
         <is>
-          <t>BOS WHS</t>
-        </is>
-      </c>
-      <c r="BC34" s="19" t="n">
-        <v/>
+          <t>UNSOLVED</t>
+        </is>
+      </c>
+      <c r="BC34" s="19" t="inlineStr">
+        <is>
+          <t>Stock out</t>
+        </is>
       </c>
       <c r="BD34" s="19" t="n">
         <v/>
@@ -23795,10 +23793,8 @@
       <c r="BE34" s="19" t="n">
         <v/>
       </c>
-      <c r="BF34" s="19" t="inlineStr">
-        <is>
-          <t>Др</t>
-        </is>
+      <c r="BF34" s="19" t="n">
+        <v/>
       </c>
       <c r="BG34" s="19" t="n">
         <v/>
@@ -23813,10 +23809,10 @@
         <v/>
       </c>
       <c r="BK34" s="19" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="BL34" s="19" t="n">
-        <v>100</v>
+        <v/>
       </c>
       <c r="BM34" s="19" t="n">
         <v/>
@@ -23872,7 +23868,7 @@
       </c>
       <c r="K35" s="29" t="inlineStr">
         <is>
-          <t>BACS12HN3-5</t>
+          <t>BACR15FT6AD12C</t>
         </is>
       </c>
       <c r="L35" s="29" t="n">
@@ -23880,11 +23876,11 @@
       </c>
       <c r="M35" s="29" t="inlineStr">
         <is>
-          <t>SCREW</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="N35" s="31" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="O35" s="29" t="inlineStr">
         <is>
@@ -23942,23 +23938,23 @@
       </c>
       <c r="AC35" s="29" t="inlineStr">
         <is>
-          <t>№2388</t>
+          <t>№2387</t>
         </is>
       </c>
       <c r="AD35" s="29" t="n">
         <v/>
       </c>
       <c r="AE35" s="33" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="AF35" s="33" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="AG35" s="33" t="n">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="AH35" s="33" t="n">
-        <v>350</v>
+        <v>275</v>
       </c>
       <c r="AI35" s="33" t="n">
         <v>0</v>
@@ -23967,7 +23963,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="33" t="n">
-        <v>6.77025</v>
+        <v>5.015</v>
       </c>
       <c r="AL35" s="33" t="n">
         <v/>
@@ -24004,7 +24000,7 @@
         <v/>
       </c>
       <c r="AV35" s="33" t="n">
-        <v>350</v>
+        <v>275</v>
       </c>
       <c r="AW35" s="29" t="n">
         <v/>
@@ -24013,7 +24009,7 @@
         <v/>
       </c>
       <c r="AY35" s="29" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="AZ35" s="34" t="n">
         <v>46281</v>
@@ -24056,7 +24052,7 @@
         <v>0</v>
       </c>
       <c r="BL35" s="29" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="BM35" s="29" t="n">
         <v/>
@@ -24064,7 +24060,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>17092612085</v>
+        <v>16092613402</v>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
@@ -24089,7 +24085,7 @@
       <c r="F36" s="19" t="inlineStr">
         <is>
           <t>DAT MOW
-P20526726</t>
+P20518726</t>
         </is>
       </c>
       <c r="G36" s="19" t="inlineStr">
@@ -24107,14 +24103,12 @@
           <t>E</t>
         </is>
       </c>
-      <c r="J36" s="19" t="inlineStr">
-        <is>
-          <t>ATR72</t>
-        </is>
+      <c r="J36" s="19" t="n">
+        <v/>
       </c>
       <c r="K36" s="19" t="inlineStr">
         <is>
-          <t>ST3086-013WE</t>
+          <t>BACS12HN3-5</t>
         </is>
       </c>
       <c r="L36" s="19" t="n">
@@ -24122,11 +24116,11 @@
       </c>
       <c r="M36" s="19" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>SCREW</t>
         </is>
       </c>
       <c r="N36" s="20" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="O36" s="19" t="inlineStr">
         <is>
@@ -24139,7 +24133,7 @@
         </is>
       </c>
       <c r="Q36" s="35" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="R36" s="19" t="n">
         <v>30</v>
@@ -24152,13 +24146,11 @@
       <c r="T36" s="19" t="n">
         <v/>
       </c>
-      <c r="U36" s="19" t="inlineStr">
-        <is>
-          <t>PRIORITY NET</t>
-        </is>
+      <c r="U36" s="19" t="n">
+        <v/>
       </c>
       <c r="V36" s="35" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="W36" s="19" t="n">
         <v/>
@@ -24175,45 +24167,43 @@
       </c>
       <c r="Z36" s="19" t="inlineStr">
         <is>
-          <t>LUFTHANSA</t>
-        </is>
-      </c>
-      <c r="AA36" s="19" t="inlineStr">
-        <is>
-          <t>WENCOR</t>
-        </is>
+          <t>BLUE OCEAN SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="AA36" s="19" t="n">
+        <v/>
       </c>
       <c r="AB36" s="19" t="n">
         <v/>
       </c>
       <c r="AC36" s="19" t="inlineStr">
         <is>
-          <t>#6203</t>
+          <t>№2388</t>
         </is>
       </c>
       <c r="AD36" s="19" t="n">
         <v/>
       </c>
       <c r="AE36" s="21" t="n">
-        <v>200</v>
+        <v>2.7</v>
       </c>
       <c r="AF36" s="21" t="n">
-        <v>6000</v>
+        <v>135</v>
       </c>
       <c r="AG36" s="21" t="n">
-        <v>310</v>
+        <v>7</v>
       </c>
       <c r="AH36" s="21" t="n">
-        <v>9300</v>
+        <v>350</v>
       </c>
       <c r="AI36" s="21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ36" s="21" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK36" s="21" t="n">
-        <v>300.9</v>
+        <v>6.77025</v>
       </c>
       <c r="AL36" s="21" t="n">
         <v/>
@@ -24234,7 +24224,7 @@
       </c>
       <c r="AQ36" s="19" t="inlineStr">
         <is>
-          <t>Частичная предоплата</t>
+          <t>Постоплата 100%</t>
         </is>
       </c>
       <c r="AR36" s="19" t="n">
@@ -24250,7 +24240,7 @@
         <v/>
       </c>
       <c r="AV36" s="21" t="n">
-        <v>9300</v>
+        <v>350</v>
       </c>
       <c r="AW36" s="19" t="n">
         <v/>
@@ -24259,17 +24249,17 @@
         <v/>
       </c>
       <c r="AY36" s="19" t="n">
-        <v>6000</v>
+        <v>135</v>
       </c>
       <c r="AZ36" s="36" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="BA36" s="19" t="n">
         <v/>
       </c>
       <c r="BB36" s="19" t="inlineStr">
         <is>
-          <t>HA WHS</t>
+          <t>BOS WHS</t>
         </is>
       </c>
       <c r="BC36" s="19" t="n">
@@ -24299,10 +24289,10 @@
         <v/>
       </c>
       <c r="BK36" s="19" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="BL36" s="19" t="n">
-        <v/>
+        <v>135</v>
       </c>
       <c r="BM36" s="19" t="n">
         <v/>
@@ -24310,7 +24300,7 @@
     </row>
     <row r="37">
       <c r="A37" s="29" t="n">
-        <v>17092615215</v>
+        <v>17092612085</v>
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
@@ -24324,7 +24314,7 @@
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>KDV-3</t>
+          <t>KDV-1</t>
         </is>
       </c>
       <c r="E37" s="40" t="inlineStr">
@@ -24334,8 +24324,8 @@
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20530826</t>
+          <t>DAT MOW
+P20526726</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
@@ -24350,17 +24340,17 @@
       </c>
       <c r="I37" s="29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J37" s="29" t="inlineStr">
         <is>
-          <t>737ALL</t>
+          <t>ATR72</t>
         </is>
       </c>
       <c r="K37" s="29" t="inlineStr">
         <is>
-          <t>1150002-1</t>
+          <t>ST3086-013WE</t>
         </is>
       </c>
       <c r="L37" s="29" t="n">
@@ -24368,11 +24358,11 @@
       </c>
       <c r="M37" s="29" t="inlineStr">
         <is>
-          <t>SENSOR</t>
+          <t>PACKING</t>
         </is>
       </c>
       <c r="N37" s="31" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O37" s="29" t="inlineStr">
         <is>
@@ -24381,7 +24371,7 @@
       </c>
       <c r="P37" s="29" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q37" s="32" t="n">
@@ -24398,8 +24388,10 @@
       <c r="T37" s="29" t="n">
         <v/>
       </c>
-      <c r="U37" s="29" t="n">
-        <v/>
+      <c r="U37" s="29" t="inlineStr">
+        <is>
+          <t>PRIORITY NET</t>
+        </is>
       </c>
       <c r="V37" s="32" t="n">
         <v>46312</v>
@@ -24414,7 +24406,7 @@
       </c>
       <c r="Y37" s="29" t="inlineStr">
         <is>
-          <t>TEST</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z37" s="29" t="inlineStr">
@@ -24422,44 +24414,42 @@
           <t>LUFTHANSA</t>
         </is>
       </c>
-      <c r="AA37" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AB37" s="29" t="inlineStr">
-        <is>
-          <t>JP280926-3</t>
-        </is>
+      <c r="AA37" s="29" t="inlineStr">
+        <is>
+          <t>WENCOR</t>
+        </is>
+      </c>
+      <c r="AB37" s="29" t="n">
+        <v/>
       </c>
       <c r="AC37" s="29" t="inlineStr">
         <is>
-          <t>#6204</t>
-        </is>
-      </c>
-      <c r="AD37" s="29" t="inlineStr">
-        <is>
-          <t>012C-3004</t>
-        </is>
+          <t>#6203</t>
+        </is>
+      </c>
+      <c r="AD37" s="29" t="n">
+        <v/>
       </c>
       <c r="AE37" s="33" t="n">
-        <v>2300</v>
+        <v>200</v>
       </c>
       <c r="AF37" s="33" t="n">
-        <v>2300</v>
+        <v>6000</v>
       </c>
       <c r="AG37" s="33" t="n">
-        <v>3600</v>
+        <v>310</v>
       </c>
       <c r="AH37" s="33" t="n">
-        <v>3600</v>
+        <v>9300</v>
       </c>
       <c r="AI37" s="33" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AJ37" s="33" t="n">
         <v/>
       </c>
       <c r="AK37" s="33" t="n">
-        <v>115.345</v>
+        <v>300.9</v>
       </c>
       <c r="AL37" s="33" t="n">
         <v/>
@@ -24468,21 +24458,19 @@
         <v/>
       </c>
       <c r="AN37" s="29" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO37" s="29" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP37" s="29" t="inlineStr">
-        <is>
-          <t>Получаем МПТ</t>
-        </is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP37" s="29" t="n">
+        <v/>
       </c>
       <c r="AQ37" s="29" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
+          <t>Частичная предоплата</t>
         </is>
       </c>
       <c r="AR37" s="29" t="n">
@@ -24498,7 +24486,7 @@
         <v/>
       </c>
       <c r="AV37" s="33" t="n">
-        <v>3600</v>
+        <v>9300</v>
       </c>
       <c r="AW37" s="29" t="n">
         <v/>
@@ -24507,35 +24495,31 @@
         <v/>
       </c>
       <c r="AY37" s="29" t="n">
-        <v>2300</v>
-      </c>
-      <c r="AZ37" s="29" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
+        <v>6000</v>
+      </c>
+      <c r="AZ37" s="34" t="n">
+        <v>46282</v>
       </c>
       <c r="BA37" s="29" t="n">
         <v/>
       </c>
       <c r="BB37" s="29" t="inlineStr">
         <is>
-          <t>pick up 02/10</t>
-        </is>
-      </c>
-      <c r="BC37" s="29" t="inlineStr">
-        <is>
-          <t>до 10.10</t>
-        </is>
+          <t>HA WHS</t>
+        </is>
+      </c>
+      <c r="BC37" s="29" t="n">
+        <v/>
       </c>
       <c r="BD37" s="29" t="n">
         <v/>
       </c>
       <c r="BE37" s="29" t="n">
-        <v>2880</v>
+        <v/>
       </c>
       <c r="BF37" s="29" t="inlineStr">
         <is>
-          <t>Ф</t>
+          <t>Др</t>
         </is>
       </c>
       <c r="BG37" s="29" t="n">
@@ -24547,10 +24531,8 @@
       <c r="BI37" s="29" t="n">
         <v/>
       </c>
-      <c r="BJ37" s="29" t="inlineStr">
-        <is>
-          <t>280926-3</t>
-        </is>
+      <c r="BJ37" s="29" t="n">
+        <v/>
       </c>
       <c r="BK37" s="29" t="n">
         <v/>
@@ -24564,7 +24546,7 @@
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>21092614525</v>
+        <v>17092615215</v>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
@@ -24589,7 +24571,7 @@
       <c r="F38" s="19" t="inlineStr">
         <is>
           <t>DDP MOW
-P20536126</t>
+P20530826</t>
         </is>
       </c>
       <c r="G38" s="19" t="inlineStr">
@@ -24639,7 +24621,7 @@
         </is>
       </c>
       <c r="Q38" s="35" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="R38" s="19" t="n">
         <v>30</v>
@@ -24656,7 +24638,7 @@
         <v/>
       </c>
       <c r="V38" s="35" t="n">
-        <v>46316</v>
+        <v>46312</v>
       </c>
       <c r="W38" s="19" t="n">
         <v/>
@@ -24668,7 +24650,7 @@
       </c>
       <c r="Y38" s="19" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>TEST</t>
         </is>
       </c>
       <c r="Z38" s="19" t="inlineStr">
@@ -24679,30 +24661,32 @@
       <c r="AA38" s="19" t="n">
         <v/>
       </c>
-      <c r="AB38" s="19" t="n">
-        <v/>
+      <c r="AB38" s="19" t="inlineStr">
+        <is>
+          <t>JP280926-3</t>
+        </is>
       </c>
       <c r="AC38" s="19" t="inlineStr">
         <is>
-          <t>#6229</t>
+          <t>#6204</t>
         </is>
       </c>
       <c r="AD38" s="19" t="inlineStr">
         <is>
-          <t>1150002-09716</t>
+          <t>012C-3004</t>
         </is>
       </c>
       <c r="AE38" s="21" t="n">
-        <v>2760</v>
+        <v>2300</v>
       </c>
       <c r="AF38" s="21" t="n">
-        <v>2760</v>
+        <v>2300</v>
       </c>
       <c r="AG38" s="21" t="n">
-        <v>4300</v>
+        <v>3600</v>
       </c>
       <c r="AH38" s="21" t="n">
-        <v>4300</v>
+        <v>3600</v>
       </c>
       <c r="AI38" s="21" t="n">
         <v>200</v>
@@ -24711,7 +24695,7 @@
         <v/>
       </c>
       <c r="AK38" s="21" t="n">
-        <v>138.414</v>
+        <v>115.345</v>
       </c>
       <c r="AL38" s="21" t="n">
         <v/>
@@ -24750,7 +24734,7 @@
         <v/>
       </c>
       <c r="AV38" s="21" t="n">
-        <v>4300</v>
+        <v>3600</v>
       </c>
       <c r="AW38" s="19" t="n">
         <v/>
@@ -24759,7 +24743,7 @@
         <v/>
       </c>
       <c r="AY38" s="19" t="n">
-        <v>2760</v>
+        <v>2300</v>
       </c>
       <c r="AZ38" s="19" t="inlineStr">
         <is>
@@ -24771,20 +24755,24 @@
       </c>
       <c r="BB38" s="19" t="inlineStr">
         <is>
-          <t>UNCONFIRMED YET</t>
-        </is>
-      </c>
-      <c r="BC38" s="19" t="n">
-        <v/>
+          <t>pick up 02/10</t>
+        </is>
+      </c>
+      <c r="BC38" s="19" t="inlineStr">
+        <is>
+          <t>до 10.10</t>
+        </is>
       </c>
       <c r="BD38" s="19" t="n">
         <v/>
       </c>
       <c r="BE38" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BF38" s="19" t="n">
-        <v/>
+        <v>2880</v>
+      </c>
+      <c r="BF38" s="19" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
       </c>
       <c r="BG38" s="19" t="n">
         <v/>
@@ -24795,8 +24783,10 @@
       <c r="BI38" s="19" t="n">
         <v/>
       </c>
-      <c r="BJ38" s="19" t="n">
-        <v/>
+      <c r="BJ38" s="19" t="inlineStr">
+        <is>
+          <t>280926-3</t>
+        </is>
       </c>
       <c r="BK38" s="19" t="n">
         <v/>
@@ -24810,7 +24800,7 @@
     </row>
     <row r="39">
       <c r="A39" s="29" t="n">
-        <v>23092613105</v>
+        <v>21092614525</v>
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
@@ -24824,7 +24814,7 @@
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>KDV-1</t>
+          <t>KDV-3</t>
         </is>
       </c>
       <c r="E39" s="40" t="inlineStr">
@@ -24834,8 +24824,8 @@
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20561926</t>
+          <t>DDP MOW
+P20536126</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
@@ -24850,27 +24840,29 @@
       </c>
       <c r="I39" s="29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J39" s="29" t="inlineStr">
         <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="K39" s="29" t="n">
-        <v>10009255</v>
+          <t>737ALL</t>
+        </is>
+      </c>
+      <c r="K39" s="29" t="inlineStr">
+        <is>
+          <t>1150002-1</t>
+        </is>
       </c>
       <c r="L39" s="29" t="n">
         <v/>
       </c>
       <c r="M39" s="29" t="inlineStr">
         <is>
-          <t>POPPET</t>
+          <t>SENSOR</t>
         </is>
       </c>
       <c r="N39" s="31" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O39" s="29" t="inlineStr">
         <is>
@@ -24879,11 +24871,11 @@
       </c>
       <c r="P39" s="29" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q39" s="32" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="R39" s="29" t="n">
         <v>30</v>
@@ -24896,13 +24888,11 @@
       <c r="T39" s="29" t="n">
         <v/>
       </c>
-      <c r="U39" s="29" t="inlineStr">
-        <is>
-          <t>PRIORITY NET</t>
-        </is>
+      <c r="U39" s="29" t="n">
+        <v/>
       </c>
       <c r="V39" s="32" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="W39" s="29" t="n">
         <v/>
@@ -24914,7 +24904,7 @@
       </c>
       <c r="Y39" s="29" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="Z39" s="29" t="inlineStr">
@@ -24922,42 +24912,42 @@
           <t>LUFTHANSA</t>
         </is>
       </c>
-      <c r="AA39" s="29" t="inlineStr">
-        <is>
-          <t>AVIALL</t>
-        </is>
+      <c r="AA39" s="29" t="n">
+        <v/>
       </c>
       <c r="AB39" s="29" t="n">
         <v/>
       </c>
       <c r="AC39" s="29" t="inlineStr">
         <is>
-          <t>#6244</t>
-        </is>
-      </c>
-      <c r="AD39" s="29" t="n">
-        <v/>
+          <t>#6229</t>
+        </is>
+      </c>
+      <c r="AD39" s="29" t="inlineStr">
+        <is>
+          <t>1150002-09716</t>
+        </is>
       </c>
       <c r="AE39" s="33" t="n">
-        <v>11</v>
+        <v>2760</v>
       </c>
       <c r="AF39" s="33" t="n">
-        <v>220</v>
+        <v>2760</v>
       </c>
       <c r="AG39" s="33" t="n">
-        <v>21</v>
+        <v>4300</v>
       </c>
       <c r="AH39" s="33" t="n">
-        <v>420</v>
+        <v>4300</v>
       </c>
       <c r="AI39" s="33" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="AJ39" s="33" t="n">
         <v/>
       </c>
       <c r="AK39" s="33" t="n">
-        <v>11.033</v>
+        <v>138.414</v>
       </c>
       <c r="AL39" s="33" t="n">
         <v/>
@@ -24966,15 +24956,17 @@
         <v/>
       </c>
       <c r="AN39" s="29" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AO39" s="29" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP39" s="29" t="n">
-        <v/>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP39" s="29" t="inlineStr">
+        <is>
+          <t>Получаем МПТ</t>
+        </is>
       </c>
       <c r="AQ39" s="29" t="inlineStr">
         <is>
@@ -24994,7 +24986,7 @@
         <v/>
       </c>
       <c r="AV39" s="33" t="n">
-        <v>420</v>
+        <v>4300</v>
       </c>
       <c r="AW39" s="29" t="n">
         <v/>
@@ -25003,17 +24995,19 @@
         <v/>
       </c>
       <c r="AY39" s="29" t="n">
-        <v>220</v>
-      </c>
-      <c r="AZ39" s="34" t="n">
-        <v>46290</v>
+        <v>2760</v>
+      </c>
+      <c r="AZ39" s="29" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
       </c>
       <c r="BA39" s="29" t="n">
         <v/>
       </c>
       <c r="BB39" s="29" t="inlineStr">
         <is>
-          <t>HA WHS</t>
+          <t>UNCONFIRMED YET</t>
         </is>
       </c>
       <c r="BC39" s="29" t="n">
@@ -25025,10 +25019,8 @@
       <c r="BE39" s="29" t="n">
         <v/>
       </c>
-      <c r="BF39" s="29" t="inlineStr">
-        <is>
-          <t>Др</t>
-        </is>
+      <c r="BF39" s="29" t="n">
+        <v/>
       </c>
       <c r="BG39" s="29" t="n">
         <v/>
@@ -25103,18 +25095,18 @@
         </is>
       </c>
       <c r="K40" s="19" t="n">
-        <v>10009072</v>
+        <v>10009255</v>
       </c>
       <c r="L40" s="19" t="n">
         <v/>
       </c>
       <c r="M40" s="19" t="inlineStr">
         <is>
-          <t>INSTRUCTION DECAL</t>
+          <t>POPPET</t>
         </is>
       </c>
       <c r="N40" s="20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O40" s="19" t="inlineStr">
         <is>
@@ -25176,23 +25168,23 @@
       </c>
       <c r="AC40" s="19" t="inlineStr">
         <is>
-          <t>#6245</t>
+          <t>#6244</t>
         </is>
       </c>
       <c r="AD40" s="19" t="n">
         <v/>
       </c>
       <c r="AE40" s="21" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AF40" s="21" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AG40" s="21" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="AH40" s="21" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="AI40" s="21" t="n">
         <v>50</v>
@@ -25201,7 +25193,7 @@
         <v/>
       </c>
       <c r="AK40" s="21" t="n">
-        <v>10.03</v>
+        <v>11.033</v>
       </c>
       <c r="AL40" s="21" t="n">
         <v/>
@@ -25238,7 +25230,7 @@
         <v/>
       </c>
       <c r="AV40" s="21" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="AW40" s="19" t="n">
         <v/>
@@ -25247,7 +25239,7 @@
         <v/>
       </c>
       <c r="AY40" s="19" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AZ40" s="36" t="n">
         <v>46290</v>
@@ -25298,7 +25290,7 @@
     </row>
     <row r="41">
       <c r="A41" s="29" t="n">
-        <v>2309268425</v>
+        <v>23092613105</v>
       </c>
       <c r="B41" s="29" t="inlineStr">
         <is>
@@ -25323,7 +25315,7 @@
       <c r="F41" s="29" t="inlineStr">
         <is>
           <t>DAT MOW
-P20557426</t>
+P20561926</t>
         </is>
       </c>
       <c r="G41" s="29" t="inlineStr">
@@ -25343,24 +25335,22 @@
       </c>
       <c r="J41" s="29" t="inlineStr">
         <is>
-          <t>BOEING</t>
-        </is>
-      </c>
-      <c r="K41" s="29" t="inlineStr">
-        <is>
-          <t>3-906S383-70</t>
-        </is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="K41" s="29" t="n">
+        <v>10009072</v>
       </c>
       <c r="L41" s="29" t="n">
         <v/>
       </c>
       <c r="M41" s="29" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>INSTRUCTION DECAL</t>
         </is>
       </c>
       <c r="N41" s="31" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="O41" s="29" t="inlineStr">
         <is>
@@ -25414,7 +25404,7 @@
       </c>
       <c r="AA41" s="29" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="AB41" s="29" t="n">
@@ -25422,23 +25412,23 @@
       </c>
       <c r="AC41" s="29" t="inlineStr">
         <is>
-          <t>#6235</t>
+          <t>#6245</t>
         </is>
       </c>
       <c r="AD41" s="29" t="n">
         <v/>
       </c>
       <c r="AE41" s="33" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AF41" s="33" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AG41" s="33" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="AH41" s="33" t="n">
-        <v>800</v>
+        <v>440</v>
       </c>
       <c r="AI41" s="33" t="n">
         <v>50</v>
@@ -25447,7 +25437,7 @@
         <v/>
       </c>
       <c r="AK41" s="33" t="n">
-        <v>20.6</v>
+        <v>10.03</v>
       </c>
       <c r="AL41" s="33" t="n">
         <v/>
@@ -25484,7 +25474,7 @@
         <v/>
       </c>
       <c r="AV41" s="33" t="n">
-        <v>800</v>
+        <v>440</v>
       </c>
       <c r="AW41" s="29" t="n">
         <v/>
@@ -25493,17 +25483,17 @@
         <v/>
       </c>
       <c r="AY41" s="29" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AZ41" s="34" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="BA41" s="29" t="n">
         <v/>
       </c>
       <c r="BB41" s="29" t="inlineStr">
         <is>
-          <t>PAID</t>
+          <t>HA WHS</t>
         </is>
       </c>
       <c r="BC41" s="29" t="n">
@@ -25515,8 +25505,10 @@
       <c r="BE41" s="29" t="n">
         <v/>
       </c>
-      <c r="BF41" s="29" t="n">
-        <v/>
+      <c r="BF41" s="29" t="inlineStr">
+        <is>
+          <t>Др</t>
+        </is>
       </c>
       <c r="BG41" s="29" t="n">
         <v/>
@@ -25542,7 +25534,7 @@
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>24092613345</v>
+        <v>2309268425</v>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
@@ -25556,7 +25548,7 @@
       </c>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>KDV-3</t>
+          <t>KDV-1</t>
         </is>
       </c>
       <c r="E42" s="40" t="inlineStr">
@@ -25566,8 +25558,8 @@
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20568326</t>
+          <t>DAT MOW
+P20557426</t>
         </is>
       </c>
       <c r="G42" s="19" t="inlineStr">
@@ -25582,17 +25574,17 @@
       </c>
       <c r="I42" s="19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J42" s="19" t="inlineStr">
         <is>
-          <t>737ALL</t>
+          <t>BOEING</t>
         </is>
       </c>
       <c r="K42" s="19" t="inlineStr">
         <is>
-          <t>398908-5</t>
+          <t>3-906S383-70</t>
         </is>
       </c>
       <c r="L42" s="19" t="n">
@@ -25600,11 +25592,11 @@
       </c>
       <c r="M42" s="19" t="inlineStr">
         <is>
-          <t>VALVE ASSY - TEMP CONT</t>
+          <t>PACKING</t>
         </is>
       </c>
       <c r="N42" s="20" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="O42" s="19" t="inlineStr">
         <is>
@@ -25613,26 +25605,30 @@
       </c>
       <c r="P42" s="19" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q42" s="35" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="R42" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="S42" s="19" t="n">
-        <v>14</v>
+      <c r="S42" s="19" t="inlineStr">
+        <is>
+          <t>STK</t>
+        </is>
       </c>
       <c r="T42" s="19" t="n">
         <v/>
       </c>
-      <c r="U42" s="19" t="n">
-        <v/>
+      <c r="U42" s="19" t="inlineStr">
+        <is>
+          <t>PRIORITY NET</t>
+        </is>
       </c>
       <c r="V42" s="35" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="W42" s="19" t="n">
         <v/>
@@ -25644,54 +25640,50 @@
       </c>
       <c r="Y42" s="19" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z42" s="19" t="inlineStr">
         <is>
-          <t>IBERIA</t>
+          <t>LUFTHANSA</t>
         </is>
       </c>
       <c r="AA42" s="19" t="inlineStr">
         <is>
-          <t>OH CAPITAL ASSETS</t>
-        </is>
-      </c>
-      <c r="AB42" s="19" t="inlineStr">
-        <is>
-          <t>KTM2509261157</t>
-        </is>
+          <t>WENCOR</t>
+        </is>
+      </c>
+      <c r="AB42" s="19" t="n">
+        <v/>
       </c>
       <c r="AC42" s="19" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD42" s="19" t="inlineStr">
-        <is>
-          <t>18426</t>
-        </is>
+          <t>#6235</t>
+        </is>
+      </c>
+      <c r="AD42" s="19" t="n">
+        <v/>
       </c>
       <c r="AE42" s="21" t="n">
-        <v>10000</v>
+        <v>2</v>
       </c>
       <c r="AF42" s="21" t="n">
-        <v>10000</v>
+        <v>400</v>
       </c>
       <c r="AG42" s="21" t="n">
-        <v>14200</v>
+        <v>4</v>
       </c>
       <c r="AH42" s="21" t="n">
-        <v>14200</v>
+        <v>800</v>
       </c>
       <c r="AI42" s="21" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AJ42" s="21" t="n">
         <v/>
       </c>
       <c r="AK42" s="21" t="n">
-        <v>501.5</v>
+        <v>20.6</v>
       </c>
       <c r="AL42" s="21" t="n">
         <v/>
@@ -25700,17 +25692,15 @@
         <v/>
       </c>
       <c r="AN42" s="19" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO42" s="19" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP42" s="19" t="inlineStr">
-        <is>
-          <t>Получаем МПТ</t>
-        </is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP42" s="19" t="n">
+        <v/>
       </c>
       <c r="AQ42" s="19" t="inlineStr">
         <is>
@@ -25730,7 +25720,7 @@
         <v/>
       </c>
       <c r="AV42" s="21" t="n">
-        <v>14200</v>
+        <v>800</v>
       </c>
       <c r="AW42" s="19" t="n">
         <v/>
@@ -25739,16 +25729,18 @@
         <v/>
       </c>
       <c r="AY42" s="19" t="n">
-        <v>10000</v>
+        <v>400</v>
       </c>
       <c r="AZ42" s="36" t="n">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="BA42" s="19" t="n">
         <v/>
       </c>
-      <c r="BB42" s="19" t="n">
-        <v/>
+      <c r="BB42" s="19" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
       </c>
       <c r="BC42" s="19" t="n">
         <v/>
@@ -25786,7 +25778,7 @@
     </row>
     <row r="43">
       <c r="A43" s="29" t="n">
-        <v>25092613455</v>
+        <v>24092613345</v>
       </c>
       <c r="B43" s="29" t="inlineStr">
         <is>
@@ -25811,7 +25803,7 @@
       <c r="F43" s="29" t="inlineStr">
         <is>
           <t>DDP MOW
-P20523626</t>
+P20568326</t>
         </is>
       </c>
       <c r="G43" s="29" t="inlineStr">
@@ -25826,27 +25818,25 @@
       </c>
       <c r="I43" s="29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J43" s="29" t="inlineStr">
         <is>
-          <t>B762</t>
+          <t>737ALL</t>
         </is>
       </c>
       <c r="K43" s="29" t="inlineStr">
         <is>
-          <t>121282-25</t>
-        </is>
-      </c>
-      <c r="L43" s="29" t="inlineStr">
-        <is>
-          <t>DEC39-166-519</t>
-        </is>
+          <t>398908-5</t>
+        </is>
+      </c>
+      <c r="L43" s="29" t="n">
+        <v/>
       </c>
       <c r="M43" s="29" t="inlineStr">
         <is>
-          <t>SHAFT ASSY</t>
+          <t>VALVE ASSY - TEMP CONT</t>
         </is>
       </c>
       <c r="N43" s="31" t="n">
@@ -25859,136 +25849,136 @@
       </c>
       <c r="P43" s="29" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q43" s="32" t="n">
+        <v>46289</v>
+      </c>
+      <c r="R43" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="S43" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="T43" s="29" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="29" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="32" t="n">
+        <v>46319</v>
+      </c>
+      <c r="W43" s="29" t="n">
+        <v/>
+      </c>
+      <c r="X43" s="29" t="inlineStr">
+        <is>
+          <t>Продажа от поставщика</t>
+        </is>
+      </c>
+      <c r="Y43" s="29" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="Z43" s="29" t="inlineStr">
+        <is>
+          <t>IBERIA</t>
+        </is>
+      </c>
+      <c r="AA43" s="29" t="inlineStr">
+        <is>
+          <t>OH CAPITAL ASSETS</t>
+        </is>
+      </c>
+      <c r="AB43" s="29" t="inlineStr">
+        <is>
+          <t>KTM2509261157</t>
+        </is>
+      </c>
+      <c r="AC43" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD43" s="29" t="inlineStr">
+        <is>
+          <t>18426</t>
+        </is>
+      </c>
+      <c r="AE43" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AF43" s="33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AG43" s="33" t="n">
+        <v>14200</v>
+      </c>
+      <c r="AH43" s="33" t="n">
+        <v>14200</v>
+      </c>
+      <c r="AI43" s="33" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ43" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AK43" s="33" t="n">
+        <v>501.5</v>
+      </c>
+      <c r="AL43" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AM43" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AN43" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="29" t="inlineStr">
+        <is>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP43" s="29" t="inlineStr">
+        <is>
+          <t>Получаем МПТ</t>
+        </is>
+      </c>
+      <c r="AQ43" s="29" t="inlineStr">
+        <is>
+          <t>Постоплата 100%</t>
+        </is>
+      </c>
+      <c r="AR43" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AS43" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AT43" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AU43" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AV43" s="33" t="n">
+        <v>14200</v>
+      </c>
+      <c r="AW43" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AX43" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AY43" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AZ43" s="34" t="n">
         <v>46290</v>
-      </c>
-      <c r="R43" s="29" t="n">
-        <v>27</v>
-      </c>
-      <c r="S43" s="29" t="inlineStr">
-        <is>
-          <t>STK</t>
-        </is>
-      </c>
-      <c r="T43" s="29" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="29" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="32" t="n">
-        <v>46317</v>
-      </c>
-      <c r="W43" s="29" t="n">
-        <v/>
-      </c>
-      <c r="X43" s="29" t="inlineStr">
-        <is>
-          <t>Продажа от поставщика</t>
-        </is>
-      </c>
-      <c r="Y43" s="29" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="Z43" s="29" t="inlineStr">
-        <is>
-          <t>IBERIA</t>
-        </is>
-      </c>
-      <c r="AA43" s="29" t="inlineStr">
-        <is>
-          <t>HANGAR BARN</t>
-        </is>
-      </c>
-      <c r="AB43" s="29" t="inlineStr">
-        <is>
-          <t>KTM3009261621</t>
-        </is>
-      </c>
-      <c r="AC43" s="29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD43" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AE43" s="33" t="n">
-        <v>11604</v>
-      </c>
-      <c r="AF43" s="33" t="n">
-        <v>11604</v>
-      </c>
-      <c r="AG43" s="33" t="n">
-        <v>16100</v>
-      </c>
-      <c r="AH43" s="33" t="n">
-        <v>16100</v>
-      </c>
-      <c r="AI43" s="33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ43" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AK43" s="33" t="n">
-        <v>581.9406</v>
-      </c>
-      <c r="AL43" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AM43" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AN43" s="29" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AO43" s="29" t="inlineStr">
-        <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP43" s="29" t="inlineStr">
-        <is>
-          <t>Получаем МПТ</t>
-        </is>
-      </c>
-      <c r="AQ43" s="29" t="inlineStr">
-        <is>
-          <t>Частичная предоплата</t>
-        </is>
-      </c>
-      <c r="AR43" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AS43" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AT43" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AU43" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AV43" s="33" t="n">
-        <v>16100</v>
-      </c>
-      <c r="AW43" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AX43" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AY43" s="29" t="n">
-        <v>11604</v>
-      </c>
-      <c r="AZ43" s="34" t="n">
-        <v>46295</v>
       </c>
       <c r="BA43" s="29" t="n">
         <v/>
@@ -26032,7 +26022,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>28092614585</v>
+        <v>25092613455</v>
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
@@ -26057,7 +26047,7 @@
       <c r="F44" s="19" t="inlineStr">
         <is>
           <t>DDP MOW
-P20579726</t>
+P20523626</t>
         </is>
       </c>
       <c r="G44" s="19" t="inlineStr">
@@ -26072,7 +26062,7 @@
       </c>
       <c r="I44" s="19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J44" s="19" t="inlineStr">
@@ -26082,15 +26072,17 @@
       </c>
       <c r="K44" s="19" t="inlineStr">
         <is>
-          <t>RDAA8046-01</t>
-        </is>
-      </c>
-      <c r="L44" s="19" t="n">
-        <v/>
+          <t>121282-25</t>
+        </is>
+      </c>
+      <c r="L44" s="19" t="inlineStr">
+        <is>
+          <t>DEC39-166-519</t>
+        </is>
       </c>
       <c r="M44" s="19" t="inlineStr">
         <is>
-          <t>CMT (TERMINAL ASSY-CAB. MANAGEMENT)</t>
+          <t>SHAFT ASSY</t>
         </is>
       </c>
       <c r="N44" s="20" t="n">
@@ -26103,17 +26095,19 @@
       </c>
       <c r="P44" s="19" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q44" s="35" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="R44" s="19" t="n">
-        <v>25</v>
-      </c>
-      <c r="S44" s="19" t="n">
-        <v>18</v>
+        <v>27</v>
+      </c>
+      <c r="S44" s="19" t="inlineStr">
+        <is>
+          <t>STK</t>
+        </is>
       </c>
       <c r="T44" s="19" t="n">
         <v/>
@@ -26122,7 +26116,7 @@
         <v/>
       </c>
       <c r="V44" s="35" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="W44" s="19" t="n">
         <v/>
@@ -26134,7 +26128,7 @@
       </c>
       <c r="Y44" s="19" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z44" s="19" t="inlineStr">
@@ -26144,12 +26138,12 @@
       </c>
       <c r="AA44" s="19" t="inlineStr">
         <is>
-          <t>SEATTLE AVIATION SOLUTIONS</t>
+          <t>HANGAR BARN</t>
         </is>
       </c>
       <c r="AB44" s="19" t="inlineStr">
         <is>
-          <t>KTM110261615</t>
+          <t>KTM3009261621</t>
         </is>
       </c>
       <c r="AC44" s="19" t="inlineStr">
@@ -26161,25 +26155,25 @@
         <v/>
       </c>
       <c r="AE44" s="21" t="n">
-        <v>3850</v>
+        <v>11604</v>
       </c>
       <c r="AF44" s="21" t="n">
-        <v>3850</v>
+        <v>11604</v>
       </c>
       <c r="AG44" s="21" t="n">
-        <v>6000</v>
+        <v>16100</v>
       </c>
       <c r="AH44" s="21" t="n">
-        <v>6000</v>
+        <v>16100</v>
       </c>
       <c r="AI44" s="21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" s="21" t="n">
         <v/>
       </c>
       <c r="AK44" s="21" t="n">
-        <v>193.0775</v>
+        <v>581.9406</v>
       </c>
       <c r="AL44" s="21" t="n">
         <v/>
@@ -26188,11 +26182,11 @@
         <v/>
       </c>
       <c r="AN44" s="19" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO44" s="19" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
+          <t>Не применимо</t>
         </is>
       </c>
       <c r="AP44" s="19" t="inlineStr">
@@ -26202,7 +26196,7 @@
       </c>
       <c r="AQ44" s="19" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
+          <t>Частичная предоплата</t>
         </is>
       </c>
       <c r="AR44" s="19" t="n">
@@ -26218,7 +26212,7 @@
         <v/>
       </c>
       <c r="AV44" s="21" t="n">
-        <v>6000</v>
+        <v>16100</v>
       </c>
       <c r="AW44" s="19" t="n">
         <v/>
@@ -26227,10 +26221,10 @@
         <v/>
       </c>
       <c r="AY44" s="19" t="n">
-        <v>3850</v>
+        <v>11604</v>
       </c>
       <c r="AZ44" s="36" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="BA44" s="19" t="n">
         <v/>
@@ -26274,7 +26268,7 @@
     </row>
     <row r="45">
       <c r="A45" s="29" t="n">
-        <v>29092616005</v>
+        <v>28092614585</v>
       </c>
       <c r="B45" s="29" t="inlineStr">
         <is>
@@ -26288,7 +26282,7 @@
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>KDV-1</t>
+          <t>KDV-3</t>
         </is>
       </c>
       <c r="E45" s="40" t="inlineStr">
@@ -26298,8 +26292,8 @@
       </c>
       <c r="F45" s="29" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20569126</t>
+          <t>DDP MOW
+P20579726</t>
         </is>
       </c>
       <c r="G45" s="29" t="inlineStr">
@@ -26314,17 +26308,17 @@
       </c>
       <c r="I45" s="29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J45" s="29" t="inlineStr">
         <is>
-          <t>BOEING</t>
+          <t>B762</t>
         </is>
       </c>
       <c r="K45" s="29" t="inlineStr">
         <is>
-          <t>BUL216</t>
+          <t>RDAA8046-01</t>
         </is>
       </c>
       <c r="L45" s="29" t="n">
@@ -26332,11 +26326,11 @@
       </c>
       <c r="M45" s="29" t="inlineStr">
         <is>
-          <t>TRANSISTOR</t>
+          <t>CMT (TERMINAL ASSY-CAB. MANAGEMENT)</t>
         </is>
       </c>
       <c r="N45" s="31" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O45" s="29" t="inlineStr">
         <is>
@@ -26345,19 +26339,17 @@
       </c>
       <c r="P45" s="29" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q45" s="32" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="R45" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="S45" s="29" t="inlineStr">
-        <is>
-          <t>STK</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="S45" s="29" t="n">
+        <v>18</v>
       </c>
       <c r="T45" s="29" t="n">
         <v/>
@@ -26366,7 +26358,7 @@
         <v/>
       </c>
       <c r="V45" s="32" t="n">
-        <v>46324</v>
+        <v>46318</v>
       </c>
       <c r="W45" s="29" t="n">
         <v/>
@@ -26378,50 +26370,52 @@
       </c>
       <c r="Y45" s="29" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="Z45" s="29" t="inlineStr">
         <is>
-          <t>LUFTHANSA</t>
+          <t>IBERIA</t>
         </is>
       </c>
       <c r="AA45" s="29" t="inlineStr">
         <is>
-          <t>MOUSER ELECTRONICS</t>
-        </is>
-      </c>
-      <c r="AB45" s="29" t="n">
-        <v/>
+          <t>SEATTLE AVIATION SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="AB45" s="29" t="inlineStr">
+        <is>
+          <t>KTM110261615</t>
+        </is>
       </c>
       <c r="AC45" s="29" t="inlineStr">
         <is>
-          <t>#6261</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AD45" s="29" t="n">
         <v/>
       </c>
       <c r="AE45" s="33" t="n">
-        <v>2</v>
+        <v>3850</v>
       </c>
       <c r="AF45" s="33" t="n">
-        <v>40</v>
+        <v>3850</v>
       </c>
       <c r="AG45" s="33" t="n">
-        <v>16</v>
+        <v>6000</v>
       </c>
       <c r="AH45" s="33" t="n">
-        <v>320</v>
+        <v>6000</v>
       </c>
       <c r="AI45" s="33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AJ45" s="33" t="n">
         <v/>
       </c>
       <c r="AK45" s="33" t="n">
-        <v>0.4</v>
+        <v>193.0775</v>
       </c>
       <c r="AL45" s="33" t="n">
         <v/>
@@ -26430,19 +26424,21 @@
         <v/>
       </c>
       <c r="AN45" s="29" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AO45" s="29" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP45" s="29" t="n">
-        <v/>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP45" s="29" t="inlineStr">
+        <is>
+          <t>Получаем МПТ</t>
+        </is>
       </c>
       <c r="AQ45" s="29" t="inlineStr">
         <is>
-          <t>Частичная предоплата</t>
+          <t>Постоплата 100%</t>
         </is>
       </c>
       <c r="AR45" s="29" t="n">
@@ -26458,7 +26454,7 @@
         <v/>
       </c>
       <c r="AV45" s="33" t="n">
-        <v>320</v>
+        <v>6000</v>
       </c>
       <c r="AW45" s="29" t="n">
         <v/>
@@ -26467,20 +26463,16 @@
         <v/>
       </c>
       <c r="AY45" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="AZ45" s="29" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
+        <v>3850</v>
+      </c>
+      <c r="AZ45" s="34" t="n">
+        <v>46296</v>
       </c>
       <c r="BA45" s="29" t="n">
         <v/>
       </c>
-      <c r="BB45" s="29" t="inlineStr">
-        <is>
-          <t>UNCONFIRMED YET</t>
-        </is>
+      <c r="BB45" s="29" t="n">
+        <v/>
       </c>
       <c r="BC45" s="29" t="n">
         <v/>
@@ -26568,7 +26560,7 @@
       </c>
       <c r="K46" s="19" t="inlineStr">
         <is>
-          <t>154MKP275KE</t>
+          <t>BUL216</t>
         </is>
       </c>
       <c r="L46" s="19" t="n">
@@ -26576,7 +26568,7 @@
       </c>
       <c r="M46" s="19" t="inlineStr">
         <is>
-          <t>CAPACITOR FILM</t>
+          <t>TRANSISTOR</t>
         </is>
       </c>
       <c r="N46" s="20" t="n">
@@ -26640,23 +26632,23 @@
       </c>
       <c r="AC46" s="19" t="inlineStr">
         <is>
-          <t>#6262</t>
+          <t>#6261</t>
         </is>
       </c>
       <c r="AD46" s="19" t="n">
         <v/>
       </c>
       <c r="AE46" s="21" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="AF46" s="21" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="AG46" s="21" t="n">
-        <v>12.3</v>
+        <v>16</v>
       </c>
       <c r="AH46" s="21" t="n">
-        <v>246</v>
+        <v>320</v>
       </c>
       <c r="AI46" s="21" t="n">
         <v>50</v>
@@ -26665,7 +26657,7 @@
         <v/>
       </c>
       <c r="AK46" s="21" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="AL46" s="21" t="n">
         <v/>
@@ -26702,7 +26694,7 @@
         <v/>
       </c>
       <c r="AV46" s="21" t="n">
-        <v>246</v>
+        <v>320</v>
       </c>
       <c r="AW46" s="19" t="n">
         <v/>
@@ -26711,7 +26703,7 @@
         <v/>
       </c>
       <c r="AY46" s="19" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="AZ46" s="19" t="inlineStr">
         <is>
@@ -26812,7 +26804,7 @@
       </c>
       <c r="K47" s="29" t="inlineStr">
         <is>
-          <t>224MKP275KB</t>
+          <t>154MKP275KE</t>
         </is>
       </c>
       <c r="L47" s="29" t="n">
@@ -26884,23 +26876,23 @@
       </c>
       <c r="AC47" s="29" t="inlineStr">
         <is>
-          <t>#6263</t>
+          <t>#6262</t>
         </is>
       </c>
       <c r="AD47" s="29" t="n">
         <v/>
       </c>
       <c r="AE47" s="33" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AF47" s="33" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AG47" s="33" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="AH47" s="33" t="n">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="AI47" s="33" t="n">
         <v>50</v>
@@ -26909,7 +26901,7 @@
         <v/>
       </c>
       <c r="AK47" s="33" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="AL47" s="33" t="n">
         <v/>
@@ -26946,7 +26938,7 @@
         <v/>
       </c>
       <c r="AV47" s="33" t="n">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="AW47" s="29" t="n">
         <v/>
@@ -26955,7 +26947,7 @@
         <v/>
       </c>
       <c r="AY47" s="29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ47" s="29" t="inlineStr">
         <is>
@@ -27056,7 +27048,7 @@
       </c>
       <c r="K48" s="19" t="inlineStr">
         <is>
-          <t>B32642B0183J</t>
+          <t>224MKP275KB</t>
         </is>
       </c>
       <c r="L48" s="19" t="n">
@@ -27128,7 +27120,7 @@
       </c>
       <c r="AC48" s="19" t="inlineStr">
         <is>
-          <t>#6264</t>
+          <t>#6263</t>
         </is>
       </c>
       <c r="AD48" s="19" t="n">
@@ -27250,7 +27242,7 @@
     </row>
     <row r="49">
       <c r="A49" s="29" t="n">
-        <v>30092609185</v>
+        <v>29092616005</v>
       </c>
       <c r="B49" s="29" t="inlineStr">
         <is>
@@ -27264,7 +27256,7 @@
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>KDV-3</t>
+          <t>KDV-1</t>
         </is>
       </c>
       <c r="E49" s="40" t="inlineStr">
@@ -27274,8 +27266,8 @@
       </c>
       <c r="F49" s="29" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20595226</t>
+          <t>DAT MOW
+P20569126</t>
         </is>
       </c>
       <c r="G49" s="29" t="inlineStr">
@@ -27290,17 +27282,17 @@
       </c>
       <c r="I49" s="29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J49" s="29" t="inlineStr">
         <is>
-          <t>B737</t>
+          <t>BOEING</t>
         </is>
       </c>
       <c r="K49" s="29" t="inlineStr">
         <is>
-          <t>S152-0020-00</t>
+          <t>B32642B0183J</t>
         </is>
       </c>
       <c r="L49" s="29" t="n">
@@ -27308,11 +27300,11 @@
       </c>
       <c r="M49" s="29" t="inlineStr">
         <is>
-          <t>CVR PANEL</t>
+          <t>CAPACITOR FILM</t>
         </is>
       </c>
       <c r="N49" s="31" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O49" s="29" t="inlineStr">
         <is>
@@ -27321,11 +27313,11 @@
       </c>
       <c r="P49" s="29" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q49" s="32" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="R49" s="29" t="n">
         <v>30</v>
@@ -27342,7 +27334,7 @@
         <v/>
       </c>
       <c r="V49" s="32" t="n">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="W49" s="29" t="n">
         <v/>
@@ -27354,7 +27346,7 @@
       </c>
       <c r="Y49" s="29" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z49" s="29" t="inlineStr">
@@ -27362,42 +27354,42 @@
           <t>LUFTHANSA</t>
         </is>
       </c>
-      <c r="AA49" s="29" t="n">
-        <v/>
+      <c r="AA49" s="29" t="inlineStr">
+        <is>
+          <t>MOUSER ELECTRONICS</t>
+        </is>
       </c>
       <c r="AB49" s="29" t="n">
         <v/>
       </c>
       <c r="AC49" s="29" t="inlineStr">
         <is>
-          <t>#6265</t>
-        </is>
-      </c>
-      <c r="AD49" s="29" t="inlineStr">
-        <is>
-          <t>000523364</t>
-        </is>
+          <t>#6264</t>
+        </is>
+      </c>
+      <c r="AD49" s="29" t="n">
+        <v/>
       </c>
       <c r="AE49" s="33" t="n">
-        <v>8800</v>
+        <v>0.6</v>
       </c>
       <c r="AF49" s="33" t="n">
-        <v>8800</v>
+        <v>12</v>
       </c>
       <c r="AG49" s="33" t="n">
-        <v>12000</v>
+        <v>13.3</v>
       </c>
       <c r="AH49" s="33" t="n">
-        <v>12000</v>
+        <v>266</v>
       </c>
       <c r="AI49" s="33" t="n">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="AJ49" s="33" t="n">
         <v/>
       </c>
       <c r="AK49" s="33" t="n">
-        <v>88</v>
+        <v>0.12</v>
       </c>
       <c r="AL49" s="33" t="n">
         <v/>
@@ -27406,21 +27398,19 @@
         <v/>
       </c>
       <c r="AN49" s="29" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AO49" s="29" t="inlineStr">
         <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP49" s="29" t="inlineStr">
-        <is>
-          <t>Получаем МПТ</t>
-        </is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP49" s="29" t="n">
+        <v/>
       </c>
       <c r="AQ49" s="29" t="inlineStr">
         <is>
-          <t>Постоплата 100%</t>
+          <t>Частичная предоплата</t>
         </is>
       </c>
       <c r="AR49" s="29" t="n">
@@ -27436,7 +27426,7 @@
         <v/>
       </c>
       <c r="AV49" s="33" t="n">
-        <v>12000</v>
+        <v>266</v>
       </c>
       <c r="AW49" s="29" t="n">
         <v/>
@@ -27445,10 +27435,12 @@
         <v/>
       </c>
       <c r="AY49" s="29" t="n">
-        <v>8800</v>
-      </c>
-      <c r="AZ49" s="34" t="n">
-        <v>46295</v>
+        <v>12</v>
+      </c>
+      <c r="AZ49" s="29" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
       </c>
       <c r="BA49" s="29" t="n">
         <v/>
@@ -27494,7 +27486,7 @@
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>30092610505</v>
+        <v>30092609185</v>
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
@@ -27508,7 +27500,7 @@
       </c>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>KDV-1</t>
+          <t>KDV-3</t>
         </is>
       </c>
       <c r="E50" s="40" t="inlineStr">
@@ -27518,8 +27510,8 @@
       </c>
       <c r="F50" s="19" t="inlineStr">
         <is>
-          <t>DAT MOW
-P20580226</t>
+          <t>DDP MOW
+P20595226</t>
         </is>
       </c>
       <c r="G50" s="19" t="inlineStr">
@@ -27534,17 +27526,17 @@
       </c>
       <c r="I50" s="19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J50" s="19" t="inlineStr">
         <is>
-          <t>B762</t>
+          <t>B737</t>
         </is>
       </c>
       <c r="K50" s="19" t="inlineStr">
         <is>
-          <t>GR501BB4-4</t>
+          <t>S152-0020-00</t>
         </is>
       </c>
       <c r="L50" s="19" t="n">
@@ -27552,11 +27544,11 @@
       </c>
       <c r="M50" s="19" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>CVR PANEL</t>
         </is>
       </c>
       <c r="N50" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O50" s="19" t="inlineStr">
         <is>
@@ -27565,14 +27557,14 @@
       </c>
       <c r="P50" s="19" t="inlineStr">
         <is>
-          <t>EXPENDABLE</t>
+          <t>ROTABLE</t>
         </is>
       </c>
       <c r="Q50" s="35" t="n">
         <v>46295</v>
       </c>
       <c r="R50" s="19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="S50" s="19" t="inlineStr">
         <is>
@@ -27586,7 +27578,7 @@
         <v/>
       </c>
       <c r="V50" s="35" t="n">
-        <v>46320</v>
+        <v>46325</v>
       </c>
       <c r="W50" s="19" t="n">
         <v/>
@@ -27598,12 +27590,12 @@
       </c>
       <c r="Y50" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z50" s="19" t="inlineStr">
         <is>
-          <t>BLUE OCEAN SOLUTIONS</t>
+          <t>LUFTHANSA</t>
         </is>
       </c>
       <c r="AA50" s="19" t="n">
@@ -27614,49 +27606,53 @@
       </c>
       <c r="AC50" s="19" t="inlineStr">
         <is>
-          <t>№2442</t>
-        </is>
-      </c>
-      <c r="AD50" s="19" t="n">
-        <v/>
+          <t>#6265</t>
+        </is>
+      </c>
+      <c r="AD50" s="19" t="inlineStr">
+        <is>
+          <t>000523364</t>
+        </is>
       </c>
       <c r="AE50" s="21" t="n">
-        <v>205.44</v>
+        <v>8800</v>
       </c>
       <c r="AF50" s="21" t="n">
-        <v>821.76</v>
+        <v>8800</v>
       </c>
       <c r="AG50" s="21" t="n">
-        <v>340</v>
+        <v>12000</v>
       </c>
       <c r="AH50" s="21" t="n">
-        <v>1360</v>
+        <v>12000</v>
       </c>
       <c r="AI50" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="AJ50" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AK50" s="21" t="n">
+        <v>88</v>
+      </c>
+      <c r="AL50" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AM50" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AN50" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ50" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AK50" s="21" t="n">
-        <v>41.211264</v>
-      </c>
-      <c r="AL50" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AM50" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AN50" s="19" t="n">
-        <v>0.22</v>
-      </c>
       <c r="AO50" s="19" t="inlineStr">
         <is>
-          <t>Не применимо</t>
-        </is>
-      </c>
-      <c r="AP50" s="19" t="n">
-        <v/>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP50" s="19" t="inlineStr">
+        <is>
+          <t>Получаем МПТ</t>
+        </is>
       </c>
       <c r="AQ50" s="19" t="inlineStr">
         <is>
@@ -27676,7 +27672,7 @@
         <v/>
       </c>
       <c r="AV50" s="21" t="n">
-        <v>1360</v>
+        <v>12000</v>
       </c>
       <c r="AW50" s="19" t="n">
         <v/>
@@ -27685,7 +27681,7 @@
         <v/>
       </c>
       <c r="AY50" s="19" t="n">
-        <v>821.76</v>
+        <v>8800</v>
       </c>
       <c r="AZ50" s="36" t="n">
         <v>46295</v>
@@ -27723,10 +27719,10 @@
         <v/>
       </c>
       <c r="BK50" s="19" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="BL50" s="19" t="n">
-        <v>821.76</v>
+        <v/>
       </c>
       <c r="BM50" s="19" t="n">
         <v/>
@@ -27734,7 +27730,7 @@
     </row>
     <row r="51">
       <c r="A51" s="29" t="n">
-        <v>30092615555</v>
+        <v>30092610505</v>
       </c>
       <c r="B51" s="29" t="inlineStr">
         <is>
@@ -27748,7 +27744,7 @@
       </c>
       <c r="D51" s="29" t="inlineStr">
         <is>
-          <t>KDV-3</t>
+          <t>KDV-1</t>
         </is>
       </c>
       <c r="E51" s="40" t="inlineStr">
@@ -27758,8 +27754,8 @@
       </c>
       <c r="F51" s="29" t="inlineStr">
         <is>
-          <t>DDP MOW
-P20594626</t>
+          <t>DAT MOW
+P20580226</t>
         </is>
       </c>
       <c r="G51" s="29" t="inlineStr">
@@ -27774,17 +27770,17 @@
       </c>
       <c r="I51" s="29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J51" s="29" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>B762</t>
         </is>
       </c>
       <c r="K51" s="29" t="inlineStr">
         <is>
-          <t>2116M23P01</t>
+          <t>GR501BB4-4</t>
         </is>
       </c>
       <c r="L51" s="29" t="n">
@@ -27792,11 +27788,11 @@
       </c>
       <c r="M51" s="29" t="inlineStr">
         <is>
-          <t>314 HPC STAGE 3 DISK</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="N51" s="31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O51" s="29" t="inlineStr">
         <is>
@@ -27805,14 +27801,14 @@
       </c>
       <c r="P51" s="29" t="inlineStr">
         <is>
-          <t>ROTABLE</t>
+          <t>EXPENDABLE</t>
         </is>
       </c>
       <c r="Q51" s="32" t="n">
         <v>46295</v>
       </c>
       <c r="R51" s="29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="S51" s="29" t="inlineStr">
         <is>
@@ -27826,7 +27822,7 @@
         <v/>
       </c>
       <c r="V51" s="32" t="n">
-        <v>46325</v>
+        <v>46320</v>
       </c>
       <c r="W51" s="29" t="n">
         <v/>
@@ -27838,54 +27834,48 @@
       </c>
       <c r="Y51" s="29" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="Z51" s="29" t="inlineStr">
         <is>
-          <t>SOHO AERO</t>
+          <t>BLUE OCEAN SOLUTIONS</t>
         </is>
       </c>
       <c r="AA51" s="29" t="n">
         <v/>
       </c>
-      <c r="AB51" s="29" t="inlineStr">
-        <is>
-          <t>LS-261001-1</t>
-        </is>
+      <c r="AB51" s="29" t="n">
+        <v/>
       </c>
       <c r="AC51" s="29" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD51" s="29" t="inlineStr">
-        <is>
-          <t>XAECR005</t>
-        </is>
+          <t>№2442</t>
+        </is>
+      </c>
+      <c r="AD51" s="29" t="n">
+        <v/>
       </c>
       <c r="AE51" s="33" t="n">
-        <v>85000</v>
+        <v>205.44</v>
       </c>
       <c r="AF51" s="33" t="n">
-        <v>85000</v>
+        <v>821.76</v>
       </c>
       <c r="AG51" s="33" t="n">
-        <v>140000</v>
+        <v>340</v>
       </c>
       <c r="AH51" s="33" t="n">
-        <v>140000</v>
+        <v>1360</v>
       </c>
       <c r="AI51" s="33" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AJ51" s="33" t="n">
         <v/>
       </c>
-      <c r="AK51" s="33" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
+      <c r="AK51" s="33" t="n">
+        <v>41.211264</v>
       </c>
       <c r="AL51" s="33" t="n">
         <v/>
@@ -27894,87 +27884,85 @@
         <v/>
       </c>
       <c r="AN51" s="29" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AO51" s="29" t="inlineStr">
+        <is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="AP51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AQ51" s="29" t="inlineStr">
+        <is>
+          <t>Постоплата 100%</t>
+        </is>
+      </c>
+      <c r="AR51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AS51" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AT51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AU51" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AV51" s="33" t="n">
+        <v>1360</v>
+      </c>
+      <c r="AW51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AX51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AY51" s="29" t="n">
+        <v>821.76</v>
+      </c>
+      <c r="AZ51" s="34" t="n">
+        <v>46295</v>
+      </c>
+      <c r="BA51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BB51" s="29" t="inlineStr">
+        <is>
+          <t>UNCONFIRMED YET</t>
+        </is>
+      </c>
+      <c r="BC51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BD51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BE51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BF51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BG51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BH51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BI51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BJ51" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BK51" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AO51" s="29" t="inlineStr">
-        <is>
-          <t>НЕТ МПТ</t>
-        </is>
-      </c>
-      <c r="AP51" s="29" t="inlineStr">
-        <is>
-          <t>Получаем МПТ</t>
-        </is>
-      </c>
-      <c r="AQ51" s="29" t="inlineStr">
-        <is>
-          <t>Частичная предоплата</t>
-        </is>
-      </c>
-      <c r="AR51" s="29" t="inlineStr">
-        <is>
-          <t>PLAN 08.10</t>
-        </is>
-      </c>
-      <c r="AS51" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AT51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AU51" s="33" t="n">
-        <v/>
-      </c>
-      <c r="AV51" s="33" t="n">
-        <v>140000</v>
-      </c>
-      <c r="AW51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AX51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="AY51" s="29" t="n">
-        <v>85000</v>
-      </c>
-      <c r="AZ51" s="34" t="n">
-        <v>46296</v>
-      </c>
-      <c r="BA51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BB51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BC51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BD51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BE51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BF51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BG51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BH51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BI51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BJ51" s="29" t="n">
-        <v/>
-      </c>
-      <c r="BK51" s="29" t="n">
-        <v/>
-      </c>
       <c r="BL51" s="29" t="n">
-        <v/>
+        <v>821.76</v>
       </c>
       <c r="BM51" s="29" t="n">
         <v/>
@@ -27982,493 +27970,741 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
+        <v>30092615555</v>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>М</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>Ray</t>
+        </is>
+      </c>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>KDV-3</t>
+        </is>
+      </c>
+      <c r="E52" s="40" t="inlineStr">
+        <is>
+          <t>1 NOT PAID</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="inlineStr">
+        <is>
+          <t>DDP MOW
+P20594626</t>
+        </is>
+      </c>
+      <c r="G52" s="19" t="inlineStr">
+        <is>
+          <t>Utair</t>
+        </is>
+      </c>
+      <c r="H52" s="19" t="inlineStr">
+        <is>
+          <t>комм</t>
+        </is>
+      </c>
+      <c r="I52" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J52" s="19" t="inlineStr">
+        <is>
+          <t>B738</t>
+        </is>
+      </c>
+      <c r="K52" s="19" t="inlineStr">
+        <is>
+          <t>2116M23P01</t>
+        </is>
+      </c>
+      <c r="L52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="M52" s="19" t="inlineStr">
+        <is>
+          <t>314 HPC STAGE 3 DISK</t>
+        </is>
+      </c>
+      <c r="N52" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="19" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="P52" s="19" t="inlineStr">
+        <is>
+          <t>ROTABLE</t>
+        </is>
+      </c>
+      <c r="Q52" s="35" t="n">
+        <v>46295</v>
+      </c>
+      <c r="R52" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="S52" s="19" t="inlineStr">
+        <is>
+          <t>STK</t>
+        </is>
+      </c>
+      <c r="T52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="35" t="n">
+        <v>46325</v>
+      </c>
+      <c r="W52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="X52" s="19" t="inlineStr">
+        <is>
+          <t>Продажа от поставщика</t>
+        </is>
+      </c>
+      <c r="Y52" s="19" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="Z52" s="19" t="inlineStr">
+        <is>
+          <t>SOHO AERO</t>
+        </is>
+      </c>
+      <c r="AA52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AB52" s="19" t="inlineStr">
+        <is>
+          <t>LS-261001-1</t>
+        </is>
+      </c>
+      <c r="AC52" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD52" s="19" t="inlineStr">
+        <is>
+          <t>XAECR005</t>
+        </is>
+      </c>
+      <c r="AE52" s="21" t="n">
+        <v>85000</v>
+      </c>
+      <c r="AF52" s="21" t="n">
+        <v>85000</v>
+      </c>
+      <c r="AG52" s="21" t="n">
+        <v>140000</v>
+      </c>
+      <c r="AH52" s="21" t="n">
+        <v>140000</v>
+      </c>
+      <c r="AI52" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AJ52" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AK52" s="21" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="AL52" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AM52" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AN52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="19" t="inlineStr">
+        <is>
+          <t>НЕТ МПТ</t>
+        </is>
+      </c>
+      <c r="AP52" s="19" t="inlineStr">
+        <is>
+          <t>Получаем МПТ</t>
+        </is>
+      </c>
+      <c r="AQ52" s="19" t="inlineStr">
+        <is>
+          <t>Частичная предоплата</t>
+        </is>
+      </c>
+      <c r="AR52" s="19" t="inlineStr">
+        <is>
+          <t>PLAN 08.10</t>
+        </is>
+      </c>
+      <c r="AS52" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AT52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AU52" s="21" t="n">
+        <v/>
+      </c>
+      <c r="AV52" s="21" t="n">
+        <v>140000</v>
+      </c>
+      <c r="AW52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AX52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="AY52" s="19" t="n">
+        <v>85000</v>
+      </c>
+      <c r="AZ52" s="36" t="n">
+        <v>46296</v>
+      </c>
+      <c r="BA52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BB52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BC52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BD52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BE52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BF52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BG52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BH52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BI52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BJ52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BK52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BL52" s="19" t="n">
+        <v/>
+      </c>
+      <c r="BM52" s="19" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="n">
         <v>1102611065</v>
       </c>
-      <c r="B52" s="19" t="inlineStr">
+      <c r="B53" s="29" t="inlineStr">
         <is>
           <t>М</t>
         </is>
       </c>
-      <c r="C52" s="19" t="inlineStr">
+      <c r="C53" s="29" t="inlineStr">
         <is>
           <t>Ray</t>
         </is>
       </c>
-      <c r="D52" s="19" t="inlineStr">
+      <c r="D53" s="29" t="inlineStr">
         <is>
           <t>KDV-3</t>
         </is>
       </c>
-      <c r="E52" s="40" t="inlineStr">
+      <c r="E53" s="40" t="inlineStr">
         <is>
           <t>1 NOT PAID</t>
         </is>
       </c>
-      <c r="F52" s="19" t="inlineStr">
+      <c r="F53" s="29" t="inlineStr">
         <is>
           <t>DDP MOW
 P20576726</t>
         </is>
       </c>
-      <c r="G52" s="19" t="inlineStr">
+      <c r="G53" s="29" t="inlineStr">
         <is>
           <t>Utair</t>
         </is>
       </c>
-      <c r="H52" s="19" t="inlineStr">
+      <c r="H53" s="29" t="inlineStr">
         <is>
           <t>комм</t>
         </is>
       </c>
-      <c r="I52" s="19" t="inlineStr">
+      <c r="I53" s="29" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J52" s="19" t="inlineStr">
+      <c r="J53" s="29" t="inlineStr">
         <is>
           <t>B762</t>
         </is>
       </c>
-      <c r="K52" s="19" t="inlineStr">
+      <c r="K53" s="29" t="inlineStr">
         <is>
           <t>314U2200-23</t>
         </is>
       </c>
-      <c r="L52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="19" t="inlineStr">
+      <c r="L53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="M53" s="29" t="inlineStr">
         <is>
           <t>PLUG ASSY</t>
         </is>
       </c>
-      <c r="N52" s="20" t="n">
+      <c r="N53" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="O52" s="19" t="inlineStr">
+      <c r="O53" s="29" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="P52" s="19" t="inlineStr">
+      <c r="P53" s="29" t="inlineStr">
         <is>
           <t>ROTABLE</t>
         </is>
       </c>
-      <c r="Q52" s="35" t="n">
+      <c r="Q53" s="32" t="n">
         <v>46296</v>
       </c>
-      <c r="R52" s="19" t="n">
+      <c r="R53" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="S52" s="19" t="inlineStr">
+      <c r="S53" s="29" t="inlineStr">
         <is>
           <t>STK</t>
         </is>
       </c>
-      <c r="T52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="35" t="n">
+      <c r="T53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="32" t="n">
         <v>46326</v>
       </c>
-      <c r="W52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="X52" s="19" t="inlineStr">
+      <c r="W53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="X53" s="29" t="inlineStr">
         <is>
           <t>Продажа от поставщика</t>
         </is>
       </c>
-      <c r="Y52" s="19" t="inlineStr">
+      <c r="Y53" s="29" t="inlineStr">
         <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="Z52" s="19" t="inlineStr">
+      <c r="Z53" s="29" t="inlineStr">
         <is>
           <t>LUFTHANSA</t>
         </is>
       </c>
-      <c r="AA52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AB52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AC52" s="19" t="inlineStr">
+      <c r="AA53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AB53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AC53" s="29" t="inlineStr">
         <is>
           <t>#6266</t>
         </is>
       </c>
-      <c r="AD52" s="19" t="inlineStr">
+      <c r="AD53" s="29" t="inlineStr">
         <is>
           <t>1356-A</t>
         </is>
       </c>
-      <c r="AE52" s="21" t="n">
+      <c r="AE53" s="33" t="n">
         <v>5500</v>
       </c>
-      <c r="AF52" s="21" t="n">
+      <c r="AF53" s="33" t="n">
         <v>5500</v>
       </c>
-      <c r="AG52" s="21" t="n">
+      <c r="AG53" s="33" t="n">
         <v>7500</v>
       </c>
-      <c r="AH52" s="21" t="n">
+      <c r="AH53" s="33" t="n">
         <v>7500</v>
       </c>
-      <c r="AI52" s="21" t="n">
+      <c r="AI53" s="33" t="n">
         <v>500</v>
       </c>
-      <c r="AJ52" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AK52" s="21" t="n">
+      <c r="AJ53" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AK53" s="33" t="n">
         <v>55</v>
       </c>
-      <c r="AL52" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AM52" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AN52" s="19" t="n">
+      <c r="AL53" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AM53" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AN53" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AO52" s="19" t="inlineStr">
+      <c r="AO53" s="29" t="inlineStr">
         <is>
           <t>НЕТ МПТ</t>
         </is>
       </c>
-      <c r="AP52" s="19" t="inlineStr">
+      <c r="AP53" s="29" t="inlineStr">
         <is>
           <t>Получаем МПТ</t>
         </is>
       </c>
-      <c r="AQ52" s="19" t="inlineStr">
+      <c r="AQ53" s="29" t="inlineStr">
         <is>
           <t>Частичная предоплата</t>
         </is>
       </c>
-      <c r="AR52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AS52" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AT52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AU52" s="21" t="n">
-        <v/>
-      </c>
-      <c r="AV52" s="21" t="n">
+      <c r="AR53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AS53" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AT53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AU53" s="33" t="n">
+        <v/>
+      </c>
+      <c r="AV53" s="33" t="n">
         <v>7500</v>
       </c>
-      <c r="AW52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AX52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="AY52" s="19" t="n">
+      <c r="AW53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AX53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="AY53" s="29" t="n">
         <v>5500</v>
       </c>
-      <c r="AZ52" s="36" t="n">
+      <c r="AZ53" s="34" t="n">
         <v>46296</v>
       </c>
-      <c r="BA52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BB52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BC52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BD52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BE52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BF52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BG52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BH52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BI52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BJ52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BK52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BL52" s="19" t="n">
-        <v/>
-      </c>
-      <c r="BM52" s="19" t="n">
+      <c r="BA53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BB53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BC53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BD53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BE53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BF53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BG53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BH53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BI53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BJ53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BK53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BL53" s="29" t="n">
+        <v/>
+      </c>
+      <c r="BM53" s="29" t="n">
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="54">
+      <c r="A54" t="n">
         <v>1102611295</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>М</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Ray</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>KDV-3</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>1 NOT PAID</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>DDP MOW
 P20584726</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Utair</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>комм</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>737CL</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>622-8001-350</t>
         </is>
       </c>
-      <c r="L53" t="n">
-        <v/>
-      </c>
-      <c r="M53" t="inlineStr">
+      <c r="L54" t="n">
+        <v/>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t>PANEL ASSY</t>
         </is>
       </c>
-      <c r="N53" t="n">
+      <c r="N54" t="n">
         <v>2</v>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>ROTABLE</t>
         </is>
       </c>
-      <c r="Q53" s="38" t="n">
+      <c r="Q54" s="38" t="n">
         <v>46296</v>
       </c>
-      <c r="R53" t="n">
+      <c r="R54" t="n">
         <v>30</v>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>STK</t>
         </is>
       </c>
-      <c r="T53" t="n">
-        <v/>
-      </c>
-      <c r="U53" t="n">
-        <v/>
-      </c>
-      <c r="V53" t="n">
-        <v/>
-      </c>
-      <c r="W53" t="n">
-        <v/>
-      </c>
-      <c r="X53" t="inlineStr">
+      <c r="T54" t="n">
+        <v/>
+      </c>
+      <c r="U54" t="n">
+        <v/>
+      </c>
+      <c r="V54" t="n">
+        <v/>
+      </c>
+      <c r="W54" t="n">
+        <v/>
+      </c>
+      <c r="X54" t="inlineStr">
         <is>
           <t>Продажа от поставщика</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>RP</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>JET TECHNIC</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>JMF GLOBAL</t>
         </is>
       </c>
-      <c r="AB53" t="n">
-        <v/>
-      </c>
-      <c r="AC53" t="inlineStr">
+      <c r="AB54" t="n">
+        <v/>
+      </c>
+      <c r="AC54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AD53" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>873
 1509</t>
         </is>
       </c>
-      <c r="AE53" t="n">
+      <c r="AE54" t="n">
         <v>10000</v>
       </c>
-      <c r="AF53" t="n">
+      <c r="AF54" t="n">
         <v>20000</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AG54" t="n">
         <v>13500</v>
       </c>
-      <c r="AH53" t="n">
+      <c r="AH54" t="n">
         <v>27000</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AI54" t="n">
         <v>1000</v>
       </c>
-      <c r="AJ53" t="n">
-        <v/>
-      </c>
-      <c r="AK53" t="n">
+      <c r="AJ54" t="n">
+        <v/>
+      </c>
+      <c r="AK54" t="n">
         <v>1003</v>
       </c>
-      <c r="AL53" t="n">
-        <v/>
-      </c>
-      <c r="AM53" t="n">
-        <v/>
-      </c>
-      <c r="AN53" t="n">
+      <c r="AL54" t="n">
+        <v/>
+      </c>
+      <c r="AM54" t="n">
+        <v/>
+      </c>
+      <c r="AN54" t="n">
         <v>0</v>
       </c>
-      <c r="AO53" t="inlineStr">
+      <c r="AO54" t="inlineStr">
         <is>
           <t>НЕТ МПТ</t>
         </is>
       </c>
-      <c r="AP53" t="inlineStr">
+      <c r="AP54" t="inlineStr">
         <is>
           <t>Получаем МПТ</t>
         </is>
       </c>
-      <c r="AQ53" t="inlineStr">
+      <c r="AQ54" t="inlineStr">
         <is>
           <t>Частичная предоплата</t>
         </is>
       </c>
-      <c r="AR53" t="n">
-        <v/>
-      </c>
-      <c r="AS53" t="n">
-        <v/>
-      </c>
-      <c r="AT53" t="n">
-        <v/>
-      </c>
-      <c r="AU53" t="n">
-        <v/>
-      </c>
-      <c r="AV53" t="n">
+      <c r="AR54" t="n">
+        <v/>
+      </c>
+      <c r="AS54" t="n">
+        <v/>
+      </c>
+      <c r="AT54" t="n">
+        <v/>
+      </c>
+      <c r="AU54" t="n">
+        <v/>
+      </c>
+      <c r="AV54" t="n">
         <v>27000</v>
       </c>
-      <c r="AW53" t="n">
-        <v/>
-      </c>
-      <c r="AX53" t="n">
-        <v/>
-      </c>
-      <c r="AY53" t="n">
+      <c r="AW54" t="n">
+        <v/>
+      </c>
+      <c r="AX54" t="n">
+        <v/>
+      </c>
+      <c r="AY54" t="n">
         <v>20000</v>
       </c>
-      <c r="AZ53" s="38" t="n">
+      <c r="AZ54" s="38" t="n">
         <v>46296</v>
       </c>
-      <c r="BA53" t="n">
-        <v/>
-      </c>
-      <c r="BB53" t="n">
-        <v/>
-      </c>
-      <c r="BC53" t="n">
-        <v/>
-      </c>
-      <c r="BD53" t="n">
-        <v/>
-      </c>
-      <c r="BE53" t="n">
-        <v/>
-      </c>
-      <c r="BF53" t="n">
-        <v/>
-      </c>
-      <c r="BG53" t="n">
-        <v/>
-      </c>
-      <c r="BH53" t="n">
-        <v/>
-      </c>
-      <c r="BI53" t="n">
-        <v/>
-      </c>
-      <c r="BJ53" t="n">
-        <v/>
-      </c>
-      <c r="BK53" t="n">
-        <v/>
-      </c>
-      <c r="BL53" t="n">
-        <v/>
-      </c>
-      <c r="BM53" t="n">
+      <c r="BA54" t="n">
+        <v/>
+      </c>
+      <c r="BB54" t="n">
+        <v/>
+      </c>
+      <c r="BC54" t="n">
+        <v/>
+      </c>
+      <c r="BD54" t="n">
+        <v/>
+      </c>
+      <c r="BE54" t="n">
+        <v/>
+      </c>
+      <c r="BF54" t="n">
+        <v/>
+      </c>
+      <c r="BG54" t="n">
+        <v/>
+      </c>
+      <c r="BH54" t="n">
+        <v/>
+      </c>
+      <c r="BI54" t="n">
+        <v/>
+      </c>
+      <c r="BJ54" t="n">
+        <v/>
+      </c>
+      <c r="BK54" t="n">
+        <v/>
+      </c>
+      <c r="BL54" t="n">
+        <v/>
+      </c>
+      <c r="BM54" t="n">
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BM52"/>
+  <autoFilter ref="A1:BM53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>